--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_21.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_21.xlsx
@@ -625,158 +625,158 @@
         <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01624151499343185</v>
+        <v>0.01679749960251797</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.772713159684116</v>
+        <v>-2.739288469885686</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.628113260816249</v>
+        <v>-6.593035361420881</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.06708234339716768</v>
+        <v>-0.03110807092733836</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.705667265017745</v>
+        <v>-7.640428614755585</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.670082914695996</v>
+        <v>-2.604985877919965</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.013371892548243</v>
+        <v>-0.9473305477588241</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.13694273275285</v>
+        <v>1.203357616995213</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.462303106021778</v>
+        <v>8.528750236127422</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.98084031943539</v>
+        <v>15.04825313346637</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.25885045804526</v>
+        <v>15.32598114734093</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.98497580830052</v>
+        <v>15.05246475335613</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13.86891673700652</v>
+        <v>13.93774088649685</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.22078204554511</v>
+        <v>11.2898898584355</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>8.134889467832245</v>
+        <v>8.2047896495286</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.864656502709266</v>
+        <v>3.93389164553686</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-8.436881859342151</v>
+        <v>-8.367482929004744</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-10.97875561971549</v>
+        <v>-10.90919530158192</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-10.76616429079498</v>
+        <v>-10.69680960396663</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-3.274170659523868</v>
+        <v>-3.204977712709223</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.055896882188193</v>
+        <v>1.125770623501211</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>5.855577273685192</v>
+        <v>5.925584528686976</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>3.693945867579657</v>
+        <v>3.763671194123866</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>1.18028811867066</v>
+        <v>1.250142466377383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 25.78</t>
+          <t>X ≈ 25.79</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>54</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.32652688059337</v>
+        <v>-7.293558427332925</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3048036328217236</v>
+        <v>-0.2713662053236021</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.784252619161542</v>
+        <v>3.819403939566399</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.596555189875211</v>
+        <v>8.632588872579859</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.75937610117285</v>
+        <v>13.82475535632641</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15.79124179798357</v>
+        <v>15.85645353384008</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.86925069085418</v>
+        <v>16.93539714772994</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.59774863937882</v>
+        <v>16.66424840726886</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>16.64359281469366</v>
+        <v>16.71008047203937</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15.87838211504705</v>
+        <v>15.94579583279398</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>18.00121525714607</v>
+        <v>18.06835600723478</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.57334582287449</v>
+        <v>19.64085242742925</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22.15009972307842</v>
+        <v>22.2189551184069</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>18.24409354390466</v>
+        <v>18.31322439832329</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>15.74626276122837</v>
+        <v>15.81618502589547</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>18.19204944354643</v>
+        <v>18.26132401288118</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>16.21667872687239</v>
+        <v>16.28613779724974</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>14.26855981273553</v>
+        <v>14.33817272239568</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>12.63984591031761</v>
+        <v>12.70924096623911</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>16.52980313144064</v>
+        <v>16.59902354308744</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>17.84245335716327</v>
+        <v>17.91234451753041</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>15.92150623682652</v>
+        <v>15.99152018727293</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>16.20133296547916</v>
+        <v>16.27106252809931</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.42690058479531</v>
+        <v>12.49675493250218</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>74</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.989104782892376</v>
+        <v>-4.95612987617563</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.324887818273474</v>
+        <v>-5.291503744355992</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.442244102429861</v>
+        <v>-9.407209939458255</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.813055905868886</v>
+        <v>-8.777164172969123</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.835899963932867</v>
+        <v>-7.770691370146643</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.621382305251721</v>
+        <v>-3.556315473151251</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.735589580813091</v>
+        <v>-5.669601189891914</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.742442791615161</v>
+        <v>4.808861903670945</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.47466666954837</v>
+        <v>7.54109485289186</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.397701097497951</v>
+        <v>9.465073768583437</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.290823070018597</v>
+        <v>4.357889163228066</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.706240380900468</v>
+        <v>6.773682689024881</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.66796922372669</v>
+        <v>13.73678556423605</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.79917081922365</v>
+        <v>14.86828499148386</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>12.79985582670715</v>
+        <v>12.86976404505945</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>8.005730667695538</v>
+        <v>8.074970345972886</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>14.61715890026016</v>
+        <v>14.68661089186236</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.8196483327993</v>
+        <v>11.88925276992596</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>9.340937412582186</v>
+        <v>9.410323478310126</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.23008445099796</v>
+        <v>12.29929657154416</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>13.04151155517933</v>
+        <v>13.11139600120847</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>8.918514466393198</v>
+        <v>8.98852206164775</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>11.89817890897105</v>
+        <v>11.96790638363481</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>14.52900268689712</v>
+        <v>14.59885703460501</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>80</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.164486812034745</v>
+        <v>-1.131492333845472</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.222480269659691</v>
+        <v>-5.189111876698519</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-11.62030507267363</v>
+        <v>-11.58530982150275</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.367118336962598</v>
+        <v>-7.331232866568328</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-11.46002436989656</v>
+        <v>-11.39487042177088</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.793030628684733</v>
+        <v>-8.728024065432081</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.078192249888829</v>
+        <v>-7.012235180181243</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.358248729536655</v>
+        <v>-7.291924608808195</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.564082000045872</v>
+        <v>-8.497765850683109</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.603960023387572</v>
+        <v>-5.536685014252882</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.626193068071046</v>
+        <v>4.693249404022701</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.103943665007634</v>
+        <v>3.171358369691845</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5069517279373557</v>
+        <v>-0.4382066121382238</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.764656678312392</v>
+        <v>1.833711244695017</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.587240717978439</v>
+        <v>8.657127691728</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>7.937204050144253</v>
+        <v>8.00643734088473</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.570777276876584</v>
+        <v>1.640187270674872</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.704850020173097</v>
+        <v>7.774440261014519</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>6.675547394229206</v>
+        <v>6.744924192043818</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.864602136414248</v>
+        <v>6.933802804307689</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.826848155347029</v>
+        <v>3.896719235668279</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.500203881468302</v>
+        <v>7.570208786771921</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>9.027286038091823</v>
+        <v>9.097011680546316</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.954678362573382</v>
+        <v>9.024532710280376</v>
       </c>
     </row>
     <row r="10">
@@ -953,240 +953,240 @@
         <v>80</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.073342790725306</v>
+        <v>-3.039909031076327</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.220531654337897</v>
+        <v>-4.618395010920665</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.168256505537073</v>
+        <v>-3.583750936311752</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.881250221200709</v>
+        <v>-4.300049936317251</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.245740999682283</v>
+        <v>-5.881971010646581</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-7.547946680833206</v>
+        <v>-7.482958384914369</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.833347597702968</v>
+        <v>-5.767406734361622</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.113071113747509</v>
+        <v>-6.04676238244334</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.805917221149301</v>
+        <v>-9.739632559941199</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.091254167620384</v>
+        <v>-8.02401460019761</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-9.065749477704031</v>
+        <v>-8.998784411679033</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.85711498514106</v>
+        <v>-6.789765500619197</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.243420645869776</v>
+        <v>-4.174707004420881</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.710972662786681</v>
+        <v>-5.641962289566479</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.108145202544286</v>
+        <v>1.177994929066962</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.037469587691305</v>
+        <v>-1.968278394365171</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3233649534365099</v>
+        <v>0.3927630410515874</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.466417268791673</v>
+        <v>1.535985665012475</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.931124436936543</v>
+        <v>3.000488318108239</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.367376293427292</v>
+        <v>4.436568928543302</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.826584430411806</v>
+        <v>3.896452375202315</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>6.250735847960776</v>
+        <v>6.320737874141535</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>7.777524750217445</v>
+        <v>7.847249030755066</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.454678362573098</v>
+        <v>6.524532710280376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 34.84</t>
+          <t>X ≈ 34.83</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.027408373704759</v>
+        <v>3.469930898864725</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.091829452350666</v>
+        <v>-3.629527489735899</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.74960981664205</v>
+        <v>2.175434755132606</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.110940887355014</v>
+        <v>0.06530571580311317</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.967846468010045</v>
+        <v>-7.452364787817615</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.961004036765573</v>
+        <v>-2.437781426261758</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.730695493249151</v>
+        <v>-2.664760607171544</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.974970651095234</v>
+        <v>-3.908675018527617</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.901284801786417</v>
+        <v>-4.834995671707595</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.673641030061013</v>
+        <v>-5.606412591169629</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.436278058276393</v>
+        <v>-4.36931017618555</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.084705975850085</v>
+        <v>1.152078482548866</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.937040358991794</v>
+        <v>-2.868338811655867</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.190667035255899</v>
+        <v>-2.121658034454512</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-3.816368207172886</v>
+        <v>-3.746552423320971</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.58579242893461</v>
+        <v>2.654988341451642</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.5168543927998783</v>
+        <v>0.586242643549916</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.5564356488404485</v>
+        <v>-0.4868815892873215</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.598041579949594</v>
+        <v>1.667395557053588</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.8159715064877986</v>
+        <v>0.8851524054679132</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.243977158859281</v>
+        <v>1.313837549581777</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.139173097211291</v>
+        <v>2.209168906156783</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.4740242571005027</v>
+        <v>0.5437440117874175</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.311474479077958</v>
+        <v>3.381328826785236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 37.1</t>
+          <t>X ≈ 37.09</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>117</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.918192859179705</v>
+        <v>-5.3490245146074</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.946107412703022</v>
+        <v>-6.922842499164631</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.134061851438631</v>
+        <v>-4.104971094625675</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.451945180402028</v>
+        <v>-1.417369719305292</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.510962907664883</v>
+        <v>-3.448241679117515</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.630354491292707</v>
+        <v>-1.565778308945724</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.797709718155886</v>
+        <v>-5.731839087054368</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.828298036285595</v>
+        <v>-1.762021474586383</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.787939705514816</v>
+        <v>-1.721661892774335</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.858226195295309</v>
+        <v>-0.7909970612864115</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.115332249180241</v>
+        <v>1.182307232925915</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.687135630046832</v>
+        <v>1.754489421334306</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.973295925139155</v>
+        <v>4.042012387056175</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.309417713115785</v>
+        <v>6.378448938094053</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.09899743788413</v>
+        <v>3.168824754675263</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.989174546837781</v>
+        <v>2.058353737487444</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>6.972768990775023</v>
+        <v>7.04216671449656</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.753616813665829</v>
+        <v>1.823165732749601</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.8235594257496</v>
+        <v>2.892907158569301</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.304601217928848</v>
+        <v>1.373775483329723</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.9445786266986005</v>
+        <v>-0.8747273126932384</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.020323245340037</v>
+        <v>-0.9503343425777473</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.308594854158237</v>
+        <v>-3.23887897903974</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.385065227170493</v>
+        <v>-3.315210879463216</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>119</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.920826895450617</v>
+        <v>-7.899940056755199</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.093659535011767</v>
+        <v>-4.067031180049057</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-7.225633252161799</v>
+        <v>-7.201743288354479</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.112986035357572</v>
+        <v>-7.084419656770962</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.824975813431024</v>
+        <v>-5.763197744639683</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.449181728900399</v>
+        <v>-1.383036878388126</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.761194871398587</v>
+        <v>-2.171282982202335</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.233716847893213</v>
+        <v>-4.122504973253136</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.044515689348245</v>
+        <v>-2.406774727013548</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.487378697929074</v>
+        <v>-4.866639175552962</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.398058851610351</v>
+        <v>-8.288952409623334</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.19033515610944</v>
+        <v>-10.60090476918874</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-11.31407236242896</v>
+        <v>-11.24547255606341</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.7015721537096</v>
+        <v>-10.63265459644172</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-12.19928855831363</v>
+        <v>-12.1295576905227</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-10.7723435528178</v>
+        <v>-10.70323923910261</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-13.4236123343579</v>
+        <v>-13.35430728397414</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-12.69404897828441</v>
+        <v>-12.62456233873176</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-11.64393934812786</v>
+        <v>-11.57464302574019</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-11.4611863097902</v>
+        <v>-11.39204978562723</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-12.0073758281469</v>
+        <v>-11.93755064414801</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-13.76666500906361</v>
+        <v>-13.69669541930944</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-13.49648980975736</v>
+        <v>-13.42678234538644</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-12.73649810801514</v>
+        <v>-12.66664376030786</v>
       </c>
     </row>
     <row r="14">
@@ -1281,240 +1281,240 @@
         <v>153</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.793551544324146</v>
+        <v>-3.767427673337032</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.042330660125735</v>
+        <v>-8.022761225168225</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.066865191192633</v>
+        <v>-1.034399404682574</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.643566989684395</v>
+        <v>-7.616287817945526</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-8.307482852576143</v>
+        <v>-8.623896463238651</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-7.084800762247284</v>
+        <v>-7.759702678758465</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.268408924075466</v>
+        <v>-5.951485299277223</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.848482026889641</v>
+        <v>-7.536854928040334</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.852208065938242</v>
+        <v>-5.163591045181533</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.212416847535984</v>
+        <v>-7.531171040145686</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.540347146587706</v>
+        <v>-9.856466663865589</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-14.37885423242086</v>
+        <v>-14.6934145372252</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-13.56465153775959</v>
+        <v>-13.87852747592265</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-15.74611905896925</v>
+        <v>-15.67605599701855</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-13.42165676678484</v>
+        <v>-13.73994364364062</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-11.79321177149583</v>
+        <v>-12.49076508807347</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-9.323372046699667</v>
+        <v>-10.02389663619175</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-8.127064859814048</v>
+        <v>-8.829569386441456</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-5.305310982453449</v>
+        <v>-5.618532740285289</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-5.773054457709016</v>
+        <v>-5.703921808791655</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-6.97011745812781</v>
+        <v>-6.900296756336864</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-8.354503654562194</v>
+        <v>-8.284536988677814</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-7.429336323252791</v>
+        <v>-7.359629860310122</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-7.507739938080647</v>
+        <v>-7.437885590373213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 43.89</t>
+          <t>X ≈ 43.88</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>133</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.994987598643547</v>
+        <v>-1.966696541090052</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.360169863099038</v>
+        <v>-2.332732153258014</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-6.088892543987917</v>
+        <v>-6.065229055304656</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.903941889457357</v>
+        <v>-5.304102397302799</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.047605105459198</v>
+        <v>-3.421825450612118</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.575853254763075</v>
+        <v>-3.942377390186635</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.125742485393708</v>
+        <v>-2.494522054071034</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.906434562225819</v>
+        <v>-6.85173630812367</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.602256577940359</v>
+        <v>-7.548227504742002</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.154540041495366</v>
+        <v>-9.10230411374814</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.936985164157385</v>
+        <v>-10.32003483194532</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-9.035447444762809</v>
+        <v>-9.8521693459735</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-8.237561918219583</v>
+        <v>-9.508011166651492</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-8.017628763581072</v>
+        <v>-9.734847717022944</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-7.929424858646556</v>
+        <v>-9.215190255956216</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.831218771753043</v>
+        <v>-6.653831386501871</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-4.023914351414277</v>
+        <v>-4.847140483530012</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3699272605501989</v>
+        <v>-0.003811844159336886</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.916494729463444</v>
+        <v>-4.290042741331675</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.230069604443393</v>
+        <v>-2.599095690223329</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.021973407650613</v>
+        <v>-1.952157526561386</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.098337989334752</v>
+        <v>-2.02837311658309</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.582060764591539</v>
+        <v>-5.512358153846584</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-7.163742690058307</v>
+        <v>-7.093888342351207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 46.15</t>
+          <t>X ≈ 46.14</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>157</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1668433492924351</v>
+        <v>-0.1359081101636193</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.405175584098352</v>
+        <v>1.438585869488726</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.475539881812786</v>
+        <v>-4.45049602381853</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.187485727224498</v>
+        <v>-5.162658271354687</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.455331290829875</v>
+        <v>-7.405740092138387</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.731574922360593</v>
+        <v>-4.67579418190747</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.502329662664465</v>
+        <v>-5.446837983619275</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.700178964148094</v>
+        <v>-0.6358663373436713</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.02477888422844643</v>
+        <v>0.04125266533231553</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7957111313412639</v>
+        <v>-0.7304187977086087</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.522011674147798</v>
+        <v>-0.4566419312275869</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.3406004967418</v>
+        <v>-3.279615271804694</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-6.367007683887984</v>
+        <v>-6.309785911216338</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.413138093125212</v>
+        <v>-3.350217257866241</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-4.070353826365498</v>
+        <v>-4.00762533867649</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-7.287967167016724</v>
+        <v>-7.231044755967929</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-6.151785553668446</v>
+        <v>-6.092623703835919</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-6.259636348691465</v>
+        <v>-6.197634073065757</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-5.411253873463302</v>
+        <v>-5.34611087138029</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-5.862922450928551</v>
+        <v>-5.795971429760463</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.77131914630607</v>
+        <v>-5.701528453697691</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-3.940318000730549</v>
+        <v>-3.870366903309275</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.03039201917165</v>
+        <v>-2.960693367407586</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-4.381308898573401</v>
+        <v>-4.311454550866124</v>
       </c>
     </row>
     <row r="17">
@@ -1524,79 +1524,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.87203553400348</v>
+        <v>2.999993906796441</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.851791376180813</v>
+        <v>1.967894068983064</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.166570073192389</v>
+        <v>2.626955468285651</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.080221671364285</v>
+        <v>0.5183201638509516</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.216656801701021</v>
+        <v>6.468465605225418</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.024919595092712</v>
+        <v>4.558739545263187</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.567135932502893</v>
+        <v>3.787826067437187</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.601397066812666</v>
+        <v>2.81138577791392</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.641553118053778</v>
+        <v>2.852290656417594</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.93304818385915</v>
+        <v>4.175679024166413</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.144645889319882</v>
+        <v>2.354534528986072</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.179123328885424</v>
+        <v>1.377879782663314</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.807751257714152</v>
+        <v>2.351215860729582</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.211572668409289</v>
+        <v>0.7334851936058655</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5546058937230924</v>
+        <v>0.7744765461016456</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2275736372043156</v>
+        <v>-0.7271170738457329</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.736186884339119</v>
+        <v>-2.257556600742284</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.2206662307304939</v>
+        <v>-0.2677107702535366</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.315911607476338</v>
+        <v>-2.845575873336458</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-4.883941738633538</v>
+        <v>-5.452551247754698</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-6.116859821367015</v>
+        <v>-6.69242045518461</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-5.506584749421727</v>
+        <v>-6.072648858952611</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-5.234310101247488</v>
+        <v>-5.800921599749294</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-6.002218189150888</v>
+        <v>-6.578614142866478</v>
       </c>
     </row>
     <row r="18">
@@ -1606,161 +1606,161 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.356059432662427</v>
+        <v>4.686983534417564</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1569880501069889</v>
+        <v>0.1931751228816267</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.285942473787351</v>
+        <v>4.304418719497946</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.968475955522415</v>
+        <v>4.979393146464652</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.998838689385032</v>
+        <v>4.644419720580707</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.484715662742531</v>
+        <v>5.52289898989234</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.62447566771818</v>
+        <v>1.978658707714679</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.739817850983535</v>
+        <v>2.393965824349976</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.476546640295311</v>
+        <v>3.821524528438893</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.49310842224822</v>
+        <v>5.823500144619068</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4.373570860579797</v>
+        <v>4.017301210493805</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6118177132686355</v>
+        <v>0.2722217085845742</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.065170207050777</v>
+        <v>5.391023802100172</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.056887583500369</v>
+        <v>2.396539172825484</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.400212741596704</v>
+        <v>1.045917191428295</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.09765528008130531</v>
+        <v>0.2525242209005683</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.859096268945557</v>
+        <v>2.198939937179645</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.731484033836331</v>
+        <v>-1.373196465704993</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.516693446551145</v>
+        <v>-1.157676469627809</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.726574773111579</v>
+        <v>-2.358016336375101</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.87336937848503</v>
+        <v>-0.8192640504821966</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.648928093786019</v>
+        <v>-1.589314179504228</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-4.472363302582096</v>
+        <v>-3.397937213406529</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.151964994070426</v>
+        <v>-2.086578400830575</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 52.94</t>
+          <t>X ≈ 52.93</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>6.948272022926652</v>
+        <v>6.62833298678769</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>9.648502756169961</v>
+        <v>9.314852172038506</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.167143339481896</v>
+        <v>4.844105566099451</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11.1360236170234</v>
+        <v>10.78674151328421</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.907823340866109</v>
+        <v>6.210518002268394</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.236920677517112</v>
+        <v>0.9556965423962396</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.107431316488032</v>
+        <v>3.810928862585875</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7904135452214973</v>
+        <v>1.110955580652053</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.597451400417903</v>
+        <v>-1.87164760562014</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.157985795792904</v>
+        <v>-1.437619904983379</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2759339035279709</v>
+        <v>0.04693960332549096</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.556695194926661</v>
+        <v>-0.2348582196712172</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.898378000630387</v>
+        <v>-2.572076642147479</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.943507432081873</v>
+        <v>-4.610556545069819</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.781167132587505</v>
+        <v>-3.45587144549777</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.9690544447433</v>
+        <v>-1.647682202896746</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.533918639490601</v>
+        <v>-4.203107142092577</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.845405073915153</v>
+        <v>-1.886186008733013</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.8012326216076531</v>
+        <v>0.7524833492217127</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.445122382707019</v>
+        <v>-1.481162503179235</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7703594840214194</v>
+        <v>-1.421634175101694</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.98036298207942</v>
+        <v>0.6811042248765631</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.5725911273143325</v>
+        <v>-0.8611945719459229</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.18028811867066</v>
+        <v>0.8805933163408426</v>
       </c>
     </row>
     <row r="20">
@@ -1773,76 +1773,76 @@
         <v>205</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.181715351800996</v>
+        <v>1.21724194993508</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.789930532389505</v>
+        <v>2.828377137081972</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.833838472912092</v>
+        <v>1.871160767143138</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.092259074939356</v>
+        <v>2.132477024450843</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.678446536395562</v>
+        <v>-1.620069797461575</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.975927463205643</v>
+        <v>-1.916534858460544</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.66760389635629</v>
+        <v>-5.616790469338717</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.974133196692222</v>
+        <v>-4.921209558796633</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.335790117526358</v>
+        <v>-8.29074366878325</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-11.05584477409617</v>
+        <v>-11.01674015214631</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.808894451684758</v>
+        <v>-9.767454390323195</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.06161654566387</v>
+        <v>-11.02405848143663</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-12.1875220394349</v>
+        <v>-12.15080495920779</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.492142819789002</v>
+        <v>-9.448834044675195</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-10.15201690901567</v>
+        <v>-10.10936694953232</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-11.01438202454496</v>
+        <v>-10.97411531580233</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-10.6626044736311</v>
+        <v>-10.62149471622381</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.849626153800195</v>
+        <v>-7.800179139606065</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-8.80277987833383</v>
+        <v>-9.044617850532987</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-6.188353257204547</v>
+        <v>-6.420304143231292</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-5.760421272317757</v>
+        <v>-5.990730680995718</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-7.789154053969348</v>
+        <v>-8.015595117361272</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.469228716601599</v>
+        <v>-9.399585855887878</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.112394808158662</v>
+        <v>-7.042540460451328</v>
       </c>
     </row>
     <row r="21">
@@ -1852,243 +1852,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.135010734817754</v>
+        <v>-1.844469481192121</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.433787157087032</v>
+        <v>-0.6413013961952103</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.358860368242404</v>
+        <v>-1.053171113006513</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.03904742097795832</v>
+        <v>0.2837083285689559</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>6.209965148335947</v>
+        <v>6.098441531062583</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.326658936523657</v>
+        <v>2.185089609314005</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.57513428656452</v>
+        <v>2.43896466473872</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.277812581019795</v>
+        <v>-1.938681135690423</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.236063780003889</v>
+        <v>-1.897147440503559</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.9725691544255781</v>
+        <v>-1.131932180104663</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6989080952897098</v>
+        <v>-0.8580120777590565</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.008117219325236</v>
+        <v>-3.18589724314392</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.637460779031443</v>
+        <v>-4.820808347855028</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.841665355847347</v>
+        <v>-3.504453986947929</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.464895710488769</v>
+        <v>-2.112345204061327</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.872395756791974</v>
+        <v>-1.518469928111386</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.9891044807292459</v>
+        <v>-0.6273540513995073</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.113334754981189</v>
+        <v>-1.757599875086932</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.898608008008196</v>
+        <v>-1.541987573795176</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.749310229727129</v>
+        <v>-3.405161277933608</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-3.785293898995889</v>
+        <v>-3.434795576242188</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.336298271420077</v>
+        <v>-1.9733013268417</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.063656802116505</v>
+        <v>-1.69859404799918</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-5.203484902732967</v>
+        <v>-4.853672417924749</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.73</t>
+          <t>X ≈ 59.72</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.449802560350896</v>
+        <v>-6.652556455553928</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.954081370166953</v>
+        <v>-2.643468378761106</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.121404745974687</v>
+        <v>-1.373999152979003</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.313971367583733</v>
+        <v>-7.520547417573276</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.754066172553017</v>
+        <v>-2.426704856783033</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.754227787952125</v>
+        <v>-4.410482744712724</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.442043060133514</v>
+        <v>-4.102605088129025</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.179917758786637</v>
+        <v>-4.385173865877348</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.687078733936389</v>
+        <v>-4.887561066013618</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-8.209220633755791</v>
+        <v>-7.839935482067972</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.384954004420898</v>
+        <v>-7.021209215492242</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.030935168874585</v>
+        <v>-5.676654017596562</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.973021447144703</v>
+        <v>-4.632240979876734</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.550192620733128</v>
+        <v>-3.765967213402774</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.116691067614646</v>
+        <v>-3.339530716332561</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-4.707111763328371</v>
+        <v>-4.91469950487253</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.745696860203502</v>
+        <v>-3.962056241292224</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-4.393205706235072</v>
+        <v>-4.606810115350434</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.721453456310329</v>
+        <v>-4.932020268207317</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.008283798461299</v>
+        <v>-2.570865293579736</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.557109435036075</v>
+        <v>-3.116976552178244</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.282773797229474</v>
+        <v>-4.822068932651852</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.023594222755136</v>
+        <v>-2.919140043468062</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.4546622967675589</v>
+        <v>-1.029815115806578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.99</t>
+          <t>X ≈ 61.98</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>146</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.707820337205874</v>
+        <v>-5.695641633979996</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.310679720795221</v>
+        <v>-3.290692404932464</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.696651585238989</v>
+        <v>-2.673916933415434</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6890004335776467</v>
+        <v>0.7227180882376416</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.041456281546743</v>
+        <v>-0.982935398008344</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.221178085637831</v>
+        <v>-2.165832225609591</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4246285281939279</v>
+        <v>0.4868766247467846</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.197617427606346</v>
+        <v>2.263459700541581</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.605534342013343</v>
+        <v>3.674809896154912</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.519026681501927</v>
+        <v>3.586825726967739</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.743541890683915</v>
+        <v>1.80609084858164</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.516962667567192</v>
+        <v>3.582135965681665</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.810173059538634</v>
+        <v>5.883631433072118</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.905130256098452</v>
+        <v>4.977621049776218</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4.930127793323742</v>
+        <v>5.004409259044969</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>6.88940363761818</v>
+        <v>6.968659194686595</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>7.438024800447792</v>
+        <v>7.519673564558516</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.965183831827275</v>
+        <v>6.044969847038615</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>6.180093075474979</v>
+        <v>6.260861227962941</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.268177106799307</v>
+        <v>2.338117996835088</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.410369026833038</v>
+        <v>2.480503335718375</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.334563260080522</v>
+        <v>2.404657374309274</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.293773152723354</v>
+        <v>3.364063593640559</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.848513979011379</v>
+        <v>1.918368326718735</v>
       </c>
     </row>
     <row r="24">
@@ -2098,325 +2098,325 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1072450973826591</v>
+        <v>0.1522563348439689</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.623232362631668</v>
+        <v>4.645065743390596</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.790073120641964</v>
+        <v>1.827736349531982</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.075828625835527</v>
+        <v>1.114782330089319</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7083029327445516</v>
+        <v>0.778991857542124</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.589264254216168</v>
+        <v>1.655613216053297</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.968801195843632</v>
+        <v>5.021595566645544</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.379531442656202</v>
+        <v>5.43303929430634</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.806836198154912</v>
+        <v>6.853836821048617</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>10.87559111662474</v>
+        <v>10.90850735190861</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>9.071718529639398</v>
+        <v>9.113601476829309</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>10.17299913728007</v>
+        <v>10.21416241820883</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>8.352455302261184</v>
+        <v>8.401345178938918</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.667529128263176</v>
+        <v>4.731990440423345</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4.700138689623692</v>
+        <v>4.763502315256581</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.070836754717895</v>
+        <v>8.116509926854761</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>6.551856733319525</v>
+        <v>6.603282445049615</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>5.756686061666329</v>
+        <v>5.808786568814639</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.58927644218884</v>
+        <v>4.645367604911449</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>4.082974710957956</v>
+        <v>4.142558242465697</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.581155703639496</v>
+        <v>2.220701729672079</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.811920604061847</v>
+        <v>1.455200595849263</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.6878708070455559</v>
+        <v>-1.028945381323851</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.07309941520460228</v>
+        <v>-0.415122462133418</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 66.52</t>
+          <t>X ≈ 66.51</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.230215328943054</v>
+        <v>6.218307816145497</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.623675018380432</v>
+        <v>1.658178905119662</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8679669012330322</v>
+        <v>0.9243852082013149</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.704563656858156</v>
+        <v>-2.605470219692137</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.792091094943309</v>
+        <v>-3.645486044352083</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.314429032956916</v>
+        <v>-4.162745210367383</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.09526710378654</v>
+        <v>-4.934693894257691</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.527839606447998</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.340277623057894</v>
+        <v>-5.171418157096106</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.727085945764529</v>
+        <v>1.802145040106964</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.712542151655228</v>
+        <v>2.780430034381439</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.417504370629331</v>
+        <v>2.501680630933407</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.423115192958505</v>
+        <v>3.491194620415364</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.482689504373113</v>
+        <v>2.565890391856087</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.3919980612543483</v>
+        <v>0.499296390050219</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.007785151691913</v>
+        <v>1.093683311993132</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.58797717182874</v>
+        <v>1.663991527128374</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.223320019776686</v>
+        <v>-4.074651993594131</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-5.430985122150986</v>
+        <v>-5.267211316895235</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-7.389987244898023</v>
+        <v>-7.193041563265247</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-5.806274388589827</v>
+        <v>-5.62291167489321</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-8.296629526891195</v>
+        <v>-8.515659044753129</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-6.59727335482247</v>
+        <v>-6.832733628045681</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-6.223893065998332</v>
+        <v>-6.90856588126892</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 68.78</t>
+          <t>X ≈ 68.77</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.002365680559954</v>
+        <v>-1.702862617307936</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.479252697925496</v>
+        <v>1.838329576590354</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.092987348343165</v>
+        <v>3.501085721357775</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.089117699272109</v>
+        <v>1.237744105015764</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.540641807377874</v>
+        <v>4.002728826266974</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.905781365874887</v>
+        <v>-3.562242972131806</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.96872383380682</v>
+        <v>-5.884579252921384</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-4.720560922073425</v>
+        <v>-4.612403100775182</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.732479971554611</v>
+        <v>-7.671691112658934</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.7963917182019</v>
+        <v>-10.77018818404431</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-8.231956115208703</v>
+        <v>-8.170547146533501</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.930897346927836</v>
+        <v>-3.798133759283786</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.765312229537152</v>
+        <v>-3.370908229240719</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.12020118843617</v>
+        <v>2.609563281909544</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.1711936135209129</v>
+        <v>-0.3741614110198554</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.523822672735484</v>
+        <v>-2.105355884425606</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.158877526245327</v>
+        <v>1.636695970844933</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.29053533152409</v>
+        <v>0.7566614685741371</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.7432997158299486</v>
+        <v>0.1973590510488492</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.1669847328244742</v>
+        <v>-0.3909889374327236</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-4.956368347929335</v>
+        <v>-4.809504097646865</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.505605846319945</v>
+        <v>-3.334962462156696</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.704113122585873</v>
+        <v>-2.285293951224986</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.016695683228427</v>
+        <v>-1.58593240599869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 71.04</t>
+          <t>X ≈ 71.03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.05722187783129584</v>
+        <v>0.7709175924503811</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.740640203977215</v>
+        <v>-6.916800382370056</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-4.678348843165715</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.923984727525124</v>
+        <v>-3.920714627314297</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.542985855832796</v>
+        <v>-2.785916864567497</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3755220407560813</v>
+        <v>1.077519909765222</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.889881404730779</v>
+        <v>-1.900311127066345</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.562907233332751</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1118859849225942</v>
+        <v>0.06884696303649918</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.647024052712595</v>
+        <v>-3.645245183588273</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.865202099030057</v>
+        <v>-4.841773776720458</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.412952718922867</v>
+        <v>-1.444052591933165</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.04490662397717</v>
+        <v>-0.3613323058481015</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.465079848570518</v>
+        <v>3.094059405940641</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.806148609533217</v>
+        <v>2.435916108359997</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.5838659677110272</v>
+        <v>0.08912655971479211</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.956765632009208</v>
+        <v>-2.250672930203855</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.569211734671647</v>
+        <v>-0.884925398730914</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.099357228456256</v>
+        <v>-1.404328135453646</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4197761194029823</v>
+        <v>0.2531059098085393</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.2758294417484</v>
+        <v>1.181147977136618</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.946143042822122</v>
+        <v>1.84059613337454</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.220918209304251</v>
+        <v>2.850364963503651</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8400977568298487</v>
+        <v>-0.1666437603078137</v>
       </c>
     </row>
     <row r="28">
@@ -2429,76 +2429,76 @@
         <v>102</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.2474472217001846</v>
+        <v>0.2807215140190138</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.814232491369587</v>
+        <v>4.847905499982929</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.315708497871682</v>
+        <v>6.351062921540169</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.543091655266757</v>
+        <v>8.579285372685661</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.17782187024271</v>
+        <v>8.243494900138387</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.384594326386747</v>
+        <v>7.450068929373018</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.53329682178367</v>
+        <v>10.59968887293362</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.352781391951396</v>
+        <v>5.419516643866828</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.413905300111253</v>
+        <v>4.480611668918755</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.561638516792861</v>
+        <v>7.629264620333302</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.875213470182644</v>
+        <v>5.942539948769671</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.152232321500058</v>
+        <v>9.221510386332781</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>12.41486970991377</v>
+        <v>12.48493571620323</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>10.06875328894689</v>
+        <v>10.13814616755796</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.973875281072452</v>
+        <v>8.043444716854978</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.124230714183462</v>
+        <v>6.193711080232596</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.350490196078368</v>
+        <v>4.419772576475097</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.652903358888857</v>
+        <v>7.722949074551018</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>9.888462839096526</v>
+        <v>9.958208100758611</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.851737186102518</v>
+        <v>7.921591533809796</v>
       </c>
     </row>
     <row r="29">
@@ -2508,489 +2508,489 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.220615436354471</v>
+        <v>3.692486219901369</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.201229395394343</v>
+        <v>4.691042754884919</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.129949983939788</v>
+        <v>0.5863570391872344</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.310893512851898</v>
+        <v>7.873403019744487</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.05088688572258349</v>
+        <v>-0.4623874528027514</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.185419919782007</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.04413273509644</v>
+        <v>5.619296716070949</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.765578089577915</v>
+        <v>5.341085271317873</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.491304680916265</v>
+        <v>4.049239119899198</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.349048217515254</v>
+        <v>5.942990110529379</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.57077590568331</v>
+        <v>10.21704975269137</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.92326094957674</v>
+        <v>12.60496701590998</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>18.37771709951065</v>
+        <v>18.14847161572052</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>15.52478134110785</v>
+        <v>15.26072607260723</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>12.23427115470215</v>
+        <v>11.93591610836008</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>8.881962783270858</v>
+        <v>8.530303030303031</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>6.116290141753566</v>
+        <v>5.729719226658887</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>7.327096199342449</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.911640414905882</v>
+        <v>4.50743657042873</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>11.67763157894737</v>
+        <v>11.3609490470634</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>13.7660101173178</v>
+        <v>13.48506954576396</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>9.742686640622587</v>
+        <v>9.409223584354969</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>10.01746180710465</v>
+        <v>9.683698296836909</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>11.25730994152038</v>
+        <v>10.94119937694693</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 77.83</t>
+          <t>X ≈ 77.82</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.708857317653489</v>
+        <v>3.201258149725959</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.881637345927011</v>
+        <v>-1.344044964413364</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.321337810013205</v>
+        <v>-2.782064013444376</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.971301335972292</v>
+        <v>-2.442386453939726</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.400400908230374</v>
+        <v>-3.830808505434391</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.40472565692572</v>
+        <v>-6.801737056179093</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.858442852809539</v>
+        <v>-2.310527845332594</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.182151437842116</v>
+        <v>2.674418604651194</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.41515686456691</v>
+        <v>5.873800523408008</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.641321453797481</v>
+        <v>5.100884847371518</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.979510508146831</v>
+        <v>6.427576068480782</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.572757030203839</v>
+        <v>4.043563507138046</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7432235499854656</v>
+        <v>-0.2374932965602099</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.347559084424013</v>
+        <v>-6.774361646690949</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.687341387291099</v>
+        <v>-2.169347049534693</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.092281337669718</v>
+        <v>-1.574960127591702</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.162545244584592</v>
+        <v>-0.6562456856217835</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.267528660679872</v>
+        <v>-0.7610863894430011</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.051405497748057</v>
+        <v>-0.5451950085186752</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.518617021276626</v>
+        <v>5.957440275133592</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.039246399512656</v>
+        <v>6.467525686114904</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.027121131104117</v>
+        <v>7.444311303653144</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.238066510352205</v>
+        <v>6.666154437187856</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>9.353614532785834</v>
+        <v>9.748216920806691</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 80.09</t>
+          <t>X ≈ 80.08</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>42</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-10.81697854860801</v>
+        <v>-10.78370425628918</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.628344539442772</v>
+        <v>-1.59467153082943</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6870926225763938</v>
+        <v>-0.651738198907907</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.92469545957921</v>
+        <v>-10.88850174216031</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.147108101746078</v>
+        <v>-4.0814350718504</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.351857239840939</v>
+        <v>-2.285465188690992</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.011364266311915</v>
+        <v>-4.944629014396483</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.173008941567822</v>
+        <v>2.239715310375324</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.362731231106338</v>
+        <v>-3.295105127565897</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-10.23122910684807</v>
+        <v>-10.16390262826104</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-17.65318015318012</v>
+        <v>-17.58550917456618</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-18.77767137166722</v>
+        <v>-18.70867124142227</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-21.3799805636541</v>
+        <v>-21.31070249882138</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-17.27700704078664</v>
+        <v>-17.20694103449717</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-14.30099461021284</v>
+        <v>-14.23160173160176</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-14.43508830436176</v>
+        <v>-14.36551886857924</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-12.15911933950463</v>
+        <v>-12.08940719144801</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-4.800139033715666</v>
+        <v>-4.730658667666532</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-9.375000000000036</v>
+        <v>-9.305717619603307</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3943908851884004</v>
+        <v>-0.3244542637597476</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.910606440121342</v>
+        <v>1.980652155783503</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1955707743489086</v>
+        <v>-0.1258255126868235</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-2.652464494569692</v>
+        <v>-2.582610146862415</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 82.35</t>
+          <t>X ≈ 82.34</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>16.78042404879463</v>
+        <v>16.12659474703315</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.17252126142304</v>
+        <v>15.7918179486833</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>19.55100261551867</v>
+        <v>19.00496169034998</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16.56448202959832</v>
+        <v>15.96642627555846</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>16.19921224457427</v>
+        <v>15.63063580301116</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.84092231212649</v>
+        <v>11.16643919841087</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13.34078345279975</v>
+        <v>12.7200719098694</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>15.33495608000842</v>
+        <v>14.76744186046508</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.10374487230382</v>
+        <v>12.48334764703098</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>16.87536400698891</v>
+        <v>18.68717615704101</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>19.42245054683151</v>
+        <v>18.9612357992029</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>23.68881118881116</v>
+        <v>23.3336491864526</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>20.29159269759678</v>
+        <v>19.88490572424765</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.52478134110788</v>
+        <v>15.01266405710339</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.32039555661603</v>
+        <v>12.02893936417399</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>13.18818287896469</v>
+        <v>12.62332628611695</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>13.05408918481577</v>
+        <v>12.48940914913948</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>15.22183304144778</v>
+        <v>14.71014984066717</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>22.25613802256135</v>
+        <v>21.902785407638</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>20.1704545454545</v>
+        <v>19.76404982225715</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>21.89998140918383</v>
+        <v>21.54708504963997</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>26.3694808989958</v>
+        <v>26.12240187892858</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>28.91698333820521</v>
+        <v>28.72245798675947</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>28.8410419989367</v>
+        <v>28.64662573353619</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 84.62</t>
+          <t>X ≈ 84.61</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.230640499011145</v>
+        <v>9.149850560986636</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.514512603414403</v>
+        <v>4.163910971939153</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.074812139328294</v>
+        <v>5.051473318256988</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.361018826135137</v>
+        <v>4.338519298814248</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.376701422063441</v>
+        <v>6.328310221615816</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>15.08767555887975</v>
+        <v>15.81760198910854</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14.31480942682573</v>
+        <v>15.04565330521816</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16.41720716225954</v>
+        <v>17.09302325581396</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.45872322728218</v>
+        <v>17.13451043772866</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>18.06584019746513</v>
+        <v>16.36159476169213</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>18.34019946458046</v>
+        <v>18.96123579920293</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.68015318015318</v>
+        <v>16.35690500040606</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.17470958071366</v>
+        <v>12.90816153820113</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.810495626822167</v>
+        <v>5.710338475708042</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.151564387784866</v>
+        <v>2.726613782778642</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.746624437406219</v>
+        <v>5.646582100070475</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>6.993483124209661</v>
+        <v>7.838246358441836</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.507547327162015</v>
+        <v>5.40782425927182</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.342718109141508</v>
+        <v>3.298134244847304</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>8.136142845513007</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>9.129418638621097</v>
+        <v>9.919178072895811</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>9.053463582978488</v>
+        <v>9.84333211148671</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.792225428619929</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.871345029239798</v>
+        <v>7.716393175396654</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 86.88</t>
+          <t>X ≈ 86.87</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.32587859424918</v>
+        <v>11.359152886568</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.99070307960488</v>
+        <v>11.02437608821822</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.340895869691671</v>
+        <v>-1.275421266705401</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.88623799825429</v>
+        <v>12.95263004940424</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>22.60768335273573</v>
+        <v>22.67441860465117</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.64919941775837</v>
+        <v>22.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.8753640069889</v>
+        <v>21.94299011052934</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>22.14972327410423</v>
+        <v>22.21704975269126</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.87062937062937</v>
+        <v>21.93830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>20.74613815214223</v>
+        <v>20.81513828238719</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.52478134110788</v>
+        <v>20.5940594059406</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>19.86585010207057</v>
+        <v>19.93591610836004</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.460910151691984</v>
+        <v>5.53030303030306</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5.326816457543032</v>
+        <v>5.396385893325558</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.22183304144778</v>
+        <v>5.291545189504404</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.4379562043795957</v>
+        <v>0.5074365704287302</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.374999999999993</v>
+        <v>-4.305717619603264</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.005844535359408</v>
+        <v>5.075890251021569</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.28061970184157</v>
+        <v>15.35036496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>20.2046783625731</v>
+        <v>20.27453271028038</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3330</v>
+        <v>3334</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1101488438659217</v>
+        <v>-0.1109096692854123</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.220514104166007</v>
+        <v>-0.2211543051071629</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3012802851079428</v>
+        <v>-0.3018694883835593</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3717459215550107</v>
+        <v>-0.3722737840718509</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.451619754122774</v>
+        <v>-0.452843760586866</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4269173750680295</v>
+        <v>-0.4281658967770028</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4660177531648841</v>
+        <v>-0.467244614875078</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3690052306474172</v>
+        <v>-0.3703575147518166</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4300233027199596</v>
+        <v>-0.4313023352615346</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3495163757861803</v>
+        <v>-0.3509166995064632</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3270939559286319</v>
+        <v>-0.3285134382259329</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.469286847204252</v>
+        <v>-0.4705460344984758</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4690668762923664</v>
+        <v>-0.4703624649969598</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5231228505088907</v>
+        <v>-0.5243616466909842</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.5055185711848935</v>
+        <v>-0.5068000148825575</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.611588350405107</v>
+        <v>-0.6127250965671109</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.5482210012522941</v>
+        <v>-0.5494387100865907</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.6055050880486519</v>
+        <v>-0.60665840331</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.6415040654854991</v>
+        <v>-0.6426083532011262</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.5867576484703036</v>
+        <v>-0.5879225327249031</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.6022688158386345</v>
+        <v>-0.6034331013241712</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.6003979616393664</v>
+        <v>-0.6015677825515482</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.6080023335832294</v>
+        <v>-0.6091552763764128</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.5460723881776559</v>
+        <v>-0.5473029225930546</v>
       </c>
     </row>
     <row r="7">
@@ -3266,161 +3266,161 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3289</v>
+        <v>3293</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1113194733836451</v>
+        <v>-0.1124997069180935</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1886989137506063</v>
+        <v>-0.1898018906656418</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.222411281762227</v>
+        <v>-0.2235403657614796</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3755437952869869</v>
+        <v>-0.3765215199476302</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3611922843913362</v>
+        <v>-0.3633536363776599</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3989545331328657</v>
+        <v>-0.4010630667658077</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4591945486301583</v>
+        <v>-0.4612672315625232</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3877780693520094</v>
+        <v>-0.3899512956208184</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5408732214668177</v>
+        <v>-0.5428608397944643</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5406214607676532</v>
+        <v>-0.5426464180463668</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.5213851450356373</v>
+        <v>-0.5234221166371853</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.661936518495132</v>
+        <v>-0.6638176537824165</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6478012417971613</v>
+        <v>-0.649752758775044</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6695199623174091</v>
+        <v>-0.6714567914557037</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.6132281271592603</v>
+        <v>-0.6152649940021604</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.6673883014472679</v>
+        <v>-0.6693334434927891</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.4498825715831885</v>
+        <v>-0.4520989551592862</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.476194272664543</v>
+        <v>-0.4783850923992361</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.515292125917945</v>
+        <v>-0.5174269832401848</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.553256908593994</v>
+        <v>-0.5553384870585347</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.6229391696297881</v>
+        <v>-0.6249628166955219</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6808768259289195</v>
+        <v>-0.6828350904048079</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.6616295382800104</v>
+        <v>-0.663599820952939</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5675928444807141</v>
+        <v>-0.5696822912379957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 26.91</t>
+          <t>X &gt; 26.92</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3235</v>
+        <v>3239</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.009119846551229216</v>
+        <v>0.007221556095927895</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.186760844251431</v>
+        <v>-0.1884420657222847</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2892922247760978</v>
+        <v>-0.2909435743097006</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5253098989032949</v>
+        <v>-0.5267197172914067</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5968988354950255</v>
+        <v>-0.5998951262220587</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.6692081967743775</v>
+        <v>-0.6721053317959829</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7484483486091804</v>
+        <v>-0.7513011545269563</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6713077269320635</v>
+        <v>-0.6742757117850857</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.827723659164711</v>
+        <v>-0.830498638756815</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.8146944725432306</v>
+        <v>-0.8175386321696649</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.8305722923981804</v>
+        <v>-0.8333807516137455</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9997124833897146</v>
+        <v>-1.002333301940936</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.028353529928005</v>
+        <v>-1.031015563766658</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.9852340672126161</v>
+        <v>-0.987965832594341</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.886307727769136</v>
+        <v>-0.8892070443493267</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.9821980814255298</v>
+        <v>-0.9849418110890227</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.7280879224693066</v>
+        <v>-0.731155696323242</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.7223199977376851</v>
+        <v>-0.7254039630379907</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7348833017932748</v>
+        <v>-0.7379395084862139</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.8384146341463463</v>
+        <v>-0.841332790741113</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.9311713787323654</v>
+        <v>-0.9340133248919358</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.9580108863273082</v>
+        <v>-0.9608268116133871</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.9431133018667168</v>
+        <v>-0.9459313327926466</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.7845024720482314</v>
+        <v>-0.7875234799017719</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3161</v>
+        <v>3165</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1261298505306101</v>
+        <v>0.1232683194413013</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06647568256916969</v>
+        <v>-0.06912877528978356</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.0750187546886707</v>
+        <v>-0.07779864191760311</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3312911692242508</v>
+        <v>-0.3338183303340116</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4274315518808578</v>
+        <v>-0.4322366990339361</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.6000968762975276</v>
+        <v>-0.6046704027405951</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6316978104304098</v>
+        <v>-0.6363077255800391</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.7980453221147528</v>
+        <v>-0.8024754538210175</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.022085217002342</v>
+        <v>-1.026232578214</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.05376985127878</v>
+        <v>-1.057953582455838</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.950465761812552</v>
+        <v>-0.9547564147095784</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.180111253385753</v>
+        <v>-1.184142206627016</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.372399048362183</v>
+        <v>-1.37629748587478</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.354751929153871</v>
+        <v>-1.358696499571209</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.206705102976748</v>
+        <v>-1.210901787040086</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.192608308390085</v>
+        <v>-1.196769141143548</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.08732495659838</v>
+        <v>-1.091634283219214</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.01593140440005</v>
+        <v>-1.020343804503817</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.970761420383532</v>
+        <v>-0.9752132718425912</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.144352290679308</v>
+        <v>-1.148570254503866</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.25827626234814</v>
+        <v>-1.262405201710713</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.189223438083495</v>
+        <v>-1.193449818444776</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.243731974312773</v>
+        <v>-1.247866243066149</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.142996423886878</v>
+        <v>-1.147268237586921</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3081</v>
+        <v>3085</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1596414808471422</v>
+        <v>0.1558066832218259</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06740304737800074</v>
+        <v>0.06364226137560536</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2247614807669649</v>
+        <v>0.2206133173585059</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1486017263748352</v>
+        <v>-0.1523618755856262</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1409637085049198</v>
+        <v>-0.1479544631120646</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3873624718213975</v>
+        <v>-0.3940161748588054</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.4643107428690101</v>
+        <v>-0.470967629512586</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6277057334767306</v>
+        <v>-0.6341915211147153</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8262527786240597</v>
+        <v>-0.8324813102083155</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.9356214534310965</v>
+        <v>-0.9418114383573624</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.095267029709561</v>
+        <v>-1.101220098825806</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.291349290864318</v>
+        <v>-1.297088736969158</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.394870903485192</v>
+        <v>-1.400623991514628</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.435749231522344</v>
+        <v>-1.441481789535977</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.461010739353377</v>
+        <v>-1.466798823766652</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.429669323866477</v>
+        <v>-1.435426035329044</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.156344164218631</v>
+        <v>-1.162475684940937</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.242371688063102</v>
+        <v>-1.248409517710122</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.169302382788281</v>
+        <v>-1.175411326011435</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.352309562398702</v>
+        <v>-1.358161776288284</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.39031454648174</v>
+        <v>-1.396191248709201</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.414849593735603</v>
+        <v>-1.420708388434186</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.510425074277833</v>
+        <v>-1.516128879659014</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.405188563749526</v>
+        <v>-1.411042654387373</v>
       </c>
     </row>
     <row r="11">
@@ -3594,161 +3594,161 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.245825666693797</v>
+        <v>0.2408839734527319</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2083676512224741</v>
+        <v>0.1882888443319075</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3418695910316529</v>
+        <v>0.3218942292698657</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.02243982048143778</v>
+        <v>-0.04194089559943137</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.004881674751445075</v>
+        <v>0.004698223677536362</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1964771880090055</v>
+        <v>-0.2052922557891037</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.3211841356091867</v>
+        <v>-0.3299642590007892</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4814780658920412</v>
+        <v>-0.4900964565868264</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5868748527986654</v>
+        <v>-0.5953524915798241</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7448681654820319</v>
+        <v>-0.7532669282251803</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8827916562208742</v>
+        <v>-0.8909688026433571</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.142978329337446</v>
+        <v>-1.150861069384469</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.318934889026423</v>
+        <v>-1.326771531936423</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.321781262678243</v>
+        <v>-1.329655353595058</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.529498735138723</v>
+        <v>-1.53720930637121</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.413466717699869</v>
+        <v>-1.421240282010281</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.19578992543569</v>
+        <v>-1.203879710924106</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.3145819901452</v>
+        <v>-1.322536510927371</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.278610661887903</v>
+        <v>-1.286583363126113</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.504783693843592</v>
+        <v>-1.512430813355351</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.529385495549214</v>
+        <v>-1.537093574803343</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.619197089682189</v>
+        <v>-1.626803463644187</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.758021204221066</v>
+        <v>-1.765403499570205</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.614715172915069</v>
+        <v>-1.622305892049077</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 35.97</t>
+          <t>X &gt; 35.96</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2898</v>
+        <v>2902</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1114215884252872</v>
+        <v>0.1262761742392726</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2901206883750049</v>
+        <v>0.3237936969883464</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2207525298729678</v>
+        <v>0.2561069535414546</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.06272215757845601</v>
+        <v>-0.04574737422605324</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2425942996121293</v>
+        <v>0.2693699983791191</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.133762810706763</v>
+        <v>-0.1260550453967326</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2355458782465547</v>
+        <v>-0.2470958841346373</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3573132155552798</v>
+        <v>-0.3687616558011939</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4335331603398132</v>
+        <v>-0.4448758383912761</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5696909380660102</v>
+        <v>-0.5810153764390762</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.7564945204680384</v>
+        <v>-0.7675128545128089</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.222154134525269</v>
+        <v>-1.23259875851236</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.261424584193286</v>
+        <v>-1.27205704888641</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.290899539222245</v>
+        <v>-1.301544989663796</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.448219385373534</v>
+        <v>-1.458793613385062</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.555607398204813</v>
+        <v>-1.565916900968439</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.256660306656627</v>
+        <v>-1.267416100486756</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.341527840094948</v>
+        <v>-1.352196213521758</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.38085192514162</v>
+        <v>-1.391428238652821</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.58726740179187</v>
+        <v>-1.597527667779467</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.627955665805956</v>
+        <v>-1.638280999273256</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.752776154295731</v>
+        <v>-1.76295272418502</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.837352012542709</v>
+        <v>-1.847361526334446</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.789800588427596</v>
+        <v>-1.79989871632197</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3230234907517087</v>
+        <v>0.3562977830705378</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.594557469326503</v>
+        <v>0.6282304779398444</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4039647853973989</v>
+        <v>0.4393192090658857</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.004275881537324722</v>
+        <v>0.01187553937332098</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4005109458729663</v>
+        <v>0.4255497349202741</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07079940666916684</v>
+        <v>-0.06557115963902049</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.001538985305394647</v>
+        <v>-0.01667758799761287</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2954271227737451</v>
+        <v>-0.3102297352274519</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3765516552030022</v>
+        <v>-0.3912370705769845</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5575519142990757</v>
+        <v>-0.5721938837542879</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8352445140131124</v>
+        <v>-0.8494263016332155</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.344551438536399</v>
+        <v>-1.358088638958336</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.481655544132842</v>
+        <v>-1.495305208313809</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.610653986731613</v>
+        <v>-1.624187463469063</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.639526242015442</v>
+        <v>-1.653203433515415</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.704740619193664</v>
+        <v>-1.718175308400866</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.602882251208761</v>
+        <v>-1.616508089482458</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.471744281838937</v>
+        <v>-1.485595620241227</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.557736545082022</v>
+        <v>-1.571416476166277</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.708931777378822</v>
+        <v>-1.722354406982262</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.656706156124393</v>
+        <v>-1.670358479104451</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.783591325222666</v>
+        <v>-1.797091449731901</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.775455064513579</v>
+        <v>-1.788902803904818</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.722685894888244</v>
+        <v>-1.7362392825383</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2662</v>
+        <v>2666</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6915502360402499</v>
+        <v>0.7248245283590791</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8041359154257748</v>
+        <v>0.8378089240391162</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7450324662650019</v>
+        <v>0.7803868899334887</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3135064281187923</v>
+        <v>0.3286269003415043</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6788103164053396</v>
+        <v>0.7017916516748244</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.009181263789550087</v>
+        <v>-0.00676455028749956</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07712331764167146</v>
+        <v>0.07949572104602964</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1640760794644933</v>
+        <v>-0.1400644113995995</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3466915049162722</v>
+        <v>-0.3012712111936509</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.4265791918152431</v>
+        <v>-0.3805063407220146</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5418655109424577</v>
+        <v>-0.5173544310965212</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9491163286974782</v>
+        <v>-0.9455248281941238</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.042114747221781</v>
+        <v>-1.060095187915387</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.204260575059791</v>
+        <v>-1.222084091817251</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.167470751542304</v>
+        <v>-1.185579218742767</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.299389473776209</v>
+        <v>-1.317116565807659</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.074457427807289</v>
+        <v>-1.092577817860374</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9700710065282578</v>
+        <v>-0.9883949302561064</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.106850694758045</v>
+        <v>-1.124910864988749</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.272974493623401</v>
+        <v>-1.290736346195033</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.193997782356298</v>
+        <v>-1.212070456733784</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.247909218394319</v>
+        <v>-1.265938834435673</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.25148694479757</v>
+        <v>-1.269432561805679</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.230332907148913</v>
+        <v>-1.248348009899665</v>
       </c>
     </row>
     <row r="15">
@@ -3922,161 +3922,161 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9650538519811604</v>
+        <v>0.9983281442999896</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.34359760775714</v>
+        <v>1.377270616370481</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8555228375647346</v>
+        <v>0.8908772612332214</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7987325074029314</v>
+        <v>0.8123403710529686</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.226798700165475</v>
+        <v>1.269571310083805</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4222933409390279</v>
+        <v>0.4652607317085469</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4030963877822629</v>
+        <v>0.4466823888174005</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2435421389316943</v>
+        <v>0.3102773908471264</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.07194298604964189</v>
+        <v>-0.005236617242140085</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.01277562014315237</v>
+        <v>0.05485048339728849</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.006866131247136309</v>
+        <v>0.05124253333390527</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1301645952300987</v>
+        <v>-0.1085064734461056</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2784845642993901</v>
+        <v>-0.2796653669583122</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.317491205574683</v>
+        <v>-0.3420770478475745</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4202047251046395</v>
+        <v>-0.4212267487828214</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.6594712547442825</v>
+        <v>-0.6368267831149907</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.5714347348258073</v>
+        <v>-0.5488087055624433</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.5336341553713311</v>
+        <v>-0.5109975200705179</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.8508266118495484</v>
+        <v>-0.8513238586535365</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.9985575009948207</v>
+        <v>-1.022046582654525</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.8417672879788398</v>
+        <v>-0.8657518638809023</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.8145457473964299</v>
+        <v>-0.8386226714436091</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.8747587842142082</v>
+        <v>-0.8986406053109803</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.8475336740948904</v>
+        <v>-0.8715078786571482</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 45.02</t>
+          <t>X &gt; 45.01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.130746407929436</v>
+        <v>1.164020700248265</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.550921291942267</v>
+        <v>1.584594300555608</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.244246425841865</v>
+        <v>1.279600849510352</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.117947867159828</v>
+        <v>1.154141584578731</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.466064569756426</v>
+        <v>1.531737599652104</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6460953178870028</v>
+        <v>0.7115699208732735</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5446517624171108</v>
+        <v>0.6110438135670577</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6437723162271283</v>
+        <v>0.7105075681425603</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.349577092957702</v>
+        <v>0.4162834617652038</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4989477249914529</v>
+        <v>0.5665738285318938</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5634874369242482</v>
+        <v>0.6308139155112755</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3683213555223688</v>
+        <v>0.4359923341363015</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.167036179838405</v>
+        <v>0.2360363100833638</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1135350129500949</v>
+        <v>0.1828130777828179</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.0001346173874026135</v>
+        <v>0.07020062367686819</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.3699752868309147</v>
+        <v>-0.3005824082198387</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3781772478703047</v>
+        <v>-0.3086078120877787</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.5842122986026297</v>
+        <v>-0.539340249018494</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.6792214520673028</v>
+        <v>-0.6591601563862426</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.9296218487394938</v>
+        <v>-0.9339173678198023</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.7757035615830716</v>
+        <v>-0.8050409592016976</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7426836395774927</v>
+        <v>-0.7721366171564057</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.6112608198244018</v>
+        <v>-0.640815212892818</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4939748360801062</v>
+        <v>-0.5237866174507175</v>
       </c>
     </row>
     <row r="17">
@@ -4086,79 +4086,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2219</v>
+        <v>2223</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.222554245641838</v>
+        <v>1.255828537960667</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.561233178436858</v>
+        <v>1.594906187050199</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.648936128546595</v>
+        <v>1.684290552215082</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.564073632963499</v>
+        <v>1.600267350382403</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.097276444525249</v>
+        <v>2.162949474420927</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.026579422311912</v>
+        <v>1.092054025298182</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9724913675265299</v>
+        <v>1.038883418676477</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7388603518372605</v>
+        <v>0.8055956037526926</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3760637483962839</v>
+        <v>0.4427701172037857</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5905481938712356</v>
+        <v>0.6581742974116764</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6402893118401209</v>
+        <v>0.7076157904271483</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6307371873409693</v>
+        <v>0.698408165954902</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6293367145860671</v>
+        <v>0.6983368448310259</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3630562737224281</v>
+        <v>0.432334338555151</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.2881322224659044</v>
+        <v>0.35819822875537</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1194905649893485</v>
+        <v>0.1888834436004245</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.03032050066971692</v>
+        <v>0.09988993645224298</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1826613405747182</v>
+        <v>-0.139721656856814</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3444178963398556</v>
+        <v>-0.3281429443960917</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5805780476833107</v>
+        <v>-0.5905334327209744</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4222508140384562</v>
+        <v>-0.4592251532476439</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.5164427226324619</v>
+        <v>-0.5533232321244697</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4401010188791474</v>
+        <v>-0.476973165992753</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2189358780758468</v>
+        <v>-0.2562815047443721</v>
       </c>
     </row>
     <row r="18">
@@ -4168,243 +4168,243 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.10723371198106</v>
+        <v>1.135917168853197</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.540919321796132</v>
+        <v>1.569263270167326</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.542833466071357</v>
+        <v>1.619482339235233</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.597901277337598</v>
+        <v>1.674651219456436</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.809277335658095</v>
+        <v>1.86694524042813</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7470426214183661</v>
+        <v>0.8537193958005957</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7910914341024409</v>
+        <v>0.8498936115741813</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6086444291413073</v>
+        <v>0.6676975292791099</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2176761116555284</v>
+        <v>0.2771155801328362</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3568632861816354</v>
+        <v>0.416345847447289</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5351149127395516</v>
+        <v>0.5943901271512217</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5923977512156355</v>
+        <v>0.6516944923061985</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4770367585814412</v>
+        <v>0.5847014124880019</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.303733767825797</v>
+        <v>0.4116302172704138</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.269502192411764</v>
+        <v>0.3295790944378041</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1437549378524565</v>
+        <v>0.2518584791748495</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.153822704539671</v>
+        <v>0.2619643858843688</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2108592662445545</v>
+        <v>-0.1309224053107911</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2065844401610804</v>
+        <v>-0.1550694305314479</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2797160731472488</v>
+        <v>-0.2562697079374061</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.02412241188673647</v>
+        <v>-0.03069297623948586</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1675658692648412</v>
+        <v>-0.1738695952800384</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1049224668331377</v>
+        <v>-0.1109517111719924</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.1853919594872693</v>
+        <v>0.1783788641265289</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 51.81</t>
+          <t>X &gt; 51.8</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1931</v>
+        <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8666422681398203</v>
+        <v>0.8717882656294051</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.666657671968139</v>
+        <v>1.671616934015013</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.413747713557953</v>
+        <v>1.419776327480157</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.422348621211029</v>
+        <v>1.428843968687232</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.573074708220012</v>
+        <v>1.660356229507684</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4702496411442354</v>
+        <v>0.5064250458268305</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7293752531562632</v>
+        <v>0.765935877150504</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4508206076377022</v>
+        <v>0.5392974081581272</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.02365919937269467</v>
+        <v>0.0134818567051127</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.02350080209258465</v>
+        <v>0.01416081707914429</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2508584650227519</v>
+        <v>0.3397934350017735</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5909596079874717</v>
+        <v>0.6799197406821875</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1372630231432623</v>
+        <v>0.2272063587151933</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1739041481254162</v>
+        <v>0.2639923610721056</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.1857675427310497</v>
+        <v>0.2762977483806637</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1616325459128092</v>
+        <v>0.2518089611952448</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.02753885176388593</v>
+        <v>0.1178918242177716</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.09824956051404143</v>
+        <v>-0.03852185536411667</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.1095644567774556</v>
+        <v>-0.08049535324329327</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.09851421188630383</v>
+        <v>-0.099941446318077</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.1128233759038082</v>
+        <v>0.0279610706050164</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.01619114684417866</v>
+        <v>-0.06858859314765198</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.2185079005993273</v>
+        <v>0.1335348137875982</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.4325395743804492</v>
+        <v>0.3468467598671481</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 54.07</t>
+          <t>X &gt; 54.06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3021899309666338</v>
+        <v>0.335464223285463</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9258412634740267</v>
+        <v>0.9595142720873682</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.065385018226017</v>
+        <v>1.100739441894504</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5207964427655085</v>
+        <v>0.5569901601844123</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.170755084137404</v>
+        <v>1.236428114033082</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3990928499924777</v>
+        <v>0.4645674529787485</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4158488273575145</v>
+        <v>0.4822408785074614</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.419302078060042</v>
+        <v>0.4860373299754741</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.122408667617357</v>
+        <v>0.1891150364248588</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.08179378702278228</v>
+        <v>0.1494198905632231</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2997514748939025</v>
+        <v>0.3670779534809299</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6974765223496249</v>
+        <v>0.7651475009635575</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.419008992525761</v>
+        <v>0.4880091227707197</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6488648154451582</v>
+        <v>0.7181428802778811</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.5539493688500485</v>
+        <v>0.6240153751395141</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3593873090523658</v>
+        <v>0.4287801876634418</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4508999318803149</v>
+        <v>0.5204693676628409</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.06390861956393223</v>
+        <v>0.1336207676205561</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1940979716926634</v>
+        <v>-0.1581020646530717</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.0264680971202722</v>
+        <v>0.02874374531495505</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.1947939412845372</v>
+        <v>0.1630165282795488</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.07329622213067211</v>
+        <v>-0.1384357501064315</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.2919319190361307</v>
+        <v>0.2262114646323212</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.3631390303716273</v>
+        <v>0.2971188198230053</v>
       </c>
     </row>
     <row r="21">
@@ -4414,79 +4414,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.186759257937787</v>
+        <v>0.2200335502566162</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6811944644166203</v>
+        <v>0.7148674730299618</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.964531651893985</v>
+        <v>0.9998860755624719</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3145545480179806</v>
+        <v>0.3507482654368843</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.544689995923108</v>
+        <v>1.610363025818785</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7107952598552245</v>
+        <v>0.7762698628414952</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.214253314144528</v>
+        <v>1.280645365294475</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.127147296577462</v>
+        <v>1.193882548492894</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.23247957091727</v>
+        <v>1.299185939724772</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.54351971853967</v>
+        <v>1.611145822080111</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.626430357703512</v>
+        <v>1.69375683629054</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.240763384668938</v>
+        <v>2.308434363282871</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.073515305939296</v>
+        <v>2.142515436184254</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.979790913539269</v>
+        <v>2.049068978371992</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.95902176767364</v>
+        <v>2.029087773963106</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.852103514806181</v>
+        <v>1.921496393417257</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.909458448608767</v>
+        <v>1.979027884391293</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.102496730024647</v>
+        <v>1.172208878081271</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.935722637053459</v>
+        <v>1.005203003102594</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8421136653895331</v>
+        <v>0.8729677664847983</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9763682810978977</v>
+        <v>0.9685836916904265</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.9393483716765729</v>
+        <v>0.8927377302813255</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.573006138181938</v>
+        <v>1.486293489349215</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.344243023264525</v>
+        <v>1.257929900574119</v>
       </c>
     </row>
     <row r="22">
@@ -4496,243 +4496,243 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5198975585088661</v>
+        <v>0.5136718370053472</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8411771860964876</v>
+        <v>0.9077580124164655</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.297902688458208</v>
+        <v>1.291896397787816</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.365290994521061</v>
+        <v>0.3602834862167867</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8752947324729377</v>
+        <v>0.9720148795587278</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4789436634957767</v>
+        <v>0.5758906866473623</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.018987815905646</v>
+        <v>1.115895355526689</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.615706693363016</v>
+        <v>1.639433181910647</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.730162218633637</v>
+        <v>1.753806661201445</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.904539791088133</v>
+        <v>2.001299148430249</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.960080677459494</v>
+        <v>2.056699898463897</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.993897058448482</v>
+        <v>3.089903847785578</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.036437203929239</v>
+        <v>3.132922538946957</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.815080392894885</v>
+        <v>2.838957365124273</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.593785915345556</v>
+        <v>2.618131851800271</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.386511902239</v>
+        <v>2.410769502606243</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.325357668338079</v>
+        <v>2.349738663004864</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.56391911001085</v>
+        <v>1.588921282798843</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.342405511454693</v>
+        <v>1.367494879466605</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.500912408759127</v>
+        <v>1.481454392058531</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.659593601228487</v>
+        <v>1.594884900477346</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.409353307289265</v>
+        <v>1.300380046939964</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.094811362412159</v>
+        <v>1.939286246302487</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.283741320113364</v>
+        <v>2.127195000579427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.86</t>
+          <t>X &gt; 60.85</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.591253488941703</v>
+        <v>1.624527781260532</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.424569970927536</v>
+        <v>1.458242979540877</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.669789473142998</v>
+        <v>1.705143896811485</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.545718148155402</v>
+        <v>1.581911865574305</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.433186358076597</v>
+        <v>1.498859387972274</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.283366977823064</v>
+        <v>1.348841580809335</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.858436818810318</v>
+        <v>1.924828869960265</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.506588154757637</v>
+        <v>2.573323406673069</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.71659621641043</v>
+        <v>2.783302585217932</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.459188775312441</v>
+        <v>3.526814878852882</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.396564049167459</v>
+        <v>3.463890527754486</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.381160120418755</v>
+        <v>4.448831099032688</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.267620881712574</v>
+        <v>4.336621011957533</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.793526075732977</v>
+        <v>3.8628041405657</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.471578829956002</v>
+        <v>3.541644836245467</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.476916891371822</v>
+        <v>3.546309769982898</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.258577198907815</v>
+        <v>3.328146634690341</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.479625796291899</v>
+        <v>2.549337944348522</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.274518967648312</v>
+        <v>2.343999333697447</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.040332771693343</v>
+        <v>2.109615152090072</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.307769236870506</v>
+        <v>2.325282968959762</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.284325548017662</v>
+        <v>2.249437007550661</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.727877085807812</v>
+        <v>2.692403716662874</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.704678362573098</v>
+        <v>2.616571463439598</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.12</t>
+          <t>X &gt; 63.11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.617905491463425</v>
+        <v>2.651179783782254</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.090607018125532</v>
+        <v>2.124280026738873</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.283951702934679</v>
+        <v>2.319306126603166</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.666219869088309</v>
+        <v>1.702413586507213</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.781257480798182</v>
+        <v>1.846930510693859</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.776299135111401</v>
+        <v>1.841773738097672</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.060109275871966</v>
+        <v>2.126501327021913</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.550046465127664</v>
+        <v>2.616781717043096</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.591562530150298</v>
+        <v>2.6582688989578</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.450772268276161</v>
+        <v>3.518398371816602</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.629070056044725</v>
+        <v>3.696396534631752</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.502713904731202</v>
+        <v>4.570384883345135</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.050653041671524</v>
+        <v>4.119653171916482</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.63717327194361</v>
+        <v>3.706451336776333</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.266426470946655</v>
+        <v>3.336492477236121</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.996933206446997</v>
+        <v>3.066326085058073</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.670716553604507</v>
+        <v>2.740285989387033</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.989364261428541</v>
+        <v>2.059076409485165</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.725180027626443</v>
+        <v>1.794660393675578</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.008285302593663</v>
+        <v>2.077567682990392</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.293338052540506</v>
+        <v>2.303513349798614</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.27725935730362</v>
+        <v>2.227667388389513</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.648280914546092</v>
+        <v>2.598203580218353</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.825102254673297</v>
+        <v>2.714494285688637</v>
       </c>
     </row>
     <row r="25">
@@ -4742,325 +4742,325 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.022307165677773</v>
+        <v>3.055581457996603</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.682667365319169</v>
+        <v>1.71634037393251</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.36350261551874</v>
+        <v>2.398857039187227</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.761316445182722</v>
+        <v>1.797510162601625</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.954082374444397</v>
+        <v>2.019755404340074</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.806425558879752</v>
+        <v>1.871900161866023</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.591595141111434</v>
+        <v>1.65798719226138</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.094290495592873</v>
+        <v>2.161025747508305</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.912592274901229</v>
+        <v>1.979298643708731</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.25482829270323</v>
+        <v>2.322454396243671</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.752401845532845</v>
+        <v>2.819728324119872</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.589379370629374</v>
+        <v>3.657050349243306</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.357745294999368</v>
+        <v>3.426745425244327</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.471209912536445</v>
+        <v>3.540487977369168</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.035492959213435</v>
+        <v>3.105558965502901</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.179660151691955</v>
+        <v>2.249053030303031</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.045566457543032</v>
+        <v>2.115135893325558</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.382547327162044</v>
+        <v>1.452259475218668</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.263849061522428</v>
+        <v>1.333329427571563</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.674107142857139</v>
+        <v>1.743389523253867</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.246978162430615</v>
+        <v>2.316914783859268</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.352213250443235</v>
+        <v>2.352675965307306</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.185647634802457</v>
+        <v>3.185186392075082</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.29192668472075</v>
+        <v>3.220961281708945</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 67.65</t>
+          <t>X &gt; 67.64</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>754</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.426674350217375</v>
+        <v>2.459948642536204</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.693620851488163</v>
+        <v>1.727293860101504</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.641188291911313</v>
+        <v>2.676542715579799</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.590524952192958</v>
+        <v>2.626718669611861</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.021011135338668</v>
+        <v>3.086684165234345</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.942923758955537</v>
+        <v>3.008398361941808</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.833187600376306</v>
+        <v>2.899579651526253</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.88089290180735</v>
+        <v>3.947628153722782</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.259278993355188</v>
+        <v>3.32598536216269</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.35281758789079</v>
+        <v>2.420443691431231</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.759802849701096</v>
+        <v>2.827129328288123</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.806968893175799</v>
+        <v>3.874639871789732</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.345607648163451</v>
+        <v>3.41460777840841</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.654754815908937</v>
+        <v>3.72403288074166</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.52632755565147</v>
+        <v>3.596393561940936</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.397249674238381</v>
+        <v>2.466642552849457</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.130529985394489</v>
+        <v>2.200099421177015</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.423424553384088</v>
+        <v>2.493136701440712</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.506921721620948</v>
+        <v>2.576402087670083</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.357095490716176</v>
+        <v>3.426377871112905</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.742277044582941</v>
+        <v>3.812213666011594</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.329451962415142</v>
+        <v>4.399497678077303</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.002105112982157</v>
+        <v>5.071850374644242</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.058789768408637</v>
+        <v>5.128644116115915</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 69.91</t>
+          <t>X &gt; 69.9</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.147708449786926</v>
+        <v>3.319152886568034</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.528423785864909</v>
+        <v>1.704376088218211</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.335914333014728</v>
+        <v>2.506357039187229</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.906230169099267</v>
+        <v>2.913403019744493</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.701474027734925</v>
+        <v>2.897612547197213</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.1727477900194</v>
+        <v>4.3645787332946</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.683990807243056</v>
+        <v>4.712630049404247</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.689545311002185</v>
+        <v>5.714418604651165</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.570547732365107</v>
+        <v>5.595905786565872</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.117739608915095</v>
+        <v>5.142990110529382</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.071071588711014</v>
+        <v>5.097049752691305</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.434032259874961</v>
+        <v>5.458300349243302</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.630568328707241</v>
+        <v>4.815138282387188</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.767156943034031</v>
+        <v>3.954059405940605</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.231821209614715</v>
+        <v>4.415916108360044</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.221744822638982</v>
+        <v>3.410303030303034</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.124569266531793</v>
+        <v>2.316385893325553</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.661640425075362</v>
+        <v>2.851545189504378</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.877763588007177</v>
+        <v>3.067436570428704</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.027889245585868</v>
+        <v>4.214282380396725</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.571366204164171</v>
+        <v>5.591736212430696</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.976952079500684</v>
+        <v>5.995890251021599</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.412240889642526</v>
+        <v>6.590364963503646</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.336299550374058</v>
+        <v>6.514532710280371</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 72.17</t>
+          <t>X &gt; 72.16</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>489</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.994590250690919</v>
+        <v>4.027864543009748</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.068412691056821</v>
+        <v>4.102085699670162</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.469203024516695</v>
+        <v>4.504557448185182</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.777904598849098</v>
+        <v>4.814098316268002</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.412634813825051</v>
+        <v>4.478307843720728</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.213296359347176</v>
+        <v>5.278770962333446</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.485420002344277</v>
+        <v>6.551812053494224</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.820362289341048</v>
+        <v>6.88709754125648</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.066377331868793</v>
+        <v>7.133083700676295</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.519535786130042</v>
+        <v>7.587161889670483</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.793895053245379</v>
+        <v>7.861221531832406</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.310302172265366</v>
+        <v>7.377973150879299</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.185810953778223</v>
+        <v>6.254811084023181</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.123963345197858</v>
+        <v>4.193241410030581</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.896524948696346</v>
+        <v>4.966590954985811</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.264591133287048</v>
+        <v>4.333984011898124</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.517000506622786</v>
+        <v>3.586569942405312</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.821015045537735</v>
+        <v>3.890727193594358</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.24163718597466</v>
+        <v>4.311117552023795</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.246676891615536</v>
+        <v>5.315959272012265</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.081509157036329</v>
+        <v>7.15155487269849</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.560783301023569</v>
+        <v>7.630528562685654</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>8.302837871775544</v>
+        <v>8.372692219482822</v>
       </c>
     </row>
     <row r="29">
@@ -5073,568 +5073,568 @@
         <v>387</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.982209343603209</v>
+        <v>5.015483635922038</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.871840030509269</v>
+        <v>3.90551303912261</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.982527163322359</v>
+        <v>4.017881586990846</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.78552971576228</v>
+        <v>3.821723433181184</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.420259930738233</v>
+        <v>3.48593296063391</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.641016275011168</v>
+        <v>4.706490877997439</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.418537739856369</v>
+        <v>5.484929791006316</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.207166556870106</v>
+        <v>7.273901808785538</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.765478487525812</v>
+        <v>7.832184856333313</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.508438942389454</v>
+        <v>7.576065045929894</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.299594075137875</v>
+        <v>8.366920553724903</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.986908440396817</v>
+        <v>7.05457941901075</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.862417221909674</v>
+        <v>5.931417352154632</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.7986831498934</v>
+        <v>2.867961214726122</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.914945709305712</v>
+        <v>2.985011715595178</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.734811960477479</v>
+        <v>2.804204839088555</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.342320333512021</v>
+        <v>2.411889769294547</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.012530715866355</v>
+        <v>3.082242863922978</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.745449744431255</v>
+        <v>3.81493011048039</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>5.482881136950908</v>
+        <v>5.552163517347637</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.930909134842643</v>
+        <v>7.000954850504804</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.421732626138983</v>
+        <v>8.49158697384626</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 76.7</t>
+          <t>X &gt; 76.69</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.16832232415274</v>
+        <v>5.333511860927011</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.546973176067901</v>
+        <v>3.716683780525905</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.679619978862789</v>
+        <v>4.842767295597483</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.679653032229119</v>
+        <v>2.847761994103465</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.243643697365847</v>
+        <v>4.435048444633104</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.752351718732761</v>
+        <v>4.942527451243315</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.265659220119247</v>
+        <v>5.452630049404242</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.559451841481703</v>
+        <v>7.738521168753735</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.565598131584736</v>
+        <v>8.741546812206892</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.791762720815306</v>
+        <v>7.968631136170401</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.744578579570515</v>
+        <v>7.922177957819507</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.536224225934838</v>
+        <v>5.720351631294584</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.804015965647054</v>
+        <v>2.994625461874371</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3112315206284606</v>
+        <v>-0.1110687991876063</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.6375542821348859</v>
+        <v>0.8333520057959305</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.232614331756267</v>
+        <v>1.427738927738922</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.420064045967472</v>
+        <v>1.61433461127428</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.958167446592455</v>
+        <v>2.150519548478741</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.460464242964782</v>
+        <v>3.648462211454337</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.969051446945336</v>
+        <v>4.155820841935189</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>5.033568079748015</v>
+        <v>5.215838776533268</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.243786657545932</v>
+        <v>6.422044097175437</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.197018415667934</v>
+        <v>6.376005989144673</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>7.728794118200106</v>
+        <v>7.902737838485514</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 78.96</t>
+          <t>X &gt; 78.95</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>217</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.233712695631688</v>
+        <v>6.266986987950517</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.898537180987361</v>
+        <v>5.932210189600703</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.145472661601694</v>
+        <v>8.180827085270181</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.127531882970743</v>
+        <v>5.163725600389647</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.9880685495596</v>
+        <v>8.053741579455277</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.01855113491662</v>
+        <v>10.08402573790289</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.784855509775035</v>
+        <v>8.851247560924982</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.888789343519136</v>
+        <v>9.955524595434568</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.93030540854177</v>
+        <v>9.997011777349272</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.156469997772341</v>
+        <v>9.224096101312782</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.509170278712574</v>
+        <v>8.576496757299601</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.386758402887438</v>
+        <v>6.45442938150137</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.340608198225183</v>
+        <v>4.409608328470142</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.736762907928146</v>
+        <v>2.806040972760869</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.077831668890845</v>
+        <v>2.14789767518031</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.672891718512226</v>
+        <v>2.742284597123302</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.538798024363302</v>
+        <v>2.608367460145828</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.355473594443147</v>
+        <v>3.425185742499771</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.41491472972519</v>
+        <v>5.484395095774325</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.297811059907829</v>
+        <v>3.367093440304558</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>4.59792862326011</v>
+        <v>4.667865244688763</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.904462046880177</v>
+        <v>5.974507762542338</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>6.179237213362306</v>
+        <v>6.248982475024391</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>7.024954860268956</v>
+        <v>7.094809207976233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 81.22</t>
+          <t>X &gt; 81.21</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>175</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.3258785942492</v>
+        <v>10.35915288656803</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.704988793890585</v>
+        <v>7.738661802503927</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.26528832980445</v>
+        <v>10.30064275347294</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.980066445182736</v>
+        <v>9.01626016260164</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.90051094587297</v>
+        <v>10.96618397576864</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.23053270173689</v>
+        <v>12.29600730472316</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.45766656968286</v>
+        <v>11.52405862083281</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>13.46482620987858</v>
+        <v>13.53156146179401</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.79205656061551</v>
+        <v>11.85876292942301</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.16107829270322</v>
+        <v>12.22870439624366</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.00686613124712</v>
+        <v>13.07419260983415</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.15634365634365</v>
+        <v>12.22401463495758</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.888995294999368</v>
+        <v>9.957995425244327</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.524781341107875</v>
+        <v>8.594059405940598</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>6.722992959213435</v>
+        <v>6.793058965502901</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.746624437406233</v>
+        <v>6.816017316017309</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.612530743257309</v>
+        <v>6.682100179039836</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>7.078975898590613</v>
+        <v>7.148688046647237</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>7.866527632950998</v>
+        <v>7.936007999000132</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>6.339285714285708</v>
+        <v>6.408568094682437</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.796085305287754</v>
+        <v>5.866021926716407</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.862987392502298</v>
+        <v>6.933033108164459</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.709191130412997</v>
+        <v>7.778936392075082</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>9.347535505430237</v>
+        <v>9.417389853137514</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 83.49</t>
+          <t>X &gt; 83.48</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.157939662951499</v>
+        <v>8.480365007780158</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.532687812429302</v>
+        <v>5.115285179127312</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.146422462846992</v>
+        <v>7.465144917975103</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.432629149653835</v>
+        <v>6.752190898532362</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.120794479133593</v>
+        <v>9.44670345628812</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.36139420664421</v>
+        <v>12.66397267268853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.82516929596422</v>
+        <v>11.13444823122241</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.83669098632352</v>
+        <v>13.12896405919662</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.35148949409425</v>
+        <v>11.65529972595981</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.57765408332482</v>
+        <v>10.12480829234755</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.85201335044016</v>
+        <v>11.15644369208524</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.282843111087388</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.394993113974287</v>
+        <v>6.724229191478095</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.173636302939933</v>
+        <v>6.503150315031505</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.514705063902632</v>
+        <v>5.087431259875196</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.583047556272099</v>
+        <v>4.924242424242422</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.448953862123176</v>
+        <v>4.790325287264949</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.343970446027896</v>
+        <v>4.685484583443767</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.033376051707819</v>
+        <v>3.386224449216577</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.693702290076338</v>
+        <v>2.057918744033095</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.387143102452427</v>
+        <v>0.7577968184913075</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.3111880468098178</v>
+        <v>0.6819508570822066</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.5859632132919472</v>
+        <v>0.9564255695642601</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.80009820990135</v>
+        <v>3.153320589068251</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 85.75</t>
+          <t>X &gt; 85.74</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>89</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.123631403237965</v>
+        <v>8.156905695556794</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.54126487735769</v>
+        <v>5.574937885971032</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.595946435743457</v>
+        <v>8.631300859411944</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.882153122550299</v>
+        <v>7.918346839969203</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.88766985438019</v>
+        <v>10.95334288427587</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.07483446738698</v>
+        <v>11.14030907037325</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.178372829714966</v>
+        <v>9.244764880864913</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.14700919543236</v>
+        <v>11.21374444734779</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.94133424921904</v>
+        <v>9.008040618026541</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.04390333283164</v>
+        <v>7.111529436372081</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.318262599946976</v>
+        <v>7.385589078534004</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.791977685236112</v>
+        <v>4.859648663850045</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.667486466748969</v>
+        <v>3.736486596993927</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.816916172568547</v>
+        <v>6.88619423740127</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.157984933531246</v>
+        <v>6.228050939820712</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>4.505853971916672</v>
+        <v>4.575246850527748</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.248164772149771</v>
+        <v>3.317734207932297</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.266776861672469</v>
+        <v>4.336489009729092</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.359304518986306</v>
+        <v>3.428784885035441</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.9480337078651715</v>
+        <v>-0.8787513274684429</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.738425128099074</v>
+        <v>-3.668488506670421</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-3.814380183741683</v>
+        <v>-3.744334468079522</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-2.416009511641583</v>
+        <v>-2.346264249979498</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.878835665943889</v>
+        <v>0.9486900136511665</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 88.01</t>
+          <t>X &gt; 88</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>7.195443811640516</v>
+        <v>7.228718103959345</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.961717572358502</v>
+        <v>3.995390580971844</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.768393919866568</v>
+        <v>9.803748343535055</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.054600606673411</v>
+        <v>9.090794324092315</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.48643227092472</v>
+        <v>14.5521053008204</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.67359688393151</v>
+        <v>14.73907148691778</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.103629302602123</v>
+        <v>8.17002135375207</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.825074657083562</v>
+        <v>7.891809908998994</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>3.019288491495587</v>
+        <v>3.086614970082614</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1583561366170017</v>
+        <v>-0.09068515800306898</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>2.843621920818016</v>
+        <v>2.912899985650739</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.184690681780715</v>
+        <v>2.254756688070181</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>4.229026093720933</v>
+        <v>4.298418972332009</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.645657037253173</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>3.989948983476729</v>
+        <v>4.059661131533353</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.206072146408545</v>
+        <v>4.275552512457679</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.04528985507246119</v>
+        <v>0.1145722354691898</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-4.845736640882009</v>
+        <v>-4.775800019453357</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-6.370967058843455</v>
+        <v>-6.300921343181294</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-7.545467254680176</v>
+        <v>-7.475721993018091</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-4.722857869310957</v>
+        <v>-4.653003521603679</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>1.096839856334164</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.522017108272365</v>
+        <v>2.557371531940852</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.706774519716895</v>
+        <v>4.742968237135798</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.427220072337299</v>
+        <v>7.49269467532357</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>4.993259184361307</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.866590722106196</v>
+        <v>7.933297090913698</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.19420458669908</v>
+        <v>4.26183069023952</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.019288491495587</v>
+        <v>3.086614970082614</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.986571399614888</v>
+        <v>10.05424237822882</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.31135554344657</v>
+        <v>10.38035567369153</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.98854945704991</v>
+        <v>13.05782752188263</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>12.32961821801261</v>
+        <v>12.39968422430207</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>17.2725043545905</v>
+        <v>17.34189723320158</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>14.23985993580389</v>
+        <v>14.30942937158642</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>17.0334272443463</v>
+        <v>17.10313939240292</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>18.69882576959696</v>
+        <v>18.76830613564609</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>15.98731884057972</v>
+        <v>16.05660122097645</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>16.89339379390059</v>
+        <v>16.96333041532925</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>16.81743873825798</v>
+        <v>16.88748445392014</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>17.09221390474011</v>
+        <v>17.1619591664022</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>14.11772184083396</v>
+        <v>14.18757618854124</v>
       </c>
     </row>
     <row r="7">
@@ -5913,158 +5913,158 @@
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0377577693871558</v>
+        <v>-0.004483477068326636</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3729332840314825</v>
+        <v>-0.3392602754181411</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.9035428390267199</v>
+        <v>-0.8681884153582331</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.928118393234676</v>
+        <v>2.96431211065358</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.562848608210629</v>
+        <v>2.628521638106307</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.613510725527028</v>
+        <v>5.679902776676975</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.516774261826647</v>
+        <v>3.583509513742079</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.103744872303821</v>
+        <v>8.170451241111323</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.239000370625313</v>
+        <v>8.306626474165753</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.604268728649728</v>
+        <v>7.671595207236756</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.87062937062937</v>
+        <v>11.93830034924331</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.65522906123314</v>
+        <v>11.72422919147809</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.34296315928969</v>
+        <v>12.41224122412241</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>10.77494101116148</v>
+        <v>10.84500701745095</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12.27909196987377</v>
+        <v>12.34848484848484</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>5.781361912088485</v>
+        <v>5.850931347871011</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.585469405084126</v>
+        <v>6.65518155314075</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>7.710683477106834</v>
+        <v>7.780163843155968</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>8.806818181818173</v>
+        <v>8.876100562214901</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>10.99089050009295</v>
+        <v>11.0608271215216</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>12.73311726263217</v>
+        <v>12.80316297829433</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>12.09880152002338</v>
+        <v>12.16854678168546</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>9.295587453482192</v>
+        <v>9.365441801189469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 26.91</t>
+          <t>X &lt; 26.92</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>164</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.454609210628846</v>
+        <v>-2.421334918310016</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3507603350292641</v>
+        <v>-0.3170873264159226</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.6485635911285001</v>
+        <v>0.683918014796987</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.812819058423145</v>
+        <v>4.849012775842048</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.276817566082023</v>
+        <v>6.342490595977701</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.683494374210767</v>
+        <v>7.748968977197038</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.349652632400641</v>
+        <v>9.416044683550588</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.851585791760129</v>
+        <v>7.918321043675562</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.94188234458764</v>
+        <v>11.00858871339514</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.77780303137917</v>
+        <v>10.84542913491961</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.05216229849451</v>
+        <v>11.11948877708154</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.43160498038547</v>
+        <v>14.49927595899941</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>15.13638205458125</v>
+        <v>15.20538218482621</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.30526914598592</v>
+        <v>14.37454721081865</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>12.42682571182667</v>
+        <v>12.49689171811614</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>14.24139795657</v>
+        <v>14.31079083518108</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9.229255481933265</v>
+        <v>9.298824917715791</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>9.124272065837985</v>
+        <v>9.193984213894609</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>9.3403952287698</v>
+        <v>9.409875594818935</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>11.35670731707317</v>
+        <v>11.4259896974699</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>13.25253129831912</v>
+        <v>13.32246791974777</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>13.78633234023749</v>
+        <v>13.85637805589965</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>13.45135140915864</v>
+        <v>13.52109667082073</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>10.3266295820853</v>
+        <v>10.39648392979257</v>
       </c>
     </row>
     <row r="9">
@@ -6077,76 +6077,76 @@
         <v>238</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.253953338523907</v>
+        <v>-3.220679046205078</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.908456584260662</v>
+        <v>-1.874783575647321</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.507820913893021</v>
+        <v>-2.472466490224534</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5598983779558324</v>
+        <v>0.5960920953747362</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.875300861839357</v>
+        <v>1.940973891735034</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.163305810980589</v>
+        <v>4.228780413966859</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.650943880607237</v>
+        <v>4.717335931757184</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.893397638450026</v>
+        <v>6.960132890365458</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.876090174060892</v>
+        <v>9.942796542868393</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.36275896497214</v>
+        <v>10.43038506851258</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.956445963179902</v>
+        <v>9.02377244176693</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.03869659752013</v>
+        <v>12.10636757613406</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>14.69571798407501</v>
+        <v>14.76471811431997</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>14.47436117304066</v>
+        <v>14.54363923787338</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>12.55492573232267</v>
+        <v>12.62499173861213</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>12.30964964749027</v>
+        <v>12.37904252610134</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>10.91505175166068</v>
+        <v>10.98462118744321</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.969732201111611</v>
+        <v>10.03944434916824</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.345519229589648</v>
+        <v>9.414999595638783</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>11.63340336134453</v>
+        <v>11.70268574174126</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>13.19104328848103</v>
+        <v>13.26097990990969</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>12.27475209838465</v>
+        <v>12.34479781404681</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>12.96969533209366</v>
+        <v>13.03944059375574</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>11.63324979114453</v>
+        <v>11.70310413885181</v>
       </c>
     </row>
     <row r="10">
@@ -6159,76 +6159,76 @@
         <v>318</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.7307251793357</v>
+        <v>-2.697450887016871</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.751435285174999</v>
+        <v>-2.717762276561658</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.820066566871198</v>
+        <v>-4.784712143202711</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.44580956559895</v>
+        <v>-1.409615848180046</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.496613941817962</v>
+        <v>-1.430940911922285</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8918085328240437</v>
+        <v>0.9572831358103144</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.691269444795175</v>
+        <v>1.757661495945122</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.2995072521068</v>
+        <v>3.366242504022232</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.227815769959619</v>
+        <v>5.294522138767121</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.340772812020383</v>
+        <v>6.408398915560824</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.872993714355843</v>
+        <v>7.94032019294287</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.795157672516169</v>
+        <v>9.862828651130101</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>10.87192431566424</v>
+        <v>10.9409244459092</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>11.27949832223995</v>
+        <v>11.34877638707268</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>11.56396330961774</v>
+        <v>11.63402931590721</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.21562713282403</v>
+        <v>11.28502001143511</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>8.565810168234847</v>
+        <v>8.635379604017373</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>9.404222978554671</v>
+        <v>9.473935126611295</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>8.676949915071383</v>
+        <v>8.746430281120517</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.43632075471697</v>
+        <v>10.5056031351137</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.83651657213412</v>
+        <v>10.90645319356278</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>11.07502692529653</v>
+        <v>11.14507264095869</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>11.97873290938873</v>
+        <v>12.04847817105082</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>10.95939534370518</v>
+        <v>11.02924969141245</v>
       </c>
     </row>
     <row r="11">
@@ -6241,158 +6241,158 @@
         <v>398</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.796928423294652</v>
+        <v>-2.763654130975823</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.255528076174016</v>
+        <v>-3.098430929325637</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.695228540260153</v>
+        <v>-4.536449978356629</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.142690195161862</v>
+        <v>-1.991258634390853</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.256703698778864</v>
+        <v>-2.327049106938126</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8132576787369032</v>
+        <v>-0.7477830757506325</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1726701590583204</v>
+        <v>0.2390622102082673</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.401653201981965</v>
+        <v>1.468388453897397</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.196938111225698</v>
+        <v>2.2636444800332</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.43315295171255</v>
+        <v>3.500779055252991</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.461281063049</v>
+        <v>4.528607541636028</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.443493692237411</v>
+        <v>6.511164670851343</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.831565287820617</v>
+        <v>7.900565418065575</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.8614647581933</v>
+        <v>7.930742823026023</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>9.463840051819311</v>
+        <v>9.533906058108776</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>8.551362412998493</v>
+        <v>8.620755291609569</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>6.909731030407357</v>
+        <v>6.979300466189883</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>7.809772739940215</v>
+        <v>7.879484887996838</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>7.523383340057954</v>
+        <v>7.592863706107089</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>9.2179648241206</v>
+        <v>9.287247204517328</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.428533259343759</v>
+        <v>9.498469880772411</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>10.10634704792225</v>
+        <v>10.17639276358441</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>11.13489105862548</v>
+        <v>11.20463632028756</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>10.05392459372887</v>
+        <v>10.12377894143615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 35.97</t>
+          <t>X &lt; 35.96</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.387839099587772</v>
+        <v>-1.466934069953709</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.013280984140145</v>
+        <v>-3.185110077789687</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.953987404441342</v>
+        <v>-3.136415238040492</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.472171935199363</v>
+        <v>-1.563104916763457</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.234647309045769</v>
+        <v>-3.380876518409146</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.05147471200705</v>
+        <v>-1.096138398179519</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4271352552387171</v>
+        <v>-0.3607432040887701</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2923140912586888</v>
+        <v>0.3590493431741208</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7330317530877153</v>
+        <v>0.7997381218952171</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.556002729543827</v>
+        <v>1.623628833084268</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.628765190271942</v>
+        <v>2.696091668858969</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.343683262844941</v>
+        <v>5.411354241458874</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.616397633180163</v>
+        <v>5.685397763425122</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.794242418952187</v>
+        <v>5.86352048378491</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>6.732117567140442</v>
+        <v>6.802183573429907</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>7.327177616761823</v>
+        <v>7.396570495372899</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.596277535387344</v>
+        <v>5.66584697116987</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>6.090096514501639</v>
+        <v>6.159808662558262</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.306219677433454</v>
+        <v>6.375700043482588</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>7.491267465069868</v>
+        <v>7.560549845466596</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>7.746470249684684</v>
+        <v>7.816406871113337</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>8.468918387654846</v>
+        <v>8.538964103317007</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>8.943294352540171</v>
+        <v>9.013039614202256</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>8.667752214868507</v>
+        <v>8.737606562575785</v>
       </c>
     </row>
     <row r="13">
@@ -6405,76 +6405,76 @@
         <v>618</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.061218179944348</v>
+        <v>-2.198539421124281</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.766970587600291</v>
+        <v>-3.895367089951918</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.183625216196475</v>
+        <v>-3.323610806471933</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.470234063370206</v>
+        <v>-1.537224999579188</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.291814528005915</v>
+        <v>-3.397871323770531</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.162902342183585</v>
+        <v>-1.186568278013965</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.45033158103373</v>
+        <v>-1.383939529883783</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1107632492060162</v>
+        <v>-0.04402799729058415</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2543774112858799</v>
+        <v>0.3210837800933817</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.098664977862718</v>
+        <v>1.166291081403159</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.343898031385827</v>
+        <v>2.411224509972854</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.653800891664972</v>
+        <v>4.721471870278904</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.309244948258744</v>
+        <v>5.378245078503703</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.896949625897513</v>
+        <v>5.966227690730236</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.047079875533349</v>
+        <v>6.117145881822815</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.318515329685489</v>
+        <v>6.387908208296565</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.860797040067311</v>
+        <v>5.930366475849837</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.270376730768149</v>
+        <v>5.340088878824773</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>5.648312191434577</v>
+        <v>5.717792557483712</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.320792880258892</v>
+        <v>6.390075260655621</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.101217066730207</v>
+        <v>6.17115368815886</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.623661773038982</v>
+        <v>6.693407034701067</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.385908136035873</v>
+        <v>6.45576248374315</v>
       </c>
     </row>
     <row r="14">
@@ -6487,76 +6487,76 @@
         <v>737</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.00026695831145</v>
+        <v>-3.104654083941348</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.806867770597556</v>
+        <v>-3.908509817822051</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.827375762859646</v>
+        <v>-3.935148337156861</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.379006913890642</v>
+        <v>-2.425385674737342</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.690222644860626</v>
+        <v>-3.766969663045373</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.205760734556542</v>
+        <v>-1.214692521766139</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.498065114059642</v>
+        <v>-1.506829410055218</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6172488965867586</v>
+        <v>-0.7039597737272132</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.04404337976651362</v>
+        <v>-0.1219320512719619</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3556896514936909</v>
+        <v>0.1862333537726286</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7657341289210962</v>
+        <v>0.6744245835438036</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.250547959503187</v>
+        <v>2.23640333027312</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.618594054448877</v>
+        <v>2.687594184693836</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.211348505286985</v>
+        <v>3.280626570119708</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.095158107497987</v>
+        <v>3.165224113787453</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.554532946807292</v>
+        <v>3.623925825418368</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>2.74201320109799</v>
+        <v>2.811582636880516</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.365659364378544</v>
+        <v>2.435371512435168</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.853152947934525</v>
+        <v>2.92263331398366</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.447252374491185</v>
+        <v>3.516534754887914</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.175422386117383</v>
+        <v>3.245359007546035</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.370837751098918</v>
+        <v>3.440883466761079</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.374242496956903</v>
+        <v>3.443987758618988</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.298301157688435</v>
+        <v>3.368155505395713</v>
       </c>
     </row>
     <row r="15">
@@ -6569,158 +6569,158 @@
         <v>890</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.118565850195239</v>
+        <v>-3.198369237325771</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.509853093921265</v>
+        <v>-4.584704753420766</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.333184466886607</v>
+        <v>-3.418077550613219</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.267467757808042</v>
+        <v>-3.296408301010231</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.465630159398572</v>
+        <v>-4.573498563913901</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.211431583977387</v>
+        <v>-2.326589231110304</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.141694962639562</v>
+        <v>-2.258951242355216</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.687618660687086</v>
+        <v>-1.869011239446827</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7998487345372638</v>
+        <v>-0.9853205233560871</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9497481006343804</v>
+        <v>-1.137367032327759</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.011711703474198</v>
+        <v>-1.134905554571269</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6181598670387842</v>
+        <v>-0.6791493151862227</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1731443590685373</v>
+        <v>-0.1703040468401369</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.05817830014772341</v>
+        <v>0.01109976468499951</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2474438169976239</v>
+        <v>0.2498174536515165</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.910348353939149</v>
+        <v>0.8442043755945079</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.6638951092284273</v>
+        <v>0.5981796152986547</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.5589116931331475</v>
+        <v>0.4933389114774727</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.449192159435746</v>
+        <v>1.450197513189643</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.860955056179783</v>
+        <v>1.930237436576512</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.43011419774362</v>
+        <v>1.500050819172273</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.354159142101011</v>
+        <v>1.424204857763172</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.516574758021349</v>
+        <v>1.586320019683434</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.440633418752881</v>
+        <v>1.510487766460159</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 45.02</t>
+          <t>X &lt; 45.01</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1023</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.952273475048194</v>
+        <v>-3.01764481237732</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.201975147755434</v>
+        <v>-4.263531781263552</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.665005099042496</v>
+        <v>-3.732567072244088</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.460087994971722</v>
+        <v>-3.530443134101667</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.257529081732287</v>
+        <v>-4.393090051455339</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.375712117273878</v>
+        <v>-2.518195833179398</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.128282814911245</v>
+        <v>-2.273985186854198</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.353556957341787</v>
+        <v>-2.499326569094009</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.676697769438526</v>
+        <v>-1.825157015366493</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.008131138642128</v>
+        <v>-2.157590160263652</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.165145530560444</v>
+        <v>-2.313443954956334</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.709137166335609</v>
+        <v>-1.860149263159798</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.220755713485808</v>
+        <v>-1.376908274353838</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.093152382089002</v>
+        <v>-1.250600788234159</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8170767271977226</v>
+        <v>-0.9775921520869986</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.03122265169195515</v>
+        <v>-0.1311755689187564</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.05311166770921005</v>
+        <v>-0.1099432205984954</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5346385155435485</v>
+        <v>0.4279974312197723</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.7507616784753637</v>
+        <v>0.7025585216482142</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.328812316715542</v>
+        <v>1.338813630396729</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.9811153290274603</v>
+        <v>1.051051950456113</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.9051602733848512</v>
+        <v>0.9752059890470122</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.5934251759373623</v>
+        <v>0.6631704375994474</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.3219804153590218</v>
+        <v>0.3918347630662993</v>
       </c>
     </row>
     <row r="17">
@@ -6733,76 +6733,76 @@
         <v>1180</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.587164884011663</v>
+        <v>-2.640847113431967</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.465363866001816</v>
+        <v>-3.516908315451509</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.773955508434355</v>
+        <v>-3.827666333099913</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.690032944111969</v>
+        <v>-3.745644599303127</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.682422898805854</v>
+        <v>-4.790146650127205</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.688502922588398</v>
+        <v>-2.802617919425067</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.575946875695287</v>
+        <v>-2.692261072873812</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.135798564842062</v>
+        <v>-2.254332443127552</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.458544689985736</v>
+        <v>-1.57939622685695</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.8483091185376</v>
+        <v>-1.969688310965168</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.948084483062679</v>
+        <v>-2.068664533022982</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.926838983801005</v>
+        <v>-2.0482429644657</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.905888874884802</v>
+        <v>-2.029979562730652</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.402522124657132</v>
+        <v>-1.528939751599424</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.250901166964958</v>
+        <v>-1.379429591471322</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.9446783326433561</v>
+        <v>-1.073072497123128</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.7748784577112104</v>
+        <v>-0.9042897823501193</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.3713872975352999</v>
+        <v>-0.4523263235979016</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.07051837189162313</v>
+        <v>-0.1017004854088626</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.3707627118644012</v>
+        <v>0.3894559621071423</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2600818234950282</v>
+        <v>0.3301275391571892</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.1111281764178358</v>
+        <v>0.1808734380799208</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3037962136980923</v>
+        <v>-0.2339418659908148</v>
       </c>
     </row>
     <row r="18">
@@ -6812,243 +6812,243 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.996269056757505</v>
+        <v>-2.039953591466215</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.889893935320501</v>
+        <v>-2.93240483577582</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.021812918461841</v>
+        <v>-3.139220887732975</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.173254075850799</v>
+        <v>-3.290776084733125</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.498890699601979</v>
+        <v>-3.587107393056712</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.849877905619827</v>
+        <v>-2.015331580606755</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.907769492382407</v>
+        <v>-1.998753645434952</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.62020270423578</v>
+        <v>-1.711808940259019</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.011715811048838</v>
+        <v>-1.10431893253525</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.217729086104157</v>
+        <v>-1.310383202813945</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.501666658277394</v>
+        <v>-1.593902985493244</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.588017245911978</v>
+        <v>-1.680318269375313</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.390806919340086</v>
+        <v>-1.559016488461793</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.116784923952359</v>
+        <v>-1.285639842179705</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.053516891147211</v>
+        <v>-1.147605336335218</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.8663899991376027</v>
+        <v>-1.035962029937927</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.8807307122682886</v>
+        <v>-1.050486751738504</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.3064688453446962</v>
+        <v>-0.4324367109481102</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.3167607767525098</v>
+        <v>-0.398223806929785</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2051886792452819</v>
+        <v>-0.2422735108419403</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5974456920168265</v>
+        <v>-0.5890045283100491</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.371513955206602</v>
+        <v>-0.3625073302331288</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.4740972792905112</v>
+        <v>-0.465961567108593</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.9273971091250175</v>
+        <v>-0.9197227696893933</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 51.81</t>
+          <t>X &lt; 51.8</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.383016284456993</v>
+        <v>-1.387989009867738</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.626963811831395</v>
+        <v>-2.629728891593359</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.412560137517694</v>
+        <v>-2.417009964179776</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.482844715230115</v>
+        <v>-2.487782964083003</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.67670913134711</v>
+        <v>-2.78740431052362</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.236095328785659</v>
+        <v>-1.282168905031988</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.565724112706469</v>
+        <v>-1.611853407719316</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.197326802985323</v>
+        <v>-1.312067881835318</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5757328315641246</v>
+        <v>-0.624188871987208</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5653139591127498</v>
+        <v>-0.6145200383204212</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9303309999798444</v>
+        <v>-1.046321946699351</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.374448701332611</v>
+        <v>-1.489883932599511</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7620140217708169</v>
+        <v>-0.8797769718500987</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8076455793544</v>
+        <v>-0.9256149495546495</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8144220067729648</v>
+        <v>-0.933058772834805</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.7916426052855812</v>
+        <v>-0.909914361001313</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6132380383697722</v>
+        <v>-0.7320981311475876</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.4457418904323589</v>
+        <v>-0.5247813411078681</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.4339784005250706</v>
+        <v>-0.4728221089450244</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4512942779291578</v>
+        <v>-0.4501317885405953</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7220151228944118</v>
+        <v>-0.6117266369217162</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.5936105055125012</v>
+        <v>-0.4830736208257136</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.863794467095758</v>
+        <v>-0.7539295150239553</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.144095479388753</v>
+        <v>-1.034260745752348</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 54.07</t>
+          <t>X &lt; 54.06</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1632</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.551016493682873</v>
+        <v>-0.5857956917743721</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.400073619424248</v>
+        <v>-1.433251030425843</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.654218999538941</v>
+        <v>-1.688627818474799</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.120263358670776</v>
+        <v>-1.156900010558545</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.816814282090562</v>
+        <v>-1.883855008897392</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9880978161636946</v>
+        <v>-1.056974664763658</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.996902598215577</v>
+        <v>-1.066799215926657</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9976759651692575</v>
+        <v>-1.067987227669612</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6780400703586267</v>
+        <v>-0.7491398061392971</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6246359930110685</v>
+        <v>-0.6969125658696456</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8643096728145849</v>
+        <v>-0.9357195717152678</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.291763791763792</v>
+        <v>-1.362552269514303</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9765252565321774</v>
+        <v>-1.049578353810254</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.22338491806083</v>
+        <v>-1.296184496498427</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.112743170100671</v>
+        <v>-1.186719645148202</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.9099588813557773</v>
+        <v>-0.9837384837384775</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.008149862114038</v>
+        <v>-1.08192809567872</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.5869904879640089</v>
+        <v>-0.6620000427694634</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3095928152282781</v>
+        <v>-0.3488325427211407</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5514705882352899</v>
+        <v>-0.5541876318431704</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7270239384097152</v>
+        <v>-0.693334210104517</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.4353319352288025</v>
+        <v>-0.3652862195666415</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.8345763765898013</v>
+        <v>-0.7648311149277163</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.9105177158582691</v>
+        <v>-0.8406633681509916</v>
       </c>
     </row>
     <row r="21">
@@ -7061,76 +7061,76 @@
         <v>1837</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.358757524349187</v>
+        <v>-0.3864092436094779</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9348632634371938</v>
+        <v>-0.9616303703393783</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.266590476764044</v>
+        <v>-1.294095303300658</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7632226631171832</v>
+        <v>-0.7925452561175774</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.800885982428341</v>
+        <v>-1.853223032317608</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.097652626448436</v>
+        <v>-1.151365171775524</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.516141666429313</v>
+        <v>-1.569766065004828</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.43993569488331</v>
+        <v>-1.494047918027022</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.530551529724029</v>
+        <v>-1.58447238739415</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.786607823996974</v>
+        <v>-1.840793673254403</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.861116834296809</v>
+        <v>-1.91491347067268</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.380997527418351</v>
+        <v>-2.433994023051071</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.227274761585385</v>
+        <v>-2.28177563206868</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.146228430879091</v>
+        <v>-2.20117353013741</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.122199870770274</v>
+        <v>-2.177905029851345</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.039089848308052</v>
+        <v>-2.094425820022344</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.087539170515697</v>
+        <v>-2.142952142485626</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.39949448847608</v>
+        <v>-1.456554701917987</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.260465134760331</v>
+        <v>-1.317658486605524</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.182294501905275</v>
+        <v>-1.207891532646755</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.290002259841721</v>
+        <v>-1.283826593442065</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.257084152718953</v>
+        <v>-1.218995494353813</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.798857706977152</v>
+        <v>-1.729112445315067</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.602616139332177</v>
+        <v>-1.5327617916249</v>
       </c>
     </row>
     <row r="22">
@@ -7140,243 +7140,243 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5293139947317798</v>
+        <v>-0.5249756431301194</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8873457008829249</v>
+        <v>-0.9312985342854319</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.276230180967353</v>
+        <v>-1.271342765881002</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6940406976744171</v>
+        <v>-0.6902244790365941</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.0322129008714</v>
+        <v>-1.096533794266193</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.7690483623603086</v>
+        <v>-0.8337423989650432</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.123541952845954</v>
+        <v>-1.187994950595758</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.521475159984426</v>
+        <v>-1.536621942490989</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.599454522525534</v>
+        <v>-1.614494995447821</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.709356854911157</v>
+        <v>-1.773391307563529</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.750325721486128</v>
+        <v>-1.81426140190753</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.443096119566704</v>
+        <v>-2.506144095201137</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.461316482482587</v>
+        <v>-2.524724597142686</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.311332495987315</v>
+        <v>-2.326077781712506</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.156732126697214</v>
+        <v>-2.171927028894856</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.024355074241242</v>
+        <v>-2.039584169304618</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.982765852039272</v>
+        <v>-1.998118522768657</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.469415729447036</v>
+        <v>-1.485578030917807</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.322988212737997</v>
+        <v>-1.339321779276602</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.431074766355145</v>
+        <v>-1.418739732625383</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.531579651496727</v>
+        <v>-1.490348350007842</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.36159274944135</v>
+        <v>-1.291547033779189</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.824643456053167</v>
+        <v>-1.72640669003966</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.949773186861236</v>
+        <v>-1.851451541688128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.86</t>
+          <t>X &lt; 60.85</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.011929012014775</v>
+        <v>-1.028073553807133</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.054954932928702</v>
+        <v>-1.071245002040946</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.261805266254655</v>
+        <v>-1.278640725676432</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.234475285488038</v>
+        <v>-1.251820593851221</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.171718035365437</v>
+        <v>-1.205116759290483</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.094259098391227</v>
+        <v>-1.127704167332091</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.393708165944894</v>
+        <v>-1.427128123457372</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.737020417461757</v>
+        <v>-1.770025839793277</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.850127030378147</v>
+        <v>-1.882928816751026</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.239640485374046</v>
+        <v>-2.272256526241918</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.209827287693479</v>
+        <v>-2.242349080866347</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.733687176133216</v>
+        <v>-2.765469848243228</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.663668415559073</v>
+        <v>-2.696312099292193</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.409512088235054</v>
+        <v>-2.442777970519415</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.232303882621004</v>
+        <v>-2.266331082651192</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.241792551010747</v>
+        <v>-2.275452365380424</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.124738296850843</v>
+        <v>-2.158719819674893</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.707833324647837</v>
+        <v>-1.742658230837655</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.600834954844608</v>
+        <v>-1.635742177882868</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.477888086642601</v>
+        <v>-1.512924826810483</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.614951311525033</v>
+        <v>-1.623838370714857</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.600653659586413</v>
+        <v>-1.583262138518528</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.84127646068665</v>
+        <v>-1.823744193014164</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.82692434623052</v>
+        <v>-1.783229022571611</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.12</t>
+          <t>X &lt; 63.11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.301168864801618</v>
+        <v>-1.313803088274732</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.194170869974954</v>
+        <v>-1.207167535942858</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.350636728743552</v>
+        <v>-1.36412554578969</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.116533338549097</v>
+        <v>-1.130795133068268</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.16415640192438</v>
+        <v>-1.191492870694432</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.164128192923997</v>
+        <v>-1.191387653260023</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.282183054377285</v>
+        <v>-1.309665032562975</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.495096765208665</v>
+        <v>-1.522385432354724</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.514306692650401</v>
+        <v>-1.541561609311287</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.885175622016121</v>
+        <v>-1.912228744689479</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.966683305398043</v>
+        <v>-1.993476563098177</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.348779912071045</v>
+        <v>-2.375094764488793</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.141156064826959</v>
+        <v>-2.16842682507172</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.95832676700023</v>
+        <v>-1.986041774497849</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.790254671904925</v>
+        <v>-1.818617843558989</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.677720448477103</v>
+        <v>-1.705983889528191</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.533648658736034</v>
+        <v>-1.562246440992723</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.233327703053092</v>
+        <v>-1.26250886454968</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.119386157025424</v>
+        <v>-1.148668203546798</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.246295512277726</v>
+        <v>-1.275286512249089</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.366125895873481</v>
+        <v>-1.370462519070358</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.35740694643566</v>
+        <v>-1.336969309046083</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.523700501462116</v>
+        <v>-1.50321099925555</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.599641840730584</v>
+        <v>-1.554425799457135</v>
       </c>
     </row>
     <row r="25">
@@ -7386,325 +7386,325 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.219647929899651</v>
+        <v>-1.229779919756083</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8607820689099697</v>
+        <v>-0.8716302383930881</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.170075038997901</v>
+        <v>-1.181048024103916</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9903769045709723</v>
+        <v>-1.001943240643328</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.056212742809485</v>
+        <v>-1.078381118677683</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.005711419076839</v>
+        <v>-1.027896514230157</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9232858112695155</v>
+        <v>-0.9459436431472596</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.100137210980023</v>
+        <v>-1.122648379098337</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.036265236729328</v>
+        <v>-1.058876132545947</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.152049580615355</v>
+        <v>-1.174820282171929</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.331993737024497</v>
+        <v>-1.354378818737267</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.628376593585337</v>
+        <v>-1.650425335552242</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.537075849448854</v>
+        <v>-1.559762432465867</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.576293071944256</v>
+        <v>-1.599027602402671</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.41599703168739</v>
+        <v>-1.439282619779867</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.11615078020769</v>
+        <v>-1.139677088981259</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.067605853213941</v>
+        <v>-1.091283159975951</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.8303789952202365</v>
+        <v>-0.8544953994331479</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.7901139710590215</v>
+        <v>-0.8142194805267096</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9386218587953721</v>
+        <v>-0.9624280935180423</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.139269842357891</v>
+        <v>-1.163004823425872</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.175320668152132</v>
+        <v>-1.175604368348665</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.475867324106545</v>
+        <v>-1.475791336336862</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.511888503694372</v>
+        <v>-1.488530712136857</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 67.65</t>
+          <t>X &lt; 67.64</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8255456936068626</v>
+        <v>-0.833960885887052</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7284570253819993</v>
+        <v>-0.7371364539008383</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.060400235193939</v>
+        <v>-1.069073672423265</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.078362930319827</v>
+        <v>-1.087256403260383</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.197730152368131</v>
+        <v>-1.215011140958708</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.177546263983835</v>
+        <v>-1.194806343570804</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.140809334578165</v>
+        <v>-1.158397707534995</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.435909281612261</v>
+        <v>-1.453161132684663</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.260575018331856</v>
+        <v>-1.278088207428127</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.9978966173059121</v>
+        <v>-1.016078608959923</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.115889968935605</v>
+        <v>-1.133814259329739</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.411267505546768</v>
+        <v>-1.428854855566918</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.271934137014398</v>
+        <v>-1.290124875507544</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.358457830266886</v>
+        <v>-1.376606257842781</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.317269717070346</v>
+        <v>-1.335716698261479</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.00158513666085</v>
+        <v>-1.020317970826063</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.925068911989392</v>
+        <v>-0.9439755524575801</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.007891590766505</v>
+        <v>-1.026722230457963</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.033741908827977</v>
+        <v>-1.052473000030986</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.277604756511899</v>
+        <v>-1.295917393444199</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.383457206581035</v>
+        <v>-1.401808282290261</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.550634497507964</v>
+        <v>-1.568772140528758</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.745079466714742</v>
+        <v>-1.762842583666156</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.761295172398547</v>
+        <v>-1.779072423732465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 69.91</t>
+          <t>X &lt; 69.9</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.83382129856966</v>
+        <v>-0.8739781380660219</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5782747617103539</v>
+        <v>-0.6184810546389201</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.819036712332526</v>
+        <v>-0.858444675710949</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9768107262867147</v>
+        <v>-0.9800637422283529</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9287760462047316</v>
+        <v>-0.9743645711438731</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.258576614144069</v>
+        <v>-1.304033569995823</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.367252871777922</v>
+        <v>-1.376529163475901</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.590024383653947</v>
+        <v>-1.599024487689562</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.564344115025584</v>
+        <v>-1.573388878668645</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.457969326344397</v>
+        <v>-1.466752009814464</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.450133305314871</v>
+        <v>-1.459052002951836</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.529657573416536</v>
+        <v>-1.538402159717265</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.342128801571441</v>
+        <v>-1.386367633711771</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.14786761797324</v>
+        <v>-1.192167279855667</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.247255822525474</v>
+        <v>-1.291209833512937</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.026158813825283</v>
+        <v>-1.070558419804655</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.7799029100458981</v>
+        <v>-0.8244399594572016</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.8996622856550545</v>
+        <v>-0.9440869944036692</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.9500337272996831</v>
+        <v>-0.9945397141562822</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.209532374100718</v>
+        <v>-1.253956296813911</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.551881589278636</v>
+        <v>-1.559878314717814</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.642823571192039</v>
+        <v>-1.65072845401437</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.743146952821739</v>
+        <v>-1.78709455430851</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.726157372297223</v>
+        <v>-1.770103718805295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 72.17</t>
+          <t>X &lt; 72.16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2910</v>
+        <v>2914</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7931122001592499</v>
+        <v>-0.7978100007319355</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.9056134278985368</v>
+        <v>-0.9102288164139338</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.030710110513333</v>
+        <v>-1.035448752976315</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.111596158425272</v>
+        <v>-1.116372031380259</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.048374583074022</v>
+        <v>-1.058364268350012</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.183792044555069</v>
+        <v>-1.193565877892311</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.391179152411915</v>
+        <v>-1.400832932513197</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.445631753210954</v>
+        <v>-1.455274228113332</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.487552718993769</v>
+        <v>-1.49713620728869</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.558288523790814</v>
+        <v>-1.567938851219253</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.606691368386315</v>
+        <v>-1.616226639519148</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.524305605414433</v>
+        <v>-1.534016807284381</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.328493823208674</v>
+        <v>-1.338707871458965</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9820679739606177</v>
+        <v>-0.9928078991209617</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.107085834894143</v>
+        <v>-1.117795831427848</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.005847901769314</v>
+        <v>-1.016582664426608</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8799027745447319</v>
+        <v>-0.890844507222198</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.9304303330378474</v>
+        <v>-0.9413315228243917</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.002867123236214</v>
+        <v>-1.013632288769649</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.173215511324642</v>
+        <v>-1.183716248801346</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.421804940408876</v>
+        <v>-1.432082779684485</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.477671948157045</v>
+        <v>-1.487895757208854</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.560671950511576</v>
+        <v>-1.570732806650717</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.685356001688064</v>
+        <v>-1.695268250598147</v>
       </c>
     </row>
     <row r="29">
@@ -7714,571 +7714,571 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3012</v>
+        <v>3016</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7581411751082925</v>
+        <v>-0.7616105224480876</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7133180146601106</v>
+        <v>-0.7169010678054804</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7836495440592302</v>
+        <v>-0.7873670306185048</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7868012517641247</v>
+        <v>-0.7906286008088728</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7378922213985675</v>
+        <v>-0.7457482435770828</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8953513152362262</v>
+        <v>-0.9029756503573552</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9896286243934469</v>
+        <v>-0.9972545532993493</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.216623120183684</v>
+        <v>-1.223998281892371</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.288692884851478</v>
+        <v>-1.295971481662434</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.250875252759904</v>
+        <v>-1.258330021483822</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.354408957300684</v>
+        <v>-1.361689105017504</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.184926184926184</v>
+        <v>-1.192479043094878</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.033550898469748</v>
+        <v>-1.041485437467458</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6400101876810069</v>
+        <v>-0.6485050355663375</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6505352008092657</v>
+        <v>-0.6591252139540131</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6318050800961217</v>
+        <v>-0.6403318903318862</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5807688356003879</v>
+        <v>-0.5893898261583956</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6661722600764364</v>
+        <v>-0.6747023286954956</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7619112135853001</v>
+        <v>-0.7702860379791048</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.9864058355437706</v>
+        <v>-0.9944593414575778</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.145397755598282</v>
+        <v>-1.153331690848539</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.168674376385745</v>
+        <v>-1.176594838441623</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.173080928759163</v>
+        <v>-1.180957542296809</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.362386710468066</v>
+        <v>-1.370029623937128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 76.7</t>
+          <t>X &lt; 76.69</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3088</v>
+        <v>3091</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.636512919733434</v>
+        <v>-0.6543345893471866</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5687824509417538</v>
+        <v>-0.5866100987396976</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7368712989232051</v>
+        <v>-0.754259927393754</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5643350992188161</v>
+        <v>-0.5817560930809762</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7185979786752839</v>
+        <v>-0.7389147839924917</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7710310918423602</v>
+        <v>-0.7913427848784451</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8174657054494077</v>
+        <v>-0.837588740814553</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.045667162728186</v>
+        <v>-1.065523461650727</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.147126718239051</v>
+        <v>-1.16690168284817</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.064674677730601</v>
+        <v>-1.084385090758865</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.0621438655281</v>
+        <v>-1.081919319473648</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.8390480487254663</v>
+        <v>-0.8589925930705817</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5575081853860056</v>
+        <v>-0.5775116209010136</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2434562315196231</v>
+        <v>-0.2637284044431496</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3343436338028525</v>
+        <v>-0.3544064722851274</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3982629749230355</v>
+        <v>-0.418390096512077</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4163176296944471</v>
+        <v>-0.4364094585143405</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4698282384488195</v>
+        <v>-0.4898561666467387</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6225028968166768</v>
+        <v>-0.6424342306048914</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6751293661060771</v>
+        <v>-0.6950552609602951</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7787633336178104</v>
+        <v>-0.7984900319131896</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.9003043319544801</v>
+        <v>-0.9199067098578055</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8977551767599223</v>
+        <v>-0.9174228760823695</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.051798321364728</v>
+        <v>-1.071310059049935</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 78.96</t>
+          <t>X &lt; 78.95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3182</v>
+        <v>3186</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5383959767336393</v>
+        <v>-0.5401927039586099</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6072994172740209</v>
+        <v>-0.6090403706346521</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8127188955646147</v>
+        <v>-0.8143289601891368</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6349955696294387</v>
+        <v>-0.6368901805050413</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8267171524891594</v>
+        <v>-0.830562179791869</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9658958696916784</v>
+        <v>-0.9695536012871813</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8774381505422113</v>
+        <v>-0.8812756639894559</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.9507906935431976</v>
+        <v>-0.9545632816698841</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9541787492732254</v>
+        <v>-0.9579461347087275</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8968512620974138</v>
+        <v>-0.9007598894706206</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8549715615764697</v>
+        <v>-0.8589114851955344</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7092078241107629</v>
+        <v>-0.7133569365603165</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5629755340463092</v>
+        <v>-0.5674078546162491</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4526622679146826</v>
+        <v>-0.4572547367377524</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4036578891547435</v>
+        <v>-0.4083718415617099</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4481807573989514</v>
+        <v>-0.4527902696343489</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4383136772954828</v>
+        <v>-0.4429501542785772</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.493348890798174</v>
+        <v>-0.4979284947061586</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6351533029941407</v>
+        <v>-0.6395392992046354</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4923885750156884</v>
+        <v>-0.4969401901361863</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5775410683386113</v>
+        <v>-0.5820361299963892</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6662660174043822</v>
+        <v>-0.6706593098315992</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6870208887961979</v>
+        <v>-0.6913670728942236</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7444102609341243</v>
+        <v>-0.7486939061665723</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 81.22</t>
+          <t>X &lt; 81.21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3224</v>
+        <v>3228</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.6713496164067934</v>
+        <v>-0.6725296726445151</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.6205107219970927</v>
+        <v>-0.6217777579356323</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8110929160683114</v>
+        <v>-0.8122271405603882</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7682160984142428</v>
+        <v>-0.7694541231126522</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8697194404536361</v>
+        <v>-0.8726122757162429</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9429933403887816</v>
+        <v>-0.945784791043053</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8965450933840913</v>
+        <v>-0.8994500738623259</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.003427758375381</v>
+        <v>-1.006222579072634</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.9136286155852602</v>
+        <v>-0.9165333130332698</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9288361165441046</v>
+        <v>-0.9317785507907956</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.9766282859822226</v>
+        <v>-0.9794945237665829</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.929123410582001</v>
+        <v>-0.9320700211270605</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7994569019535973</v>
+        <v>-0.8026449840530674</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7244456224048008</v>
+        <v>-0.7277441765177102</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.6228600742362573</v>
+        <v>-0.6263328876239029</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.6281987591991367</v>
+        <v>-0.6316252762482648</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.6202587513706206</v>
+        <v>-0.6237068423776932</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.6450400235677236</v>
+        <v>-0.6484671790794252</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6893277844714731</v>
+        <v>-0.6926871536665686</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.6079615861214407</v>
+        <v>-0.6114106889101976</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.575157334935362</v>
+        <v>-0.5786878049013993</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.632717150939385</v>
+        <v>-0.6361840523839817</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6806206082359552</v>
+        <v>-0.6840110042882301</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7692670468561786</v>
+        <v>-0.772555269893104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 83.49</t>
+          <t>X &lt; 83.48</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4380229554317481</v>
+        <v>-0.4532332700804247</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4226707805774979</v>
+        <v>-0.4074489952922633</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5386903002611376</v>
+        <v>-0.5533756461104673</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5362700164092189</v>
+        <v>-0.5507841574053103</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.6412335888743073</v>
+        <v>-0.6569163281827244</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7718149202090245</v>
+        <v>-0.7874309961064441</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.7058472376665605</v>
+        <v>-0.7213358873354139</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.784521275766096</v>
+        <v>-0.799874063435233</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.725762507310165</v>
+        <v>-0.7411849012004197</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6901448290866199</v>
+        <v>-0.6749703156502207</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7030655098030749</v>
+        <v>-0.7183948270894547</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.598882824492577</v>
+        <v>-0.6142430561785659</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.516441902752554</v>
+        <v>-0.531601510422071</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5063351933643574</v>
+        <v>-0.5214541569975353</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4759259125769688</v>
+        <v>-0.4604253550545891</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4426307518489452</v>
+        <v>-0.4578030996146225</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4365423210829249</v>
+        <v>-0.4516922030746855</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4318016561698386</v>
+        <v>-0.4469351278590707</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3808644494548332</v>
+        <v>-0.3961043331121985</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.3285452322738394</v>
+        <v>-0.3438855585345735</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.272832020126053</v>
+        <v>-0.288092742975536</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.269384822438731</v>
+        <v>-0.2846352607413181</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2822435590945034</v>
+        <v>-0.2975567968875552</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3705970352237173</v>
+        <v>-0.3858158069926318</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 85.75</t>
+          <t>X &lt; 85.74</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3310</v>
+        <v>3314</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3287868722974494</v>
+        <v>-0.3294896066893855</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3478323345607919</v>
+        <v>-0.3485255904388538</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4805194499270797</v>
+        <v>-0.4811092276793332</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.487115021998747</v>
+        <v>-0.487724754700622</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.5653089056483012</v>
+        <v>-0.5667978938468963</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.5716651004609048</v>
+        <v>-0.5731403543404667</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5162266846432075</v>
+        <v>-0.5177992511061191</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.567301614191507</v>
+        <v>-0.5688246385920763</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.508695319083742</v>
+        <v>-0.51028826570208</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.453155848606734</v>
+        <v>-0.4548464279321607</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4623742281527186</v>
+        <v>-0.4640443260583211</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3930671977029618</v>
+        <v>-0.3948325431198967</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3559395353013102</v>
+        <v>-0.3577940484398852</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4390740805788695</v>
+        <v>-0.4408383076574722</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4173677346272271</v>
+        <v>-0.4191847041587664</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3769439773014156</v>
+        <v>-0.3787878787878753</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3424630118570207</v>
+        <v>-0.3443548474151896</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3692405411819237</v>
+        <v>-0.3711054129052584</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.346357521110626</v>
+        <v>-0.3482428510838034</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2319704284852193</v>
+        <v>-0.2339876617973644</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1536365695774862</v>
+        <v>-0.1557705708071708</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1511602955584408</v>
+        <v>-0.1533015463245988</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1905370483849538</v>
+        <v>-0.1926214618357136</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2787053232275056</v>
+        <v>-0.280687567329764</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 88.01</t>
+          <t>X &lt; 88</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3330</v>
+        <v>3334</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2592690347397593</v>
+        <v>-0.2598521774772493</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.280179975287723</v>
+        <v>-0.2807490607686702</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4504894763941252</v>
+        <v>-0.4509007849558486</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4612981603609825</v>
+        <v>-0.4617192223545032</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.5710583925222963</v>
+        <v>-0.5721399132859375</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5762602663463952</v>
+        <v>-0.5773305745813033</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4361402509240762</v>
+        <v>-0.4374027766178443</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4287780937675478</v>
+        <v>-0.430059007289131</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3702325702834912</v>
+        <v>-0.371583016061777</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3196120695660838</v>
+        <v>-0.321048121250783</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3270939559286319</v>
+        <v>-0.3285134382259329</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2598314312856544</v>
+        <v>-0.2613410135779759</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2296176096057465</v>
+        <v>-0.2311995352510792</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3135420121855432</v>
+        <v>-0.3150315031503084</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2958749653148729</v>
+        <v>-0.2974072538894319</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3419658219449531</v>
+        <v>-0.3434252761003265</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3084847111713813</v>
+        <v>-0.3099894433999708</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3357209153867871</v>
+        <v>-0.3371973254656879</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3416539905229783</v>
+        <v>-0.3431174876725294</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2568236352729372</v>
+        <v>-0.2583838868291508</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1522238113381889</v>
+        <v>-0.1539275574224632</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1202058848086338</v>
+        <v>-0.1219514755971147</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09764508350818346</v>
+        <v>-0.09941014894012312</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.1556819977872621</v>
+        <v>-0.157380906996174</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_21.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_21.xlsx
@@ -622,2375 +622,2375 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01679749960251797</v>
+        <v>0.3007713317529266</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.739288469885686</v>
+        <v>0.05684100957873284</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.593035361420881</v>
+        <v>-6.286236900724646</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.03110807092733836</v>
+        <v>0.7692115130134312</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.640428614755585</v>
+        <v>-7.153495379150328</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.604985877919965</v>
+        <v>-4.449240315127604</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.9473305477588241</v>
+        <v>-0.1398117229061953</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.203357616995213</v>
+        <v>-0.4427608102958089</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.528750236127422</v>
+        <v>7.342198859543224</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.04825313346637</v>
+        <v>14.21208664300555</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.32598114734093</v>
+        <v>14.48776005591201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.05246475335613</v>
+        <v>14.21614005460036</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13.93774088649685</v>
+        <v>13.10934954059015</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.2898898584355</v>
+        <v>10.30937100362187</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>8.2047896495286</v>
+        <v>7.075169081747738</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.93389164553686</v>
+        <v>2.521158939114343</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-8.367482929004744</v>
+        <v>-10.37520422472566</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-10.90919530158192</v>
+        <v>-13.07053466477893</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-10.69680960396663</v>
+        <v>-12.86015642310454</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-3.204977712709223</v>
+        <v>-4.966583095616151</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.125770623501211</v>
+        <v>-0.4113196543707147</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>5.925584528686976</v>
+        <v>4.638583699549947</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>3.763671194123866</v>
+        <v>2.32030734101334</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>1.250142466377383</v>
+        <v>-0.4051713242788963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 25.79</t>
+          <t>X ≈ 25.74</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.293558427332925</v>
+        <v>-5.291756822227988</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2713662053236021</v>
+        <v>-1.989822100506601</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.819403939566399</v>
+        <v>2.085926675690267</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.632588872579859</v>
+        <v>5.046864023199646</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.82475535632641</v>
+        <v>8.325296430365938</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15.85645353384008</v>
+        <v>13.81150061444963</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.93539714772994</v>
+        <v>11.24772515592619</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.66424840726886</v>
+        <v>14.50230770753566</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>16.71008047203937</v>
+        <v>12.85615329734602</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15.94579583279398</v>
+        <v>13.84560002784355</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>18.06835600723478</v>
+        <v>12.34263316203818</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.64085242742925</v>
+        <v>15.62884451560544</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22.2189551184069</v>
+        <v>16.30243520839812</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>18.31322439832329</v>
+        <v>14.27980102109526</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>15.81618502589547</v>
+        <v>15.3850147588384</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>18.26132401288118</v>
+        <v>17.73092926772851</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>16.28613779724974</v>
+        <v>17.63310003665932</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>14.33817272239568</v>
+        <v>15.72334518498805</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>12.70924096623911</v>
+        <v>14.15943339818864</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>16.59902354308744</v>
+        <v>17.94505617209532</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>17.91234451753041</v>
+        <v>19.16775433091264</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>15.99152018727293</v>
+        <v>17.31387875601137</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>16.27106252809931</v>
+        <v>17.56286654427394</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.49675493250218</v>
+        <v>13.83475541564884</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 28.05</t>
+          <t>X ≈ 27.97</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.95612987617563</v>
+        <v>-6.659170671779016</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.291503744355992</v>
+        <v>-5.64844009395366</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.407209939458255</v>
+        <v>-11.9271140820797</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.777164172969123</v>
+        <v>-11.26252626133067</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.770691370146643</v>
+        <v>-7.765221813722221</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.556315473151251</v>
+        <v>-3.836124716632341</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.669601189891914</v>
+        <v>-4.628464850662354</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.808861903670945</v>
+        <v>3.883537548945675</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.54109485289186</v>
+        <v>5.271783089611311</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.465073768583437</v>
+        <v>7.001514895045574</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.357889163228066</v>
+        <v>3.49327750524477</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.773682689024881</v>
+        <v>5.740476282476259</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.73678556423605</v>
+        <v>14.7232403935929</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.86828499148386</v>
+        <v>15.74257309712275</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>12.86976404505945</v>
+        <v>13.80537907009974</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>8.074970345972886</v>
+        <v>10.5815623213706</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>14.68661089186236</v>
+        <v>15.53393256688762</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.88925276992596</v>
+        <v>15.40624950080655</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>9.410323478310126</v>
+        <v>13.09778726968086</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.29929657154416</v>
+        <v>15.84458203962522</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>13.11139600120847</v>
+        <v>16.5474065924021</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>8.98852206164775</v>
+        <v>12.68251402562677</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>11.96790638363481</v>
+        <v>15.46112530677531</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>14.59885703460501</v>
+        <v>17.83565957478014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 30.31</t>
+          <t>X ≈ 30.2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.131492333845472</v>
+        <v>0.8823461242292723</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.189111876698519</v>
+        <v>-3.132644039617404</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-11.58530982150275</v>
+        <v>-8.151207112559142</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.331232866568328</v>
+        <v>-4.970414548216311</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-11.39487042177088</v>
+        <v>-10.27920927707392</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.728024065432081</v>
+        <v>-10.1277783331623</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.012235180181243</v>
+        <v>-8.404134784677581</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.291924608808195</v>
+        <v>-6.192228698724058</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.497765850683109</v>
+        <v>-6.067228505940001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.536685014252882</v>
+        <v>-5.601570120489008</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.693249404022701</v>
+        <v>6.013553373968669</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.171358369691845</v>
+        <v>4.478313393090303</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4382066121382238</v>
+        <v>0.8456635288760381</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.833711244695017</v>
+        <v>3.122388758516287</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.657127691728</v>
+        <v>8.754675153054286</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8.00643734088473</v>
+        <v>8.055002223304612</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.640187270674872</v>
+        <v>1.639423664908691</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.774440261014519</v>
+        <v>7.824445834910222</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>6.744924192043818</v>
+        <v>6.777776490847884</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.933802804307689</v>
+        <v>8.25837285542552</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.896719235668279</v>
+        <v>5.165179731518123</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.570208786771921</v>
+        <v>8.887065055656869</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>9.097011680546316</v>
+        <v>9.133793333298691</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>9.024532710280376</v>
+        <v>8.974900081109844</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 32.57</t>
+          <t>X ≈ 32.42</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.039909031076327</v>
+        <v>-5.308435253431995</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.618395010920665</v>
+        <v>-6.750037406585555</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.583750936311752</v>
+        <v>-6.800234088055468</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.300049936317251</v>
+        <v>-4.99899543725904</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.881971010646581</v>
+        <v>-6.4718341570237</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-7.482958384914369</v>
+        <v>-7.51712949980945</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.767406734361622</v>
+        <v>-5.914640144531674</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.04676238244334</v>
+        <v>-6.221017172888445</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.739632559941199</v>
+        <v>-10.89165697427521</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.02401460019761</v>
+        <v>-6.890738955408146</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-8.998784411679033</v>
+        <v>-7.821949171672976</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.789765500619197</v>
+        <v>-5.70044249637013</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.174707004420881</v>
+        <v>-3.211893696201351</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.641962289566479</v>
+        <v>-4.66100537327732</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.177994929066962</v>
+        <v>0.663817000997291</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.968278394365171</v>
+        <v>-2.380701124545467</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3927630410515874</v>
+        <v>-0.08023622242097872</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.535985665012475</v>
+        <v>0.9894775849422928</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.000488318108239</v>
+        <v>2.407362360295529</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.436568928543302</v>
+        <v>2.622374933068272</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.896452375202315</v>
+        <v>2.056769319539967</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>6.320737874141535</v>
+        <v>5.594714718551835</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>7.847249030755066</v>
+        <v>7.044940415792063</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.524532710280376</v>
+        <v>8.090349219434735</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 34.83</t>
+          <t>X ≈ 34.65</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.469930898864725</v>
+        <v>3.854992421119483</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.629527489735899</v>
+        <v>-1.300601133638246</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.175434755132606</v>
+        <v>4.336036842150705</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.06530571580311317</v>
+        <v>-0.1866545836482061</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.452364787817615</v>
+        <v>-8.329954899926101</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.437781426261758</v>
+        <v>-1.290034161204922</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.664760607171544</v>
+        <v>-4.050616929728257</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.908675018527617</v>
+        <v>-3.371745330401339</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.834995671707595</v>
+        <v>-5.215542613106741</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.606412591169629</v>
+        <v>-6.010378228560398</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.36931017618555</v>
+        <v>-5.741721269068989</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.152078482548866</v>
+        <v>-0.1037208765946005</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.868338811655867</v>
+        <v>-5.160389862063063</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.121658034454512</v>
+        <v>-3.435768242032658</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-3.746552423320971</v>
+        <v>-5.104252872797296</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.654988341451642</v>
+        <v>1.378756304273431</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.586242643549916</v>
+        <v>0.2885627625491196</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4868815892873215</v>
+        <v>-0.8321560397396297</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.667395557053588</v>
+        <v>1.359072097083939</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.8851524054679132</v>
+        <v>1.573753086006171</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.313837549581777</v>
+        <v>1.996987739727885</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.209168906156783</v>
+        <v>1.922842994919662</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.5437440117874175</v>
+        <v>2.167516692110681</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.381328826785236</v>
+        <v>4.976905344927296</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 37.09</t>
+          <t>X ≈ 36.88</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.3490245146074</v>
+        <v>-4.762724612396902</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.922842499164631</v>
+        <v>-10.84278902296109</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.104971094625675</v>
+        <v>-5.419055332092221</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.417369719305292</v>
+        <v>-3.507386851517381</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.448241679117515</v>
+        <v>-2.945606876735425</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.565778308945724</v>
+        <v>-3.628925424171328</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.731839087054368</v>
+        <v>-4.420934457967491</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.762021474586383</v>
+        <v>-3.056034320162432</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.721661892774335</v>
+        <v>-2.093542567274319</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.7909970612864115</v>
+        <v>-1.214857873398842</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.182307232925915</v>
+        <v>1.564589101883087</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.754489421334306</v>
+        <v>1.2878912637863</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.042012387056175</v>
+        <v>3.526282686358464</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.378448938094053</v>
+        <v>4.11761069165474</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.168824754675263</v>
+        <v>1.763745852644931</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>2.058353737487444</v>
+        <v>1.486095256504271</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>7.04216671449656</v>
+        <v>4.736836229992463</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.823165732749601</v>
+        <v>0.4131596657101824</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.892907158569301</v>
+        <v>2.305570238399056</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.373775483329723</v>
+        <v>0.8423195096845433</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.8747273126932384</v>
+        <v>-1.402575934580788</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.9503343425777473</v>
+        <v>-0.6381164725288286</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.23887897903974</v>
+        <v>-3.754420202310669</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.315210879463216</v>
+        <v>-3.917345424687703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 39.36</t>
+          <t>X ≈ 39.1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.899940056755199</v>
+        <v>-7.07863983856646</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.067031180049057</v>
+        <v>-0.1794887701806687</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-7.201743288354479</v>
+        <v>-3.807487884437627</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.084419656770962</v>
+        <v>-0.4287303170998058</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.763197744639683</v>
+        <v>-2.289217661373982</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.383036878388126</v>
+        <v>1.835722311604002</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.171282982202335</v>
+        <v>0.2510683091646797</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-4.122504973253136</v>
+        <v>-0.8492136818441978</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.406774727013548</v>
+        <v>1.664547872544986</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.866639175552962</v>
+        <v>-1.515351594448944</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-8.288952409623334</v>
+        <v>-5.226761987767425</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.60090476918874</v>
+        <v>-6.302425845460391</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-11.24547255606341</v>
+        <v>-7.415178964666858</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.63265459644172</v>
+        <v>-6.071156566407787</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-12.1295576905227</v>
+        <v>-6.752959760338626</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-10.70323923910261</v>
+        <v>-6.99344081566845</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-13.35430728397414</v>
+        <v>-9.492789005011161</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-12.62456233873176</v>
+        <v>-7.233861671255113</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-11.57464302574019</v>
+        <v>-7.82059775125218</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-11.39204978562723</v>
+        <v>-7.609202728721854</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-11.93755064414801</v>
+        <v>-8.178167521801349</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-13.69669541930944</v>
+        <v>-10.65421932373921</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-13.42678234538644</v>
+        <v>-10.41404569443495</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-12.66664376030786</v>
+        <v>-9.779530298637283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 41.62</t>
+          <t>X ≈ 41.33</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.767427673337032</v>
+        <v>-4.77457968372714</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.022761225168225</v>
+        <v>-8.195705010907865</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.034399404682574</v>
+        <v>-1.179243696912245</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.616287817945526</v>
+        <v>-7.494979097207533</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-8.623896463238651</v>
+        <v>-8.404780219504715</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-7.759702678758465</v>
+        <v>-6.3479886712447</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.951485299277223</v>
+        <v>-6.503339206074365</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.536854928040334</v>
+        <v>-8.721763855919718</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.163591045181533</v>
+        <v>-6.686778584627916</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.531171040145686</v>
+        <v>-8.756407396228283</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.856466663865589</v>
+        <v>-11.04033080435741</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-14.6934145372252</v>
+        <v>-15.14991074170878</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-13.87852747592265</v>
+        <v>-14.35119841988573</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-15.67605599701855</v>
+        <v>-15.8814404374037</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-13.73994364364062</v>
+        <v>-15.28959158311518</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-12.49076508807347</v>
+        <v>-12.81918347853309</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-10.02389663619175</v>
+        <v>-11.0092259974239</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-8.829569386441456</v>
+        <v>-12.42511809568502</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-5.618532740285289</v>
+        <v>-9.01684221036242</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-5.703921808791655</v>
+        <v>-10.08629642198673</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-6.900296756336864</v>
+        <v>-11.29667561153497</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-8.284536988677814</v>
+        <v>-12.01648248156256</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-7.359629860310122</v>
+        <v>-11.7772346110559</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-7.437885590373213</v>
+        <v>-11.3026072217142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 43.88</t>
+          <t>X ≈ 43.55</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.966696541090052</v>
+        <v>0.9361442276487182</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.332732153258014</v>
+        <v>-0.7820591404841082</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-6.065229055304656</v>
+        <v>-4.989708188275493</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.304102397302799</v>
+        <v>-5.580203174650116</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.421825450612118</v>
+        <v>-2.89092570740479</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.942377390186635</v>
+        <v>-2.743325121851136</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.494522054071034</v>
+        <v>-2.05184216328022</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.85173630812367</v>
+        <v>-6.063485380606132</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.548227504742002</v>
+        <v>-8.165220405102637</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.10230411374814</v>
+        <v>-7.476031230178258</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.32003483194532</v>
+        <v>-7.950473924101857</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-9.8521693459735</v>
+        <v>-8.230260494217944</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.508011166651492</v>
+        <v>-6.372681971857709</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-9.734847717022944</v>
+        <v>-7.366042801368927</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-9.215190255956216</v>
+        <v>-7.305384123350457</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-6.653831386501871</v>
+        <v>-6.006211612573424</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-4.847140483530012</v>
+        <v>-2.391548427361563</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.003811844159336886</v>
+        <v>1.941266680025336</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-4.290042741331675</v>
+        <v>-2.312504073855635</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.599095690223329</v>
+        <v>-1.354468903074157</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.952157526561386</v>
+        <v>-0.4305414080445189</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.02837311658309</v>
+        <v>-1.251394058438379</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.512358153846584</v>
+        <v>-3.246039354014385</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-7.093888342351207</v>
+        <v>-4.901918358338776</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 46.14</t>
+          <t>X ≈ 45.77</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1359081101636193</v>
+        <v>-0.1638633332323636</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.438585869488726</v>
+        <v>2.377313888537778</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.45049602381853</v>
+        <v>-3.759630118121457</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.162658271354687</v>
+        <v>-3.737540960587808</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.405740092138387</v>
+        <v>-5.234026734245845</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.67579418190747</v>
+        <v>-3.251711616685007</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.446837983619275</v>
+        <v>-2.817257267415386</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6358663373436713</v>
+        <v>1.168849891246623</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.04125266533231553</v>
+        <v>3.134816666693233</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7304187977086087</v>
+        <v>-0.1088134760353938</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4566419312275869</v>
+        <v>-0.4517829306876706</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.279615271804694</v>
+        <v>-3.18453196648565</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-6.309785911216338</v>
+        <v>-5.525249363920992</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.350217257866241</v>
+        <v>-3.931583990654325</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-4.00762533867649</v>
+        <v>-3.99831088511359</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-7.231044755967929</v>
+        <v>-7.747873111277869</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-6.092623703835919</v>
+        <v>-7.239980707693036</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-6.197634073065757</v>
+        <v>-7.376489296791561</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-5.34611087138029</v>
+        <v>-5.933821233013845</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-5.795971429760463</v>
+        <v>-5.722714630167644</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.701528453697691</v>
+        <v>-6.291430179103401</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-3.870366903309275</v>
+        <v>-3.902320872924172</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.960693367407586</v>
+        <v>-3.660286874341132</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-4.311454550866124</v>
+        <v>-5.675826594933575</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 48.41</t>
+          <t>X ≈ 48</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.999993906796441</v>
+        <v>1.774712684689369</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.967894068983064</v>
+        <v>1.530870737565813</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.626955468285651</v>
+        <v>3.109648117535869</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5183201638509516</v>
+        <v>0.09482872725134683</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.468465605225418</v>
+        <v>4.780389438669289</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.558739545263187</v>
+        <v>2.094975790253727</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.787826067437187</v>
+        <v>2.723685380676756</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.81138577791392</v>
+        <v>2.420041824255534</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.852290656417594</v>
+        <v>2.545993483998707</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.175679024166413</v>
+        <v>3.886416094305417</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.354534528986072</v>
+        <v>2.029530113018481</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.377879782663314</v>
+        <v>1.044640066581984</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.351215860729582</v>
+        <v>-1.485785303585914</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7334851936058655</v>
+        <v>1.108866026775232</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7744765461016456</v>
+        <v>-0.2815681041645419</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.7271170738457329</v>
+        <v>-2.569644515460944</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.257556600742284</v>
+        <v>-2.67529091269104</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2677107702535366</v>
+        <v>0.03880449284829979</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.845575873336458</v>
+        <v>-3.310397632475279</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-5.452551247754698</v>
+        <v>-5.237292289372974</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-6.69242045518461</v>
+        <v>-6.519218637306004</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-6.072648858952611</v>
+        <v>-5.88409071232924</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-5.800921599749294</v>
+        <v>-5.643238457189</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-6.578614142866478</v>
+        <v>-7.236673155780139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 50.67</t>
+          <t>X ≈ 50.23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.686983534417564</v>
+        <v>4.488426898037012</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1931751228816267</v>
+        <v>0.7597130677266932</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.304418719497946</v>
+        <v>1.99624788984142</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.979393146464652</v>
+        <v>4.896841715491668</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.644419720580707</v>
+        <v>4.627681493737512</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.52289898989234</v>
+        <v>6.170757361774392</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.978658707714679</v>
+        <v>1.894091589531229</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.393965824349976</v>
+        <v>2.288682003245</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.821524528438893</v>
+        <v>3.113112169040534</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.823500144619068</v>
+        <v>7.219689448570747</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4.017301210493805</v>
+        <v>5.396468455988177</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2722217085845742</v>
+        <v>1.624550519485069</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.391023802100172</v>
+        <v>7.519442218563505</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.396539172825484</v>
+        <v>2.369796076718309</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.045917191428295</v>
+        <v>2.392846379311983</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2525242209005683</v>
+        <v>2.952690004065502</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.198939937179645</v>
+        <v>3.551317548251752</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.373196465704993</v>
+        <v>0.610560484174627</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.157676469627809</v>
+        <v>1.52745529888012</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.358016336375101</v>
+        <v>1.038920922353341</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8192640504821966</v>
+        <v>3.285934699492032</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.589314179504228</v>
+        <v>1.804970915870207</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.397937213406529</v>
+        <v>-0.06221443430600715</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.086578400830575</v>
+        <v>1.183849983052852</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 52.93</t>
+          <t>X ≈ 52.45</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>6.62833298678769</v>
+        <v>6.269452169489909</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>9.314852172038506</v>
+        <v>8.554948597384012</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.844105566099451</v>
+        <v>5.424691020421285</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.78674151328421</v>
+        <v>6.098272526695766</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>6.210518002268394</v>
+        <v>3.940123692693923</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9556965423962396</v>
+        <v>2.192961426991964</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.810928862585875</v>
+        <v>3.932322513836404</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.110955580652053</v>
+        <v>1.104140256468476</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.87164760562014</v>
+        <v>-0.6666430029595745</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.437619904983379</v>
+        <v>-1.457878370988325</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.04693960332549096</v>
+        <v>-0.5533115473783567</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2348582196712172</v>
+        <v>-1.459314890272111</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.572076642147479</v>
+        <v>-1.937643824461034</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.610556545069819</v>
+        <v>-4.085925343536623</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.45587144549777</v>
+        <v>-3.499504647766081</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.647682202896746</v>
+        <v>-2.309086547549271</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.203107142092577</v>
+        <v>-3.684068034348719</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.886186008733013</v>
+        <v>-2.55026635289601</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.7524833492217127</v>
+        <v>0.2029629838790754</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.481162503179235</v>
+        <v>-1.490033187238325</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.421634175101694</v>
+        <v>-3.328768208937475</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.6811042248765631</v>
+        <v>-2.769882967952377</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.8611945719459229</v>
+        <v>-3.800996489862506</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.8805933163408426</v>
+        <v>-1.417746859146838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 55.2</t>
+          <t>X ≈ 54.68</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.21724194993508</v>
+        <v>3.034170476524942</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.828377137081972</v>
+        <v>3.886181463907</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.871160767143138</v>
+        <v>3.187183041643799</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.132477024450843</v>
+        <v>6.966069093279167</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.620069797461575</v>
+        <v>1.003863483890534</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.916534858460544</v>
+        <v>-0.4931464748584204</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.616790469338717</v>
+        <v>-4.012764715517228</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.921209558796633</v>
+        <v>-3.771081937424285</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.29074366878325</v>
+        <v>-5.838693843653196</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-11.01674015214631</v>
+        <v>-9.370661674504127</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.767454390323195</v>
+        <v>-8.007679267896691</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.02405848143663</v>
+        <v>-6.63934629953382</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-12.15080495920779</v>
+        <v>-9.948468933765376</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.448834044675195</v>
+        <v>-9.651392979650261</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-10.10936694953232</v>
+        <v>-10.33631449395195</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-10.97411531580233</v>
+        <v>-9.235813031476418</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-10.62149471622381</v>
+        <v>-10.44632821379336</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.800179139606065</v>
+        <v>-7.284804441106715</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-9.044617850532987</v>
+        <v>-9.279345944292778</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-6.420304143231292</v>
+        <v>-9.622588673014278</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-5.990730680995718</v>
+        <v>-7.988505404736856</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.015595117361272</v>
+        <v>-6.413882899707446</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.399585855887878</v>
+        <v>-8.935065691948594</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.042540460451328</v>
+        <v>-6.34085626548805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 57.46</t>
+          <t>X ≈ 56.91</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.844469481192121</v>
+        <v>-0.2380681582275912</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6413013961952103</v>
+        <v>0.9271538655052893</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.053171113006513</v>
+        <v>0.621658903113925</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.2837083285689559</v>
+        <v>1.43342956776668</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>6.098441531062583</v>
+        <v>6.784500018619624</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.185089609314005</v>
+        <v>-0.08769014684716581</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.43896466473872</v>
+        <v>0.9997165362577292</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.938681135690423</v>
+        <v>-1.648529327730699</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.897147440503559</v>
+        <v>-4.338732599335181</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.131932180104663</v>
+        <v>-3.724824138435864</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8580120777590565</v>
+        <v>-2.986532394071176</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.18589724314392</v>
+        <v>-7.496655832670839</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.820808347855028</v>
+        <v>-7.203920498363537</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.504453986947929</v>
+        <v>-5.103533509663571</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.112345204061327</v>
+        <v>-3.905309301319839</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.518469928111386</v>
+        <v>-5.706601256676471</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.6273540513995073</v>
+        <v>-2.984742985636345</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.757599875086932</v>
+        <v>-3.120504044218976</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.541987573795176</v>
+        <v>-2.908952334303393</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.405161277933608</v>
+        <v>-2.696746295454965</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-3.434795576242188</v>
+        <v>-2.796621336531693</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.9733013268417</v>
+        <v>-4.767728574583771</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.69859404799918</v>
+        <v>-5.478745349899782</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-4.853672417924749</v>
+        <v>-6.298961578258186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.72</t>
+          <t>X ≈ 59.14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.652556455553928</v>
+        <v>-6.709463529651678</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.643468378761106</v>
+        <v>-1.084618080275256</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.373999152979003</v>
+        <v>-0.1920181385194297</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.520547417573276</v>
+        <v>-3.983901052301292</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.426704856783033</v>
+        <v>-1.053933308272754</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.410482744712724</v>
+        <v>0.4676509911194273</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.102605088129025</v>
+        <v>0.2219912346435038</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.385173865877348</v>
+        <v>-2.745948654603126</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.887561066013618</v>
+        <v>-2.08432794356829</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.839935482067972</v>
+        <v>-3.941524166336002</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.021209215492242</v>
+        <v>-4.745854282206267</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.676654017596562</v>
+        <v>-1.80243485168041</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.632240979876734</v>
+        <v>-2.376482912860233</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.765967213402774</v>
+        <v>-2.091645547737357</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.339530716332561</v>
+        <v>-1.700357321315749</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-4.91469950487253</v>
+        <v>-0.6092658003893447</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.962056241292224</v>
+        <v>-0.1800964655131452</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-4.606810115350434</v>
+        <v>-1.395543094807202</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.932020268207317</v>
+        <v>-1.18445202417189</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.570865293579736</v>
+        <v>0.6442922419888006</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.116976552178244</v>
+        <v>-0.4623905934321755</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.822068932651852</v>
+        <v>-1.080063115408393</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.919140043468062</v>
+        <v>2.404230317273807</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.029815115806578</v>
+        <v>1.161010241903263</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.98</t>
+          <t>X ≈ 61.36</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.695641633979996</v>
+        <v>-5.626137462847424</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.290692404932464</v>
+        <v>-3.094196327034439</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.673916933415434</v>
+        <v>-2.960009975083089</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7227180882376416</v>
+        <v>-2.857958144167497</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.982935398008344</v>
+        <v>-2.439066501559026</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.165832225609591</v>
+        <v>-4.365503478764886</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4868766247467846</v>
+        <v>-1.691249605358237</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.263459700541581</v>
+        <v>0.08604508811632172</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.674809896154912</v>
+        <v>0.2113311011212602</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.586825726967739</v>
+        <v>0.1046899675334032</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.80609084858164</v>
+        <v>3.164490925694551</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.582135965681665</v>
+        <v>3.580047728332104</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.883631433072118</v>
+        <v>5.252529380406635</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.977621049776218</v>
+        <v>7.102954602279887</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.004409259044969</v>
+        <v>7.119088068216335</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>6.968659194686595</v>
+        <v>6.288444180169662</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>7.519673564558516</v>
+        <v>4.788077365792446</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>6.044969847038615</v>
+        <v>2.558383913128935</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>6.260861227962941</v>
+        <v>2.07235667089455</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.338117996835088</v>
+        <v>-1.926897203942467</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.480503335718375</v>
+        <v>-0.4013201709402594</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.404657374309274</v>
+        <v>0.6658511746387958</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.364063593640559</v>
+        <v>-0.06246172688303631</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.918368326718735</v>
+        <v>0.4796246309401795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.25</t>
+          <t>X ≈ 63.59</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1522563348439689</v>
+        <v>-1.864597212296992</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.645065743390596</v>
+        <v>-0.2108251640281722</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.827736349531982</v>
+        <v>-2.071826694041057</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.114782330089319</v>
+        <v>-0.755577053364469</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.778991857542124</v>
+        <v>3.41939478016338</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.655613216053297</v>
+        <v>0.3952419870200785</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.021595566645544</v>
+        <v>3.427446945095625</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.43303929430634</v>
+        <v>5.04621781395975</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.853836821048617</v>
+        <v>6.453492623510392</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>10.90850735190861</v>
+        <v>8.866938388482083</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>9.113601476829309</v>
+        <v>4.674216356123495</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>10.21416241820883</v>
+        <v>5.686992526012794</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>8.401345178938918</v>
+        <v>4.582022195671989</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.731990440423345</v>
+        <v>1.131849437189601</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4.763502315256581</v>
+        <v>2.372877157174791</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.116509926854761</v>
+        <v>4.853806801909819</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>6.603282445049615</v>
+        <v>4.74983701808187</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>5.808786568814639</v>
+        <v>3.973584568799787</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.645367604911449</v>
+        <v>3.545595646531886</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>4.142558242465697</v>
+        <v>3.116606583386918</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.220701729672079</v>
+        <v>1.259298022651741</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.455200595849263</v>
+        <v>1.184135500696378</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.028945381323851</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.415122462133418</v>
+        <v>1.265630991685292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 66.51</t>
+          <t>X ≈ 65.81</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.218307816145497</v>
+        <v>3.004473793587437</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.658178905119662</v>
+        <v>4.775431169980813</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9243852082013149</v>
+        <v>2.88569479482269</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.605470219692137</v>
+        <v>1.616866103378406</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.645486044352083</v>
+        <v>-3.397815907110029</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.162745210367383</v>
+        <v>-2.564455808475962</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.934693894257691</v>
+        <v>-3.354397056992141</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>-5.00840410495578</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.171418157096106</v>
+        <v>-1.493552221336138</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.802145040106964</v>
+        <v>3.842330953036047</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.780430034381439</v>
+        <v>6.844023367087644</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.501680630933407</v>
+        <v>4.538895540902935</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.491194620415364</v>
+        <v>6.166429091998801</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.565890391856087</v>
+        <v>4.557350968102604</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.499296390050219</v>
+        <v>1.824668843385723</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.093683311993132</v>
+        <v>3.746154477266906</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.663991527128374</v>
+        <v>5.012867664291527</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.074651993594131</v>
+        <v>0.7584938133680339</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-5.267211316895235</v>
+        <v>-2.468442995781871</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-7.193041563265247</v>
+        <v>-2.949079339618009</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-5.62291167489321</v>
+        <v>-2.144483957326159</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-8.515659044753129</v>
+        <v>-5.667922341350341</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-6.832733628045681</v>
+        <v>-4.044977511244376</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-6.90856588126892</v>
+        <v>-6.965737195189007</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 68.77</t>
+          <t>X ≈ 68.03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.702862617307936</v>
+        <v>2.371140186204059</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.838329576590354</v>
+        <v>-0.2092314597776692</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.501085721357775</v>
+        <v>3.983158995645766</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.237744105015764</v>
+        <v>1.854946327860127</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.002728826266974</v>
+        <v>4.671508530256766</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.562242972131806</v>
+        <v>2.517405216881194</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.884579252921384</v>
+        <v>0.1962806855028916</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-4.612403100775182</v>
+        <v>-0.08784863537619003</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.671691112658934</v>
+        <v>-3.840403225984943</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.77018818404431</v>
+        <v>-5.415560426300921</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-8.170547146533501</v>
+        <v>-5.156495008703679</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.798133759283786</v>
+        <v>0.01247672036640779</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.370908229240719</v>
+        <v>0.4570246384480896</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.609563281909544</v>
+        <v>4.884567986396199</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.3741614110198554</v>
+        <v>2.649728287289378</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.105355884425606</v>
+        <v>3.195808377384466</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.636695970844933</v>
+        <v>3.087242182852037</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.7566614685741371</v>
+        <v>-0.1794578957178175</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1973590510488492</v>
+        <v>1.602488647738959</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3909889374327236</v>
+        <v>-2.116445962968548</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-4.809504097646865</v>
+        <v>-4.267753031450439</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.334962462156696</v>
+        <v>-3.555513978602576</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.285293951224986</v>
+        <v>-1.737076343717902</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.58593240599869</v>
+        <v>-0.3244121884010696</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 71.03</t>
+          <t>X ≈ 70.27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7709175924503811</v>
+        <v>1.037453521884913</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.916800382370056</v>
+        <v>-0.7120181914045389</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.678348843165715</v>
+        <v>1.046322620788857</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.920714627314297</v>
+        <v>0.4627781603515189</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.785916864567497</v>
+        <v>0.9330973001310525</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.077519909765222</v>
+        <v>0.3530113646212456</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.900311127066345</v>
+        <v>-3.403744956044576</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>0.7764308628654959</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.06884696303649918</v>
+        <v>-0.5954564042739889</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.645245183588273</v>
+        <v>-4.389333317462651</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.841773776720458</v>
+        <v>-4.88441236479926</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.444052591933165</v>
+        <v>-1.414413061960069</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3613323058481015</v>
+        <v>-0.2784784471835735</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.094059405940641</v>
+        <v>3.235849806333242</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.435916108359997</v>
+        <v>2.554138210389446</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.08912655971479211</v>
+        <v>-2.948663886113998</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.250672930203855</v>
+        <v>-3.822523035101867</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.884925398730914</v>
+        <v>-1.689377299788994</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.404328135453646</v>
+        <v>-0.7247884381591163</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2531059098085393</v>
+        <v>-1.289033621418788</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.181147977136618</v>
+        <v>-0.6072373134724387</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.84059613337454</v>
+        <v>-0.682399835427681</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.850364963503651</v>
+        <v>0.3245934284766037</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.1666437603078137</v>
+        <v>-2.127621901690723</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 73.3</t>
+          <t>X ≈ 72.49</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.2807215140190138</v>
+        <v>-3.138813318811273</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.847905499982929</v>
+        <v>-4.442982668970323</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.351062921540169</v>
+        <v>-1.442181725352384</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.579285372685661</v>
+        <v>3.320322779899975</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.243494900138387</v>
+        <v>1.971538800219633</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.450068929373018</v>
+        <v>3.190475751954388</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.59968887293362</v>
+        <v>7.725023736886669</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.419516643866828</v>
+        <v>2.018869694790865</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.480611668918755</v>
+        <v>3.206768370876468</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.629264620333302</v>
+        <v>5.61183974197867</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.942539948769671</v>
+        <v>3.706373066284186</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>4.506621939864544</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>3.374922383431489</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.221510386332781</v>
+        <v>4.254894511308201</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>12.48493571620323</v>
+        <v>2.414034098016828</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>10.13814616755796</v>
+        <v>4.10434966712846</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>8.043444716854978</v>
+        <v>1.436584249084248</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>0.8931746982333451</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.193711080232596</v>
+        <v>-1.49368178967292</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.419772576475097</v>
+        <v>1.621141673270323</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>1.053697171889524</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.722949074551018</v>
+        <v>0.9785346499341827</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>9.958208100758611</v>
+        <v>3.419971333014814</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.921591533809796</v>
+        <v>3.25783233872535</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 75.56</t>
+          <t>X ≈ 74.72</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.692486219901369</v>
+        <v>3.895911005910932</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.691042754884919</v>
+        <v>1.506196889011001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.5863570391872344</v>
+        <v>3.463247111964634</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.873403019744487</v>
+        <v>2.876133709088258</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4623874528027514</v>
+        <v>2.597931171023042</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>4.901316456183032</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.619296716070949</v>
+        <v>7.968951819033222</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.341085271317873</v>
+        <v>7.668430203641492</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.049239119899198</v>
+        <v>5.634697281087512</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.942990110529379</v>
+        <v>8.082886866608561</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.21704975269137</v>
+        <v>12.3091892724759</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.60496701590998</v>
+        <v>15.99167829809323</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>18.14847161572052</v>
+        <v>14.90708932713245</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>15.26072607260723</v>
+        <v>19.04428017802136</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>11.93591610836008</v>
+        <v>22.79440131805783</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>8.530303030303031</v>
+        <v>16.81347290256753</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.729719226658887</v>
+        <v>13.41288919413919</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>14.3789061878787</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.50743657042873</v>
+        <v>14.59336841502453</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>11.3609490470634</v>
+        <v>15.90685595898448</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>13.48506954576396</v>
+        <v>17.53721365540603</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>9.409223584354969</v>
+        <v>19.6598533312529</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>9.683698296836909</v>
+        <v>16.606784519828</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>10.94119937694693</v>
+        <v>14.24684332773635</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 77.82</t>
+          <t>X ≈ 76.94</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.201258149725959</v>
+        <v>4.344623149067914</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.344044964413364</v>
+        <v>4.103305098319176</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.782064013444376</v>
+        <v>-2.50897926238531</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.442386453939726</v>
+        <v>1.182855231874711</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.830808505434391</v>
+        <v>-5.509880377916851</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.801737056179093</v>
+        <v>-6.421711552708302</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.310527845332594</v>
+        <v>-1.886736015858702</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.674418604651194</v>
+        <v>2.030125335751919</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.873800523408008</v>
+        <v>3.19594231422802</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.100884847371518</v>
+        <v>5.2307199942761</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.427576068480782</v>
+        <v>5.506917806249618</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.043563507138046</v>
+        <v>5.246187041254885</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2374932965602099</v>
+        <v>11.26761417079097</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.774361646690949</v>
+        <v>5.202135247715539</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.169347049534693</v>
+        <v>5.627410713291688</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.574960127591702</v>
+        <v>6.206688382739472</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.6562456856217835</v>
+        <v>3.928894927536234</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.7610863894430011</v>
+        <v>0.5351412571572354</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5451950085186752</v>
+        <v>1.836560006042149</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.957440275133592</v>
+        <v>6.398972538057649</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.467525686114904</v>
+        <v>11.26631064537253</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.444311303653144</v>
+        <v>7.930278558199923</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.666154437187856</v>
+        <v>10.34782608695655</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>9.748216920806691</v>
+        <v>15.62046970136274</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 80.08</t>
+          <t>X ≈ 79.16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-10.78370425628918</v>
+        <v>-5.708910976997096</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.59467153082943</v>
+        <v>-2.702017164840235</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.651738198907907</v>
+        <v>-4.17266483671429</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.88850174216031</v>
+        <v>-12.66761798706793</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.0814350718504</v>
+        <v>-5.067619371869618</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>-4.937679962119347</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.285465188690992</v>
+        <v>-4.065870356050077</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.944629014396483</v>
+        <v>-5.08548482931787</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.239715310375324</v>
+        <v>-0.7442944615184786</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.295105127565897</v>
+        <v>-4.752541410664534</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-10.16390262826104</v>
+        <v>-6.079598624180527</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-17.58550917456618</v>
+        <v>-9.527543039520204</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-18.70867124142227</v>
+        <v>-15.41308984595966</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-21.31070249882138</v>
+        <v>-22.04488182218792</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-17.20694103449717</v>
+        <v>-15.36752361620714</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-14.23160173160176</v>
+        <v>-13.84941259902771</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-14.36551886857924</v>
+        <v>-10.72748655913976</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-12.08940719144801</v>
+        <v>-9.247467438494937</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-4.730658667666532</v>
+        <v>-9.033005211349163</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-9.305717619603307</v>
+        <v>-5.592612314677282</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3244542637597476</v>
+        <v>-2.934250364445099</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.980652155783503</v>
+        <v>0.2163935652125133</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1258255126868235</v>
+        <v>-1.1528751753156</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-2.582610146862415</v>
+        <v>-2.927917395411527</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 82.34</t>
+          <t>X ≈ 81.4</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>16.12659474703315</v>
+        <v>3.600230414746584</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>15.7918179486833</v>
+        <v>6.211466436185496</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>19.00496169034998</v>
+        <v>10.67105804857962</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15.96642627555846</v>
+        <v>7.221512992628632</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.63063580301116</v>
+        <v>-1.625473718899357</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.16643919841087</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12.7200719098694</v>
+        <v>-2.263622125133914</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>14.76744186046508</v>
+        <v>0.2886002886003212</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.48334764703098</v>
+        <v>6.130814912570152</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18.68717615704101</v>
+        <v>8.191906274493618</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>18.9612357992029</v>
+        <v>5.606998431955098</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>23.3336491864526</v>
+        <v>11.04470219176956</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>19.88490572424765</v>
+        <v>4.215524360033029</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.01266405710339</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>12.02893936417399</v>
+        <v>-2.429149797570759</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>12.62332628611695</v>
+        <v>-1.867845778751096</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>12.48940914913948</v>
+        <v>-1.971726190476232</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>14.71014984066717</v>
+        <v>3.609675418647875</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>21.902785407638</v>
+        <v>15.25270907436513</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>19.76404982225715</v>
+        <v>9.753009805138433</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>21.54708504963997</v>
+        <v>14.89985101804341</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>26.12240187892858</v>
+        <v>20.5389742103738</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>28.72245798675947</v>
+        <v>23.63975155279504</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>28.64662573353619</v>
+        <v>20.62046970136272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 84.61</t>
+          <t>X ≈ 83.62</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.149850560986636</v>
+        <v>13.84867761971545</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.163910971939153</v>
+        <v>11.42885774053339</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.051473318256988</v>
+        <v>14.5219897255983</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.338519298814248</v>
+        <v>11.75567448331182</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.328310221615816</v>
+        <v>13.65402938669074</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>15.81760198910854</v>
+        <v>15.98487603616709</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>15.04565330521816</v>
+        <v>15.18979402393437</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>17.09302325581396</v>
+        <v>21.40661271096053</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>17.13451043772866</v>
+        <v>19.36062857716639</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.36159476169213</v>
+        <v>22.91240316890357</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>18.96123579920293</v>
+        <v>23.18463818350791</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.35690500040606</v>
+        <v>18.56023014208004</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.90816153820113</v>
+        <v>17.44533802462927</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.710338475708042</v>
+        <v>12.84927787623966</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.726613782778642</v>
+        <v>12.16712349435461</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.646582100070475</v>
+        <v>14.90234055665252</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.838246358441836</v>
+        <v>16.9723731884058</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>5.40782425927182</v>
+        <v>14.66557603976597</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.298134244847304</v>
+        <v>12.70612522343345</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.136142845513007</v>
+        <v>19.44245079892717</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>9.919178072895811</v>
+        <v>18.87500629754643</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>9.84333211148671</v>
+        <v>16.62593073211294</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.792225428619929</v>
+        <v>14.69565217391304</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.716393175396654</v>
+        <v>12.35960013614532</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 86.87</t>
+          <t>X ≈ 85.84</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.359152886568</v>
+        <v>5.548282362798496</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>11.02437608821822</v>
+        <v>5.302375527094625</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>8.593135970657585</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>12.54618831730389</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>16.81608472265913</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.275421266705401</v>
+        <v>21.51847287411174</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.95263004940424</v>
+        <v>25.26884540733359</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>22.67441860465117</v>
+        <v>20.41847041847041</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.71590578656587</v>
+        <v>25.09185387360908</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.94299011052934</v>
+        <v>24.29580237838975</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>22.21704975269126</v>
+        <v>29.1134919384486</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.93830034924331</v>
+        <v>24.29145543852277</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>20.81513828238719</v>
+        <v>18.63110877561748</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.5940594059406</v>
+        <v>13.83742016872976</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>19.93591610836004</v>
+        <v>8.609811241390169</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.53030303030306</v>
+        <v>9.171115260209845</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5.396385893325558</v>
+        <v>9.067234848484837</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.291545189504404</v>
+        <v>8.934350743323236</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.5074365704287302</v>
+        <v>9.14881297046901</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.305717619603264</v>
+        <v>4.817944870073489</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>13.34140945960188</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.075890251021569</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.35036496350365</v>
+        <v>8.964426877470352</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>20.27453271028038</v>
+        <v>13.34774242863545</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 22.39</t>
+          <t>X &gt; 22.41</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3334</v>
+        <v>3358</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1109096692854123</v>
+        <v>-0.09690061157703411</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2211543051071629</v>
+        <v>-0.06072291292689158</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3018694883835593</v>
+        <v>-0.115734324480826</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3722737840718509</v>
+        <v>-0.1294131682442909</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.452843760586866</v>
+        <v>-0.2108622717145821</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4281658967770028</v>
+        <v>-0.2151548725491708</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.467244614875078</v>
+        <v>-0.2826697441815753</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3703575147518166</v>
+        <v>-0.1856142934981193</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4313023352615346</v>
+        <v>-0.1891207106563542</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3509166995064632</v>
+        <v>-0.1083818122713254</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3285134382259329</v>
+        <v>-0.05643336022186674</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.4705460344984758</v>
+        <v>-0.1676759345551986</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4703624649969598</v>
+        <v>-0.1376113733342237</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5243616466909842</v>
+        <v>-0.1606364065239276</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.5068000148825575</v>
+        <v>-0.1125474809685301</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.6127250965671109</v>
+        <v>-0.2168823630818864</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.5494387100865907</v>
+        <v>-0.2141375681030198</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.60665840331</v>
+        <v>-0.2997861067470211</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.6426083532011262</v>
+        <v>-0.2462077091190125</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.5879225327249031</v>
+        <v>-0.2520892005554884</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.6034331013241712</v>
+        <v>-0.2070474390484804</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.6015677825515482</v>
+        <v>-0.264597218197629</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.6091552763764128</v>
+        <v>-0.2117348589771737</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.5473029225930546</v>
+        <v>-0.2074040330029803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 24.65</t>
+          <t>X &gt; 24.63</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3293</v>
+        <v>3319</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1124997069180935</v>
+        <v>-0.1015734665905512</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1898018906656418</v>
+        <v>-0.06210435100393141</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2235403657614796</v>
+        <v>-0.04322766570604131</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3765215199476302</v>
+        <v>-0.1399724820644366</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3633536363776599</v>
+        <v>-0.1292826720791496</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4010630667658077</v>
+        <v>-0.1654021361042908</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4612672315625232</v>
+        <v>-0.2843484012559117</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3899512956208184</v>
+        <v>-0.1825926863408114</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5428608397944643</v>
+        <v>-0.277617686624346</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5426464180463668</v>
+        <v>-0.276654867334841</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.5234221166371853</v>
+        <v>-0.2273353015382895</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6638176537824165</v>
+        <v>-0.3366933565428667</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.649752758775044</v>
+        <v>-0.2932701487614793</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6714567914557037</v>
+        <v>-0.2836645140851388</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.6152649940021604</v>
+        <v>-0.1970069404279897</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.6693334434927891</v>
+        <v>-0.2490557920621939</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.4520989551592862</v>
+        <v>-0.09473967729004329</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.4783850923992361</v>
+        <v>-0.1497230775926752</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.5174269832401848</v>
+        <v>-0.09798716080764081</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.5553384870585347</v>
+        <v>-0.1966914114902991</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.6249628166955219</v>
+        <v>-0.2046471328123971</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6828350904048079</v>
+        <v>-0.3222121792678792</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.663599820952939</v>
+        <v>-0.2414876898899863</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5696822912379957</v>
+        <v>-0.2050801630542693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 26.92</t>
+          <t>X &gt; 26.86</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3239</v>
+        <v>3263</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.007221556095927895</v>
+        <v>-0.01249891313798912</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1884420657222847</v>
+        <v>-0.0290206262193351</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2909435743097006</v>
+        <v>-0.07976846960373507</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5267197172914067</v>
+        <v>-0.2289895964667608</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5998951262220587</v>
+        <v>-0.2743811795069604</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.6721053317959829</v>
+        <v>-0.4052754287892526</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7513011545269563</v>
+        <v>-0.4822632401165308</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6742757117850857</v>
+        <v>-0.4346167200696058</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.830498638756815</v>
+        <v>-0.5030210501249215</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.8175386321696649</v>
+        <v>-0.5190227110767935</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.8333807516137455</v>
+        <v>-0.443062618105948</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.002333301940936</v>
+        <v>-0.6106958453079017</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.031015563766658</v>
+        <v>-0.578087647995595</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.987965832594341</v>
+        <v>-0.5336044681060201</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.8892070443493267</v>
+        <v>-0.4644274783252982</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.9849418110890227</v>
+        <v>-0.5576304667015748</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.731155696323242</v>
+        <v>-0.3989870030581031</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.7254039630379907</v>
+        <v>-0.4221385917528195</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7379395084862139</v>
+        <v>-0.3426747339929861</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.841332790741113</v>
+        <v>-0.5080422740955086</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.9340133248919358</v>
+        <v>-0.5371186259072829</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.9608268116133871</v>
+        <v>-0.6248849014179356</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.9459313327926466</v>
+        <v>-0.5470481670929246</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.7875234799017719</v>
+        <v>-0.446033516534925</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 29.18</t>
+          <t>X &gt; 29.08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3165</v>
+        <v>3184</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1232683194413013</v>
+        <v>0.1524153673056787</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06912877528978356</v>
+        <v>0.1104059246446738</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.07779864191760311</v>
+        <v>0.2141826307058068</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3338183303340116</v>
+        <v>0.04476963610994744</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4322366990339361</v>
+        <v>-0.08852175422334341</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.6046704027405951</v>
+        <v>-0.3201507134187693</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6363077255800391</v>
+        <v>-0.379389519251859</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.8024754538210175</v>
+        <v>-0.5417568542568603</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.026232578214</v>
+        <v>-0.646302936757813</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.057953582455838</v>
+        <v>-0.7056189644950308</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.9547564147095784</v>
+        <v>-0.5407293485534126</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.184142206627016</v>
+        <v>-0.7682783195839562</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.37629748587478</v>
+        <v>-0.95773743294707</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.358696499571209</v>
+        <v>-0.9374417883488135</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.210901787040086</v>
+        <v>-0.8184836081386067</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.196769141143548</v>
+        <v>-0.8340111922850255</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.091634283219214</v>
+        <v>-0.7943075577144114</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.020343804503817</v>
+        <v>-0.8148655576171961</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.9752132718425912</v>
+        <v>-0.6761535337072644</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.148570254503866</v>
+        <v>-0.913776357256296</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.262405201710713</v>
+        <v>-0.9610123106580488</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.193449818444776</v>
+        <v>-0.955062198916842</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.247866243066149</v>
+        <v>-0.944235888335264</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.147268237586921</v>
+        <v>-0.89963080114984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 31.44</t>
+          <t>X &gt; 31.31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3085</v>
+        <v>3105</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1558066832218259</v>
+        <v>0.1338438601246921</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06364226137560536</v>
+        <v>0.1929183069882185</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2206133173585059</v>
+        <v>0.4270218544474957</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1523618755856262</v>
+        <v>0.1723701354857283</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1479544631120646</v>
+        <v>0.1707582181776814</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3940161748588054</v>
+        <v>-0.07061687059759691</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.470967629512586</v>
+        <v>-0.1752172564600301</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6341915211147153</v>
+        <v>-0.3979928363138896</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8324813102083155</v>
+        <v>-0.5083792266240366</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.9418114383573624</v>
+        <v>-0.5810520912829489</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.101220098825806</v>
+        <v>-0.7074888767592782</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.297088736969158</v>
+        <v>-0.9017664823218752</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.400623991514628</v>
+        <v>-1.003621064503925</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.441481789535977</v>
+        <v>-1.040735383583062</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.466798823766652</v>
+        <v>-1.062051898681034</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.435426035329044</v>
+        <v>-1.060172886272639</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.162475684940937</v>
+        <v>-0.856228577549274</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.248409517710122</v>
+        <v>-1.03467412444801</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.175411326011435</v>
+        <v>-0.8658026390018989</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.358161776288284</v>
+        <v>-1.147141828368014</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.396191248709201</v>
+        <v>-1.116879998687651</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.420708388434186</v>
+        <v>-1.205473810224845</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.516128879659014</v>
+        <v>-1.200649514264114</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.411042654387373</v>
+        <v>-1.150866852582531</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 33.7</t>
+          <t>X &gt; 33.54</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3005</v>
+        <v>3022</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2408839734527319</v>
+        <v>0.2833174426611578</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1882888443319075</v>
+        <v>0.383608354713779</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3218942292698657</v>
+        <v>0.6255202803997619</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.04194089559943137</v>
+        <v>0.3144030085955265</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.004698223677536362</v>
+        <v>0.3531987102828111</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2052922557891037</v>
+        <v>0.1339034961213201</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.3299642590007892</v>
+        <v>-0.01758254444482077</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4900964565868264</v>
+        <v>-0.2380619892140672</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5953524915798241</v>
+        <v>-0.2231998576448646</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7532669282251803</v>
+        <v>-0.4077549338632309</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8909688026433571</v>
+        <v>-0.5120884120081826</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.150861069384469</v>
+        <v>-0.7699696229022948</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.326771531936423</v>
+        <v>-0.9429702940105784</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.329655353595058</v>
+        <v>-0.9413037458780238</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.53720930637121</v>
+        <v>-1.109453327758899</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.421240282010281</v>
+        <v>-1.02390424174034</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.203879710924106</v>
+        <v>-0.877541405304278</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.322536510927371</v>
+        <v>-1.090267966896519</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.286583363126113</v>
+        <v>-0.9557009497039743</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.512430813355351</v>
+        <v>-1.250672566686738</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.537093574803343</v>
+        <v>-1.204045085852734</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.626803463644187</v>
+        <v>-1.392242720843129</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.765403499570205</v>
+        <v>-1.427116742654142</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.622305892049077</v>
+        <v>-1.40467920664522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 35.96</t>
+          <t>X &gt; 35.76</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2902</v>
+        <v>2921</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1262761742392726</v>
+        <v>0.1598189240633161</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3237936969883464</v>
+        <v>0.4418436023425159</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2561069535414546</v>
+        <v>0.4972210086651287</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.04574737422605324</v>
+        <v>0.3317281769682126</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2693699983791191</v>
+        <v>0.6534378457265291</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1260550453967326</v>
+        <v>0.1831392727012471</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2470958841346373</v>
+        <v>0.1218684904451521</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3687616558011939</v>
+        <v>-0.1297079948765401</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4448758383912761</v>
+        <v>-0.0505786257716565</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5810153764390762</v>
+        <v>-0.2140319099794823</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.7675128545128089</v>
+        <v>-0.3312623529314536</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.23259875851236</v>
+        <v>-0.7930066387794099</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.27205704888641</v>
+        <v>-0.7971437358547107</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.301544989663796</v>
+        <v>-0.8550521491263581</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.458793613385062</v>
+        <v>-0.9713243465713362</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.565916900968439</v>
+        <v>-1.106981514984909</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.267416100486756</v>
+        <v>-0.9178620218579283</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.352196213521758</v>
+        <v>-1.099192754518171</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.391428238652821</v>
+        <v>-1.035739319346426</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.597527667779467</v>
+        <v>-1.348333296204707</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.638280999273256</v>
+        <v>-1.314727836754358</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.76295272418502</v>
+        <v>-1.506869101292295</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.847361526334446</v>
+        <v>-1.551409100377946</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.79989871632197</v>
+        <v>-1.625336529380185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 38.23</t>
+          <t>X &gt; 37.99</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2785</v>
+        <v>2802</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3562977830705378</v>
+        <v>0.3688776966681573</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6282304779398444</v>
+        <v>0.9210981642308553</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4393192090658857</v>
+        <v>0.7484832800962948</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01187553937332098</v>
+        <v>0.4947741043021736</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4255497349202741</v>
+        <v>0.8062880677011819</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.06557115963902049</v>
+        <v>0.3450363815263202</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.01667758799761287</v>
+        <v>0.3147998076689618</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3102297352274519</v>
+        <v>-0.005427897549971306</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3912370705769845</v>
+        <v>0.03618536746132861</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5721938837542879</v>
+        <v>-0.1715271670648164</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8494263016332155</v>
+        <v>-0.4117785282073001</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.358088638958336</v>
+        <v>-0.8813816746128538</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.495305208313809</v>
+        <v>-0.9807582056060866</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.624187463469063</v>
+        <v>-1.066239471771951</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.653203433515415</v>
+        <v>-1.087481860385296</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.718175308400866</v>
+        <v>-1.217108615558502</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.616508089482458</v>
+        <v>-1.15801515960603</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.485595620241227</v>
+        <v>-1.163421854449354</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.571416476166277</v>
+        <v>-1.177643615339186</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.722354406982262</v>
+        <v>-1.441369585962313</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.670358479104451</v>
+        <v>-1.31099695751049</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.797091449731901</v>
+        <v>-1.543764733991395</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.788902803904818</v>
+        <v>-1.457847957933268</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.7362392825383</v>
+        <v>-1.527995680507381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 40.49</t>
+          <t>X &gt; 40.21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2666</v>
+        <v>2677</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7248245283590791</v>
+        <v>0.7166325311486617</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8378089240391162</v>
+        <v>0.972489037148847</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7803868899334887</v>
+        <v>0.9612200733599252</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3286269003415043</v>
+        <v>0.537896275641458</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7017916516748244</v>
+        <v>0.9508297995406991</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.00676455028749956</v>
+        <v>0.2754302024976525</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07949572104602964</v>
+        <v>0.3177756901168678</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1400644113995995</v>
+        <v>0.03397188692397179</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3012712111936509</v>
+        <v>-0.03984948989221948</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.3805063407220146</v>
+        <v>-0.1087785479303278</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5173544310965212</v>
+        <v>-0.1869473991654473</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9455248281941238</v>
+        <v>-0.6282511100421004</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.060095187915387</v>
+        <v>-0.6803089733002992</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.222084091817251</v>
+        <v>-0.8325395700799589</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.185579218742767</v>
+        <v>-0.8229376924756409</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.317116565807659</v>
+        <v>-0.9473882102489242</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.092577817860374</v>
+        <v>-0.7688307252856532</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9883949302561064</v>
+        <v>-0.8799683702877061</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.124910864988749</v>
+        <v>-0.8674571129151545</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.290736346195033</v>
+        <v>-1.153368411944783</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.212070456733784</v>
+        <v>-0.9903408796112103</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.265938834435673</v>
+        <v>-1.11836061605397</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.269432561805679</v>
+        <v>-1.039646718836252</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.248348009899665</v>
+        <v>-1.142698023702657</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 42.75</t>
+          <t>X &gt; 42.44</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2513</v>
+        <v>2521</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9983281442999896</v>
+        <v>1.056429875662992</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.377270616370481</v>
+        <v>1.539818775941725</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8908772612332214</v>
+        <v>1.093672412972161</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8123403710529686</v>
+        <v>1.03497226063331</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.269571310083805</v>
+        <v>1.529756877276157</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4652607317085469</v>
+        <v>0.6852887285999216</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4466823888174005</v>
+        <v>0.7398676868665035</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3102773908471264</v>
+        <v>0.5757786207135851</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.005236617242140085</v>
+        <v>0.3714638535345003</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.05485048339728849</v>
+        <v>0.4263385089258662</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.05124253333390527</v>
+        <v>0.4846622046464972</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1085064734461056</v>
+        <v>0.270352183309754</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2796653669583122</v>
+        <v>0.1656484855126052</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3420770478475745</v>
+        <v>0.09868951968700657</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4212267487828214</v>
+        <v>0.07226183427556521</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.6368267831149907</v>
+        <v>-0.2127590702836955</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.5488087055624433</v>
+        <v>-0.1351529535865055</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.5109975200705179</v>
+        <v>-0.1655521238926383</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.8513238586535365</v>
+        <v>-0.3631714821330121</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.022046582654525</v>
+        <v>-0.6005969841119665</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.8657518638809023</v>
+        <v>-0.3525827605393772</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.8386226714436091</v>
+        <v>-0.4439825870895291</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.8986406053109803</v>
+        <v>-0.3752025652518611</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.8715078786571482</v>
+        <v>-0.5140007468721137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 45.01</t>
+          <t>X &gt; 44.66</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2380</v>
+        <v>2387</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.164020700248265</v>
+        <v>1.063182400520105</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.584594300555608</v>
+        <v>1.670162990772496</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.279600849510352</v>
+        <v>1.435177649908574</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.154141584578731</v>
+        <v>1.40633108272295</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.531737599652104</v>
+        <v>1.777922552327375</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7115699208732735</v>
+        <v>0.8777622334011141</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6110438135670577</v>
+        <v>0.8965870500502646</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7105075681425603</v>
+        <v>0.948489712534645</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4162834617652038</v>
+        <v>0.8506912061349894</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5665738285318938</v>
+        <v>0.8699570866552193</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6308139155112755</v>
+        <v>0.9581889081455728</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4359923341363015</v>
+        <v>0.7475545707369449</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2360363100833638</v>
+        <v>0.53269342949568</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1828130777828179</v>
+        <v>0.517740265820855</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.07020062367686819</v>
+        <v>0.486423777435121</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.3005824082198387</v>
+        <v>0.1124703560534712</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3086078120877787</v>
+        <v>-0.008484753550540347</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.539340249018494</v>
+        <v>-0.2838234769403982</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.6591601563862426</v>
+        <v>-0.2537409973023443</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.9339173678198023</v>
+        <v>-0.5582765663738272</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.8050409592016976</v>
+        <v>-0.3482063639052271</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7721366171564057</v>
+        <v>-0.3986565974955951</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.640815212892818</v>
+        <v>-0.2140412205957247</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.5237866174507175</v>
+        <v>-0.2676744125878514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 47.28</t>
+          <t>X &gt; 46.89</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.255828537960667</v>
+        <v>1.152522359561857</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.594906187050199</v>
+        <v>1.618676049002616</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.684290552215082</v>
+        <v>1.813406350322445</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.600267350382403</v>
+        <v>1.780851204528041</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.162949474420927</v>
+        <v>2.288455489147537</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.092054025298182</v>
+        <v>1.178425048553443</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.038883418676477</v>
+        <v>1.166988299232038</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8055956037526926</v>
+        <v>0.932445510758761</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4427701172037857</v>
+        <v>0.6843863411415327</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6581742974116764</v>
+        <v>0.9412203815567324</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7076157904271483</v>
+        <v>1.060847531916806</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.698408165954902</v>
+        <v>1.033845815244838</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6983368448310259</v>
+        <v>0.9737661182747885</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.432334338555151</v>
+        <v>0.8416910656181429</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.35819822875537</v>
+        <v>0.812952773090359</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1888834436004245</v>
+        <v>0.6847740152479247</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.09988993645224298</v>
+        <v>0.5180331541218592</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.139721656856814</v>
+        <v>0.2325863490442828</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3281429443960917</v>
+        <v>0.159819900758464</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5905334327209744</v>
+        <v>-0.1822590534144553</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4592251532476439</v>
+        <v>0.08451375207773992</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.5533232321244697</v>
+        <v>-0.1435583446329289</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.476973165992753</v>
+        <v>0.03687644048595473</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2562815047443721</v>
+        <v>0.126087678890805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 49.54</t>
+          <t>X &gt; 49.12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.135917168853197</v>
+        <v>1.110744591927393</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.569263270167326</v>
+        <v>1.624571849290945</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.619482339235233</v>
+        <v>1.726368533818892</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.674651219456436</v>
+        <v>1.894061346887149</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.86694524042813</v>
+        <v>2.121131387021371</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8537193958005957</v>
+        <v>1.11688207309156</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8498936115741813</v>
+        <v>1.062461876497146</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6676975292791099</v>
+        <v>0.8325589477421858</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2771155801328362</v>
+        <v>0.5593863411415327</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.416345847447289</v>
+        <v>0.7434614368158208</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5943901271512217</v>
+        <v>0.9958040972145383</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6516944923061985</v>
+        <v>1.033121021390059</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.5847014124880019</v>
+        <v>1.138915854035218</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4116302172704138</v>
+        <v>0.8237512600728252</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.3295790944378041</v>
+        <v>0.8864457816350466</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2518584791748495</v>
+        <v>0.9032961228255019</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2619643858843688</v>
+        <v>0.7324529955385586</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1309224053107911</v>
+        <v>0.2455980803955526</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.1550694305314479</v>
+        <v>0.3928321092249973</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2562697079374061</v>
+        <v>0.1571676386882856</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.03069297623948586</v>
+        <v>0.5279298357773641</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1738695952800384</v>
+        <v>0.2418970661476436</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1109517111719924</v>
+        <v>0.4182750427279203</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.1783788641265289</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 51.8</t>
+          <t>X &gt; 51.34</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1936</v>
+        <v>1943</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8717882656294051</v>
+        <v>0.8638939035755939</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.671616934015013</v>
+        <v>1.687778203888023</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.419776327480157</v>
+        <v>1.706644978206334</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.428843968687232</v>
+        <v>1.674609564930464</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.660356229507684</v>
+        <v>1.937945532593325</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5064250458268305</v>
+        <v>0.7475304050560752</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.765935877150504</v>
+        <v>1.001683997315027</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5392974081581272</v>
+        <v>0.7261413080708579</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.0134818567051127</v>
+        <v>0.3727527500135608</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.01416081707914429</v>
+        <v>0.2701601616386711</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3397934350017735</v>
+        <v>0.6741909531353514</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6799197406821875</v>
+        <v>0.989897661261665</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2272063587151933</v>
+        <v>0.6726087290928433</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2639923610721056</v>
+        <v>0.7107618807811846</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.2762977483806637</v>
+        <v>0.7763537153097175</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2518089611952448</v>
+        <v>0.7535205535326241</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1178918242177716</v>
+        <v>0.5264423076922995</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.03852185536411667</v>
+        <v>0.2189255835676533</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.08049535324329327</v>
+        <v>0.3099105997391263</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.099941446318077</v>
+        <v>0.09272658553313562</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.0279610706050164</v>
+        <v>0.3263669481564193</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.06858859314765198</v>
+        <v>0.1276631563892252</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.1335348137875982</v>
+        <v>0.4533905886562906</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.3468467598671481</v>
+        <v>0.5792962582335335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 54.06</t>
+          <t>X &gt; 53.57</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1771</v>
+        <v>1786</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.335464223285463</v>
+        <v>0.3887132497410164</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9595142720873682</v>
+        <v>1.084113169297382</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.100739441894504</v>
+        <v>1.379806664305029</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5569901601844123</v>
+        <v>1.2857433359287</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.236428114033082</v>
+        <v>1.761942189292213</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4645674529787485</v>
+        <v>0.6204684395219502</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4822408785074614</v>
+        <v>0.7440634782255273</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4860373299754741</v>
+        <v>0.6929129570638963</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1891150364248588</v>
+        <v>0.4641218055660659</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1494198905632231</v>
+        <v>0.4220650046523531</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3670779534809299</v>
+        <v>0.7820957082196998</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7651475009635575</v>
+        <v>1.205197980741389</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4880091227707197</v>
+        <v>0.9020654205306826</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7181428802778811</v>
+        <v>1.132419156379115</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.6240153751395141</v>
+        <v>1.152227042858925</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.4287801876634418</v>
+        <v>1.02274189444519</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5204693676628409</v>
+        <v>0.8965711563487559</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1336207676205561</v>
+        <v>0.4623539900764939</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1581020646530717</v>
+        <v>0.3193119299127076</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02874374531495505</v>
+        <v>0.2318605633187545</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.1630165282795488</v>
+        <v>0.6476750218763172</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1384357501064315</v>
+        <v>0.3823746578011011</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.2262114646323212</v>
+        <v>0.8273764628597888</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.2971188198230053</v>
+        <v>0.7548482008028046</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 56.33</t>
+          <t>X &gt; 55.79</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1566</v>
+        <v>1605</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2200335502566162</v>
+        <v>0.09037819799777935</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7148674730299618</v>
+        <v>0.7681166824909482</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.9998860755624719</v>
+        <v>1.175984156954051</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3507482654368843</v>
+        <v>0.6451583128256289</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.610363025818785</v>
+        <v>1.847432685041568</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7762698628414952</v>
+        <v>0.7460536728570588</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.280645365294475</v>
+        <v>1.280503293220811</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.193882548492894</v>
+        <v>1.196329203732034</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.299185939724772</v>
+        <v>1.174906623328489</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.611145822080111</v>
+        <v>1.526416113018286</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.69375683629054</v>
+        <v>1.773341359731894</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.308434363282871</v>
+        <v>2.089847522629128</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.142515436184254</v>
+        <v>2.125708235563444</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.049068978371992</v>
+        <v>2.348537534336323</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.029087773963106</v>
+        <v>2.447819577539789</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.921496393417257</v>
+        <v>2.179625658676855</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.979027884391293</v>
+        <v>2.175739247311824</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.172208878081271</v>
+        <v>1.336021077954477</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.005203003102594</v>
+        <v>1.401777397346486</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8729677664847983</v>
+        <v>1.343172284051647</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9685836916904265</v>
+        <v>1.621599418896245</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.8927377302813255</v>
+        <v>1.148806195439143</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.486293489349215</v>
+        <v>1.928312307109216</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.257929900574119</v>
+        <v>1.555049140615047</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 58.59</t>
+          <t>X &gt; 58.02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1371</v>
+        <v>1394</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5136718370053472</v>
+        <v>0.1400928186316079</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9077580124164655</v>
+        <v>0.7440443398682532</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.291896397787816</v>
+        <v>1.259888481602736</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3602834862167867</v>
+        <v>0.5258432233044203</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9720148795587278</v>
+        <v>1.100143440145601</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5758906866473623</v>
+        <v>0.872251625480871</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.115895355526689</v>
+        <v>1.323004014683669</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.639433181910647</v>
+        <v>1.626935480732492</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.753806661201445</v>
+        <v>2.009467509972708</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.001299148430249</v>
+        <v>2.321259508324474</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.056699898463897</v>
+        <v>2.493810055608833</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.089903847785578</v>
+        <v>3.540889278703943</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.132922538946957</v>
+        <v>3.537868682377358</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.838957365124273</v>
+        <v>3.476505246161274</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.618131851800271</v>
+        <v>3.409448123766026</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.410769502606243</v>
+        <v>3.373308498805656</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.349738663004864</v>
+        <v>2.956845238095234</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.588921282798843</v>
+        <v>2.010574019689486</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.367494879466605</v>
+        <v>2.0542623136866</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.481454392058531</v>
+        <v>1.954666416243825</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.594884900477346</v>
+        <v>2.290354497372071</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.300380046939964</v>
+        <v>2.044350554459825</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.939286246302487</v>
+        <v>3.049466658349452</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.127195000579427</v>
+        <v>2.743855641104467</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.85</t>
+          <t>X &gt; 60.25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1187</v>
+        <v>1209</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.624527781260532</v>
+        <v>1.188205245788268</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.458242979540877</v>
+        <v>1.02386447859989</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.705143896811485</v>
+        <v>1.482057815533757</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.581911865574305</v>
+        <v>1.215919890787518</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.498859387972274</v>
+        <v>1.429758161781173</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.348841580809335</v>
+        <v>0.9341632196552823</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.924828869960265</v>
+        <v>1.491479915682369</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.573323406673069</v>
+        <v>2.296069943128764</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.783302585217932</v>
+        <v>2.635896094674997</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.526814878852882</v>
+        <v>3.279584553661266</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.463890527754486</v>
+        <v>3.601616426573095</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.448831099032688</v>
+        <v>4.358519521980291</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.336621011957533</v>
+        <v>4.442876990995181</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.8628041405657</v>
+        <v>4.328538246054769</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.541644836245467</v>
+        <v>4.191345565734707</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>3.546309769982898</v>
+        <v>3.982718131023255</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.328146634690341</v>
+        <v>3.436856995884774</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.549337944348522</v>
+        <v>2.531774736134388</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.343999333697447</v>
+        <v>2.549847220637652</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.109615152090072</v>
+        <v>2.155178593445797</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.325282968959762</v>
+        <v>2.711576864451303</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.249437007550661</v>
+        <v>2.522445284753971</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.692403716662874</v>
+        <v>3.148200093501643</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.616571463439598</v>
+        <v>2.986061099212179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.11</t>
+          <t>X &gt; 62.47</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1041</v>
+        <v>1067</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.651179783782254</v>
+        <v>2.095081220133402</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.124280026738873</v>
+        <v>1.571910059106052</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.319306126603166</v>
+        <v>2.073223350929815</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.702413586507213</v>
+        <v>1.758085477445064</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.846930510693859</v>
+        <v>1.944634546218182</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.841773738097672</v>
+        <v>1.639460943343813</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.126501327021913</v>
+        <v>1.915048418013917</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.616781717043096</v>
+        <v>2.590187590187583</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.6582688989578</v>
+        <v>2.958565475260421</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.518398371816602</v>
+        <v>3.702110356126276</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.696396534631752</v>
+        <v>3.659790579454764</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.570384883345135</v>
+        <v>4.462121203984076</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.119653171916482</v>
+        <v>4.335125688936685</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.706451336776333</v>
+        <v>3.959309452630251</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.336492477236121</v>
+        <v>3.801711605704348</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.066326085058073</v>
+        <v>3.675864242570782</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.740285989387033</v>
+        <v>3.257031979458446</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.059076409485165</v>
+        <v>2.528233496084496</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.794660393675578</v>
+        <v>2.613393291924929</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.077567682990392</v>
+        <v>2.69843516629409</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.303513349798614</v>
+        <v>3.125851821363767</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.227667388389513</v>
+        <v>2.769527162576232</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.598203580218353</v>
+        <v>3.575485921519096</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.714494285688637</v>
+        <v>3.319626214952223</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.38</t>
+          <t>X &gt; 64.7</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.055581457996603</v>
+        <v>2.768052883539887</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.71634037393251</v>
+        <v>1.874896856897507</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.398857039187227</v>
+        <v>2.777700058134293</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.797510162601625</v>
+        <v>2.18529785932607</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.019755404340074</v>
+        <v>1.693989988913906</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.871900161866023</v>
+        <v>1.85092359491199</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.65798719226138</v>
+        <v>1.658007001678762</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.161025747508305</v>
+        <v>2.172770172770164</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.979298643708731</v>
+        <v>2.364581146336342</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.322454396243671</v>
+        <v>2.824316118171069</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.819728324119872</v>
+        <v>3.487382689779707</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.657050349243306</v>
+        <v>4.253946801665599</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.426745425244327</v>
+        <v>4.293164111585824</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.540487977369168</v>
+        <v>4.439853643850974</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.105558965502901</v>
+        <v>4.0445507937768</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.249053030303031</v>
+        <v>3.475665671630487</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.115135893325558</v>
+        <v>3.003320596797664</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.452259475218668</v>
+        <v>2.282587206313806</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.333329427571563</v>
+        <v>2.454959777709924</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.743389523253867</v>
+        <v>2.627364366239938</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.316914783859268</v>
+        <v>3.443084100750134</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.352675965307306</v>
+        <v>3.038974210373802</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.185186392075082</v>
+        <v>4.050152555301302</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.220961281708945</v>
+        <v>3.668715315397804</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 67.64</t>
+          <t>X &gt; 66.92</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.459948642536204</v>
+        <v>2.723357926620864</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.727293860101504</v>
+        <v>1.326555950252029</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.676542715579799</v>
+        <v>2.757283843245354</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.626718669611861</v>
+        <v>2.292758882288801</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.086684165234345</v>
+        <v>2.656586931447769</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.008398361941808</v>
+        <v>2.685643299594197</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.899579651526253</v>
+        <v>2.605593166616543</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.947628153722782</v>
+        <v>3.530358530358519</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.32598536216269</v>
+        <v>3.093954468777696</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.420443691431231</v>
+        <v>2.631862205452123</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.827129328288123</v>
+        <v>2.852815677772348</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.874639871789732</v>
+        <v>4.200077744052294</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.41460777840841</v>
+        <v>3.939026664180503</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.72403288074166</v>
+        <v>4.417640981508754</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.596393561940936</v>
+        <v>4.464215569274465</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.466642552849457</v>
+        <v>3.424530239013436</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.200099421177015</v>
+        <v>2.623419260700388</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.493136701440712</v>
+        <v>2.570714379686876</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.576402087670083</v>
+        <v>3.385720406336148</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.426377871112905</v>
+        <v>3.681581233709821</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.812213666011594</v>
+        <v>4.499404007426868</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.399497678077303</v>
+        <v>4.684997678431166</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.071850374644242</v>
+        <v>5.580522646108498</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.128644116115915</v>
+        <v>5.679139844778625</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 69.9</t>
+          <t>X &gt; 69.15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.319152886568034</v>
+        <v>2.793251134484819</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.704376088218211</v>
+        <v>1.631313764429805</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.506357039187229</v>
+        <v>2.514024242690894</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.913403019744493</v>
+        <v>2.379637311058246</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.897612547197213</v>
+        <v>2.256750926684106</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.3645787332946</v>
+        <v>2.719028044132564</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.712630049404247</v>
+        <v>3.083691112087536</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.714418604651165</v>
+        <v>4.248346514808993</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.595905786565872</v>
+        <v>4.469991073832155</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.142990110529382</v>
+        <v>4.228772633940629</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.097049752691305</v>
+        <v>4.442163267119938</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.458300349243302</v>
+        <v>5.031054822189944</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.815138282387188</v>
+        <v>4.629986441161783</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.954059405940605</v>
+        <v>4.324985153976392</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.415916108360044</v>
+        <v>4.824277889293377</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.410303030303034</v>
+        <v>3.469917233430429</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.316385893325553</v>
+        <v>2.531379399585923</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.851545189504378</v>
+        <v>3.116451690587489</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.067436570428704</v>
+        <v>3.739580458432769</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.214282380396725</v>
+        <v>4.832127255550688</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.591736212430696</v>
+        <v>6.239136732329086</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.995890251021599</v>
+        <v>6.320224210373802</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.590364963503646</v>
+        <v>7.032608695652179</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.514532710280371</v>
+        <v>6.870469701362715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 72.16</t>
+          <t>X &gt; 71.38</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.027864543009748</v>
+        <v>3.245136178199147</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.102085699670162</v>
+        <v>2.234410986854748</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.504557448185182</v>
+        <v>2.891762774064503</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.814098316268002</v>
+        <v>2.872974341986684</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.478307843720728</v>
+        <v>2.597416201887349</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.278770962333446</v>
+        <v>3.327963574615829</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.551812053494224</v>
+        <v>4.753345581488922</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.88709754125648</v>
+        <v>5.141904374150052</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.133083700676295</v>
+        <v>5.773672055427248</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.587161889670483</v>
+        <v>6.446792043830264</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.861221531832406</v>
+        <v>6.842519667476338</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.377973150879299</v>
+        <v>6.689908049741334</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.254811084023181</v>
+        <v>5.893265223820414</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.193241410030581</v>
+        <v>4.605293072525029</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.966590954985811</v>
+        <v>5.408537806653719</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.333984011898124</v>
+        <v>5.121850684629493</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.586569942405312</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.890727193594358</v>
+        <v>4.353315340370038</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.311117552023795</v>
+        <v>4.88856341610181</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.315959272012265</v>
+        <v>6.407514436067387</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>8.001170131150303</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.15155487269849</v>
+        <v>8.12247126341898</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.630528562685654</v>
+        <v>8.759033057145309</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>8.372692219482822</v>
+        <v>9.186285025527745</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 74.43</t>
+          <t>X &gt; 73.6</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.015483635922038</v>
+        <v>4.634943365347347</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.90551303912261</v>
+        <v>3.688101950204228</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.017881586990846</v>
+        <v>3.835277007191145</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.821723433181184</v>
+        <v>2.775585088756756</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.48593296063391</v>
+        <v>2.733671808470511</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.706490877997439</v>
+        <v>3.357895134094754</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.484929791006316</v>
+        <v>4.106401294069791</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.273901808785538</v>
+        <v>5.821799483771315</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.832184856333313</v>
+        <v>6.332495584839016</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.576065045929894</v>
+        <v>6.62856395643432</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.366920553724903</v>
+        <v>7.525269286396167</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.05457941901075</v>
+        <v>7.165216748303024</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.931417352154632</v>
+        <v>6.441516894814164</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.867961214726122</v>
+        <v>4.681576012885635</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.985011715595178</v>
+        <v>6.060451293462229</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.804204839088555</v>
+        <v>5.343364064037601</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2.411889769294547</v>
+        <v>4.761014752791063</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.082242863922978</v>
+        <v>5.106599547150992</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.81493011048039</v>
+        <v>6.277999573339841</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>5.552163517347637</v>
+        <v>7.449523817441872</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>9.513658263429562</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>7.000954850504804</v>
+        <v>9.67773019123505</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>9.921364676513427</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.49158697384626</v>
+        <v>10.47692903150625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 76.69</t>
+          <t>X &gt; 75.83</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.333511860927011</v>
+        <v>4.84060680482353</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.716683780525905</v>
+        <v>4.295298771514879</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.842767295597483</v>
+        <v>3.938808262437668</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.847761994103465</v>
+        <v>2.747603668419856</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.435048444633104</v>
+        <v>2.771446725925315</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.942527451243315</v>
+        <v>2.9283803319234</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.452630049404242</v>
+        <v>3.03150191250505</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.738521168753735</v>
+        <v>5.307905307905301</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.741546812206892</v>
+        <v>6.52668410362002</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.968631136170401</v>
+        <v>6.223844125162593</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.922177957819507</v>
+        <v>6.193964336141555</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.720351631294584</v>
+        <v>4.708923167168749</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.994625461874371</v>
+        <v>4.085654230162909</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1110687991876063</v>
+        <v>0.6846155265634479</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.8333520057959305</v>
+        <v>1.403602815669572</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.427738927738922</v>
+        <v>2.15137658909503</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.61433461127428</v>
+        <v>2.353306574923543</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.150519548478741</v>
+        <v>2.526232867315457</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.648462211454337</v>
+        <v>3.963936684675296</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>4.155820841935189</v>
+        <v>5.095954322394839</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>5.215838776533268</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.422044097175437</v>
+        <v>6.899830479486958</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.376005989144673</v>
+        <v>8.06089615742588</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>7.902737838485514</v>
+        <v>9.427809150904004</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 78.95</t>
+          <t>X &gt; 78.05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.266986987950517</v>
+        <v>5.034779129629989</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.932210189600703</v>
+        <v>4.370462252085119</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.180827085270181</v>
+        <v>6.463048484921565</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.163725600389647</v>
+        <v>3.360186035067322</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.053741579455277</v>
+        <v>6.013498187855006</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.08402573790289</v>
+        <v>6.588841835694105</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.851247560924982</v>
+        <v>4.956939739779372</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.955524595434568</v>
+        <v>6.591121297003639</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.997011777349272</v>
+        <v>7.8306340807437</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.224096101312782</v>
+        <v>6.612641657254329</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.576496757299601</v>
+        <v>6.462935743588616</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.45442938150137</v>
+        <v>4.498590076037146</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.409608328470142</v>
+        <v>1.273993317236169</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.806040972760869</v>
+        <v>-1.083945385547146</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.14789767518031</v>
+        <v>-0.2499730421229103</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.742284597123302</v>
+        <v>0.5637651634980543</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>2.608367460145828</v>
+        <v>1.7364804964539</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.425185742499771</v>
+        <v>3.305724050866765</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.484395095774325</v>
+        <v>4.796782022693392</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.367093440304558</v>
+        <v>4.585836552858758</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>4.667865244688763</v>
+        <v>5.720519711052489</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.974507762542338</v>
+        <v>6.49642101888444</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>6.248982475024391</v>
+        <v>7.165587419056429</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>7.094809207976233</v>
+        <v>7.003448424766965</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 81.21</t>
+          <t>X &gt; 80.28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.35915288656803</v>
+        <v>8.88511893662929</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.738661802503927</v>
+        <v>6.905108054682643</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.30064275347294</v>
+        <v>10.27469140943845</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.01626016260164</v>
+        <v>9.104254528549319</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.96618397576864</v>
+        <v>9.984765752611821</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.29600730472316</v>
+        <v>10.71973404069083</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.52405862083281</v>
+        <v>8.19054798221535</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>13.53156146179401</v>
+        <v>10.77580094921136</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.85876292942301</v>
+        <v>10.90372985889547</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.22870439624366</v>
+        <v>10.68571304575704</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.07419260983415</v>
+        <v>10.95794806036137</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.22401463495758</v>
+        <v>9.525296741728226</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.957995425244327</v>
+        <v>7.254335260115603</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.594059405940598</v>
+        <v>6.428066516601568</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>6.793058965502901</v>
+        <v>5.167877452635601</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.816017316017309</v>
+        <v>5.729181471455263</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.682100179039836</v>
+        <v>6.203335741811166</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>7.148688046647237</v>
+        <v>7.804555682892342</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>7.936007999000132</v>
+        <v>9.753121956280893</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>6.408568094682437</v>
+        <v>8.2336043550971</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.866021926716407</v>
+        <v>8.822229217878217</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.933033108164459</v>
+        <v>8.747066695922932</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.778936392075082</v>
+        <v>10.14677054536316</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>9.417389853137514</v>
+        <v>10.56266623315462</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 83.48</t>
+          <t>X &gt; 82.51</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.480365007780158</v>
+        <v>10.22548921391838</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.115285179127312</v>
+        <v>7.081031653576844</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.465144917975103</v>
+        <v>10.17416363864178</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.752190898532362</v>
+        <v>9.581761439833556</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.44670345628812</v>
+        <v>12.92939170553132</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.66397267268853</v>
+        <v>13.81096299268882</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.13444823122241</v>
+        <v>10.84196793697785</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>13.12896405919662</v>
+        <v>13.43559821820691</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.65529972595981</v>
+        <v>12.11425176557217</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.12480829234755</v>
+        <v>11.31820027035283</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.15644369208524</v>
+        <v>12.31507296611659</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.724229191478095</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.503150315031505</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.087431259875196</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.924242424242422</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.790325287264949</v>
+        <v>8.276721014492757</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.685484583443767</v>
+        <v>8.868474590490578</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.386224449216577</v>
+        <v>8.35829913647693</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.057918744033095</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.7577968184913075</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.6819508570822066</v>
+        <v>5.756365514721629</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.9564255695642601</v>
+        <v>6.724637681159429</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.153320589068251</v>
+        <v>8.011774049188809</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 85.74</t>
+          <t>X &gt; 84.73</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.156905695556794</v>
+        <v>8.413895011019832</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.574937885971032</v>
+        <v>4.907118610098578</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.631300859411944</v>
+        <v>8.000250595163521</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.918346839969203</v>
+        <v>8.494804918094417</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.95334288427587</v>
+        <v>12.56707286495161</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.14030907037325</v>
+        <v>12.7240064709497</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.244764880864913</v>
+        <v>8.668054893499587</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.21374444734779</v>
+        <v>9.450090971830093</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.008040618026541</v>
+        <v>8.491063359775076</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.111529436372081</v>
+        <v>5.52109882107748</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.385589078534004</v>
+        <v>6.880290357420932</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.859648663850045</v>
+        <v>4.429795359471377</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.736486596993927</v>
+        <v>3.314903242020605</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.88619423740127</v>
+        <v>5.240582224065754</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.228050939820712</v>
+        <v>4.558427842180699</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>4.575246850527748</v>
+        <v>4.032775339261242</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.317734207932297</v>
+        <v>3.928894927536234</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.336489009729092</v>
+        <v>5.969923865852891</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.428784885035441</v>
+        <v>6.184386092998665</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.8787513274684429</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.668488506670421</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-3.744334468079522</v>
+        <v>0.3215829060259736</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-2.346264249979498</v>
+        <v>2.739130434782609</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.9486900136511665</v>
+        <v>5.837861005710543</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 88</t>
+          <t>X &gt; 86.96</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>7.228718103959345</v>
+        <v>9.314516129032256</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.995390580971844</v>
+        <v>4.782895007614108</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.803748343535055</v>
+        <v>7.813915191436806</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.090794324092315</v>
+        <v>7.221512992628583</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.5521053008204</v>
+        <v>11.23166913824353</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.73907148691778</v>
+        <v>9.960031315670186</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.17002135375207</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.891809908998994</v>
+        <v>6.002886002885994</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>3.086614970082614</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.09068515800306898</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>2.912899985650739</v>
+        <v>2.538718870028497</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.254756688070181</v>
+        <v>3.285135916714864</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>4.298418972332009</v>
+        <v>2.417868506963103</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>2.313988095238095</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>4.059661131533353</v>
+        <v>5.038246847219355</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.275552512457679</v>
+        <v>5.252709074365129</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.1145722354691898</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-4.775800019453357</v>
+        <v>-2.243006124813775</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-6.300921343181294</v>
+        <v>-0.8895972181976219</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-7.475721993018091</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-4.653003521603679</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 22.39</t>
+          <t>X &lt; 22.41</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.096839856334164</v>
+        <v>0.4971807218998165</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.557371531940852</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.742968237135798</v>
+        <v>5.792941564057159</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.803097709672102</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.49269467532357</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>10.5935207320089</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.993259184361307</v>
+        <v>6.002886002885994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.933297090913698</v>
+        <v>8.987957769712956</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.26183069023952</v>
+        <v>5.334763417350764</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.086614970082614</v>
+        <v>4.178427003383675</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.05424237822882</v>
+        <v>11.04470219176952</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.38035567369153</v>
+        <v>11.35838150289018</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.05782752188263</v>
+        <v>13.96729029859991</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>12.39968422430207</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>17.34189723320158</v>
+        <v>18.13215422124883</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>14.30942937158642</v>
+        <v>15.17113095238096</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>17.10313939240292</v>
+        <v>17.89538970436222</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>18.76830613564609</v>
+        <v>19.53842336007941</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>16.05660122097645</v>
+        <v>16.89586694799553</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>16.96333041532925</v>
+        <v>17.75699387518624</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>16.88748445392014</v>
+        <v>17.68183135323095</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>17.1619591664022</v>
+        <v>17.92546583850933</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>14.18757618854124</v>
+        <v>14.90618398707701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 24.65</t>
+          <t>X &lt; 24.63</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.004483477068326636</v>
+        <v>-0.3316175537986652</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3392602754181411</v>
+        <v>0.3399068031580086</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.8681884153582331</v>
+        <v>0.002643893926979501</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.96431211065358</v>
+        <v>3.997397658421505</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.628521638106307</v>
+        <v>3.72183951832217</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>3.878773124320254</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.679902776676975</v>
+        <v>6.75341588272974</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.583509513742079</v>
+        <v>3.696201861339475</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.170451241111323</v>
+        <v>8.411286734326332</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.306626474165753</v>
+        <v>8.532666431767552</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.671595207236756</v>
+        <v>7.887470253711328</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.93830034924331</v>
+        <v>12.19804426254278</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.72422919147809</v>
+        <v>12.00058333775257</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.41224122412241</v>
+        <v>12.66978046898</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>10.84500701745095</v>
+        <v>11.0701948944344</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12.34848484848484</v>
+        <v>12.54893010591461</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>5.850931347871011</v>
+        <v>6.023031345565748</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.65518155314075</v>
+        <v>6.807578433064705</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>7.780163843155968</v>
+        <v>7.939471852871023</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>8.876100562214901</v>
+        <v>9.071489490590565</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>11.0608271215216</v>
+        <v>11.25633856719148</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>12.80316297829433</v>
+        <v>13.01603843055728</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>12.16854678168546</v>
+        <v>12.34224172317511</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>9.365441801189469</v>
+        <v>9.427809150904004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 26.92</t>
+          <t>X &lt; 26.86</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.421334918310016</v>
+        <v>-2.027475212959082</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3170873264159226</v>
+        <v>-0.4552002304811325</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.683918014796987</v>
+        <v>0.7143480918697165</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.849012775842048</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.342490595977701</v>
+        <v>5.300933207507597</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.748968977197038</v>
+        <v>7.276048631687502</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9.416044683550588</v>
+        <v>8.299148437636603</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.918321043675562</v>
+        <v>7.388167388167389</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.00858871339514</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.84542913491961</v>
+        <v>10.3564084389958</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.11948877708154</v>
+        <v>9.416522241478901</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.49927595899941</v>
+        <v>13.38236452943185</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>15.20538218482621</v>
+        <v>13.4795936241023</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.37454721081865</v>
+        <v>13.23135956266919</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>12.49689171811614</v>
+        <v>12.54920518078413</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>14.31079083518108</v>
+        <v>14.322630411725</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9.298824917715791</v>
+        <v>9.976325757575758</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>9.193984213894609</v>
+        <v>9.843441652414157</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>9.409875594818935</v>
+        <v>10.05790387955993</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>11.4259896974699</v>
+        <v>12.09067214280073</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>13.32246791974777</v>
+        <v>13.94747006566242</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>13.85637805589965</v>
+        <v>14.47836814976774</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>13.52109667082073</v>
+        <v>14.11594202898551</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>10.39648392979257</v>
+        <v>10.92350000439301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 29.18</t>
+          <t>X &lt; 29.08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.220679046205078</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.874783575647321</v>
+        <v>-2.149189301519385</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.472466490224534</v>
+        <v>-3.403883403410966</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5960920953747362</v>
+        <v>-0.7175970776290228</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.940973891735034</v>
+        <v>1.056025110140496</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.228780413966859</v>
+        <v>3.671975109581204</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.717335931757184</v>
+        <v>4.106401294069791</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.960132890365458</v>
+        <v>6.260497244103796</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.942796542868393</v>
+        <v>8.437606481656751</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.43038506851258</v>
+        <v>9.280899248732496</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>9.02377244176693</v>
+        <v>7.50395393546799</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.10636757613406</v>
+        <v>10.91589657116063</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>14.76471811431997</v>
+        <v>13.89936510944755</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>14.54363923787338</v>
+        <v>14.06096711358821</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>12.62499173861213</v>
+        <v>12.96897666612939</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>12.37904252610134</v>
+        <v>13.12044461937528</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>10.98462118744321</v>
+        <v>11.78705601092896</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>10.03944434916824</v>
+        <v>11.65417190576736</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.414999595638783</v>
+        <v>11.04896200176559</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>11.70268574174126</v>
+        <v>13.31272877469343</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>13.26097990990969</v>
+        <v>14.79446460118155</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>12.34479781404681</v>
+        <v>13.89962994807872</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>13.03944059375574</v>
+        <v>14.55310049893087</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>11.70310413885181</v>
+        <v>13.16145330792009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 31.44</t>
+          <t>X &lt; 31.31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.697450887016871</v>
+        <v>-2.459035396841244</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.717762276561658</v>
+        <v>-2.3953447093253</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.784712143202711</v>
+        <v>-4.578831380876323</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.409615848180046</v>
+        <v>-1.76566082426659</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.430940911922285</v>
+        <v>-1.73162144114611</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9572831358103144</v>
+        <v>0.2828973041708593</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.757661495945122</v>
+        <v>1.035802908037205</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.366242504022232</v>
+        <v>3.207662650387107</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.294522138767121</v>
+        <v>4.883579176170279</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.408398915560824</v>
+        <v>5.635515297050013</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.94032019294287</v>
+        <v>7.146140404533611</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.862828651130101</v>
+        <v>9.346338635820814</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>10.9409244459092</v>
+        <v>10.70822670412857</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>11.34877638707268</v>
+        <v>11.3887852123549</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>11.63402931590721</v>
+        <v>11.9450209233491</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.28502001143511</v>
+        <v>11.88712989572913</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>8.635379604017373</v>
+        <v>9.306469298245609</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>9.473935126611295</v>
+        <v>10.72157280918307</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>8.746430281120517</v>
+        <v>10.00724246666941</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.5056031351137</v>
+        <v>12.07941405104728</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.90645319356278</v>
+        <v>12.44076211932598</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>11.14507264095869</v>
+        <v>12.67519712059052</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>12.04847817105082</v>
+        <v>13.22842912908872</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>11.02924969141245</v>
+        <v>12.1374975651398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 33.7</t>
+          <t>X &lt; 33.54</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.763654130975823</v>
+        <v>-3.050015890672178</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.098430929325637</v>
+        <v>-3.295922726376048</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.536449978356629</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.991258634390853</v>
+        <v>-2.433659421164514</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.327049106938126</v>
+        <v>-2.709217561263848</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.7477830757506325</v>
+        <v>-1.320756861669715</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2390622102082673</v>
+        <v>-0.3917009428679492</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.468388453897397</v>
+        <v>1.273821963477126</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.2636444800332</v>
+        <v>1.648056291880451</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.500779055252991</v>
+        <v>3.068753565134024</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.528607541636028</v>
+        <v>4.079904835895988</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.511164670851343</v>
+        <v>6.266377068616812</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.900565418065575</v>
+        <v>7.860844557077364</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.930742823026023</v>
+        <v>8.105221333082675</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>9.533906058108776</v>
+        <v>9.63981571967053</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>8.620755291609569</v>
+        <v>8.969592644894135</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>6.979300466189883</v>
+        <v>7.387879720853853</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>7.879484887996838</v>
+        <v>8.732828128007526</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>7.592863706107089</v>
+        <v>8.454679517714865</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>9.287247204517328</v>
+        <v>10.14709847508914</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.498469880772411</v>
+        <v>10.31857022986603</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>10.17639276358441</v>
+        <v>11.2286293827876</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>11.20463632028756</v>
+        <v>11.96487470550439</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>10.12377894143615</v>
+        <v>11.31012487377651</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 35.96</t>
+          <t>X &lt; 35.76</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.466934069953709</v>
+        <v>-1.668859469727956</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.185110077789687</v>
+        <v>-2.900959599317424</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.136415238040492</v>
+        <v>-3.169460407323406</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.563104916763457</v>
+        <v>-1.986714677137549</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.380876518409146</v>
+        <v>-3.84018208745384</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.096138398179519</v>
+        <v>-1.316384576130318</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3607432040887701</v>
+        <v>-1.125273294477424</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3590493431741208</v>
+        <v>0.3449541911080374</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7997381218952171</v>
+        <v>0.2756444420150217</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.623628833084268</v>
+        <v>1.254740875789764</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.696091668858969</v>
+        <v>2.118691866725463</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.411354241458874</v>
+        <v>4.997928452688086</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.685397763425122</v>
+        <v>5.263706946677161</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.86352048378491</v>
+        <v>5.804427520352526</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>6.802183573429907</v>
+        <v>6.700182408684448</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>7.396570495372899</v>
+        <v>7.45872508628122</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.66584697116987</v>
+        <v>5.974174063116372</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>6.159808662558262</v>
+        <v>6.827483251840377</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.375700043482588</v>
+        <v>7.04194547898615</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>7.560549845466596</v>
+        <v>8.43996387670785</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>7.816406871113337</v>
+        <v>8.661474010435597</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>8.538964103317007</v>
+        <v>9.375266123588794</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>9.013039614202256</v>
+        <v>10.01337792642141</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>8.737606562575785</v>
+        <v>10.04847759090907</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 38.23</t>
+          <t>X &lt; 37.99</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.198539421124281</v>
+        <v>-2.264671456545095</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.895367089951918</v>
+        <v>-4.42751119959722</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.323610806471933</v>
+        <v>-3.605527985194861</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.537224999579188</v>
+        <v>-2.280997276654844</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.397871323770531</v>
+        <v>-3.674766279373998</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.186568278013965</v>
+        <v>-1.760644174973351</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.383939529883783</v>
+        <v>-1.757004142477641</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.04402799729058415</v>
+        <v>-0.3047360874836968</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3210837800933817</v>
+        <v>-0.1768071777995885</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.166291081403159</v>
+        <v>0.7843298253836224</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.411224509972854</v>
+        <v>2.015031293662084</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.721471870278904</v>
+        <v>4.294359882321778</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.378245078503703</v>
+        <v>4.936656263273569</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.966227690730236</v>
+        <v>5.487144246568882</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.117145881822815</v>
+        <v>5.763456318357946</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.387908208296565</v>
+        <v>6.324760337177608</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.930366475849837</v>
+        <v>5.741646698615547</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.340088878824773</v>
+        <v>5.608762593453946</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>5.717792557483712</v>
+        <v>6.142713638491088</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.390075260655621</v>
+        <v>6.996277719332824</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.17115368815886</v>
+        <v>6.748322035843472</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.471881558616609</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.693407034701067</v>
+        <v>7.396027226003618</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.45576248374315</v>
+        <v>7.393632640659838</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 40.49</t>
+          <t>X &lt; 40.21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.104654083941348</v>
+        <v>-3.076581455141223</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.908509817822051</v>
+        <v>-3.721955667675985</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.935148337156861</v>
+        <v>-3.645091846797932</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.425385674737342</v>
+        <v>-1.973845576897759</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.766969663045373</v>
+        <v>-3.447805847489768</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.214692521766139</v>
+        <v>-1.160379565060268</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.506829410055218</v>
+        <v>-1.422838408185129</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.7039597737272132</v>
+        <v>-0.3962009288241006</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1219320512719619</v>
+        <v>0.131195357690892</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1862333537726286</v>
+        <v>0.4003902006872764</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6744245835438036</v>
+        <v>0.8057810075685694</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.23640333027312</v>
+        <v>2.52653593725173</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.687594184693836</v>
+        <v>2.876357534847564</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.280626570119708</v>
+        <v>3.560214019353204</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.165224113787453</v>
+        <v>3.676994391129931</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.623925825418368</v>
+        <v>4.105142617672627</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>2.811582636880516</v>
+        <v>3.202327452285836</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.435371512435168</v>
+        <v>3.468910723955133</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.92263331398366</v>
+        <v>3.816528743377873</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.516534754887914</v>
+        <v>4.5637383575447</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.245359007546035</v>
+        <v>4.262605440717905</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.440883466761079</v>
+        <v>4.453754503316546</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>3.443987758618988</v>
+        <v>4.431077404040998</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.368155505395713</v>
+        <v>4.53524999430546</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 42.75</t>
+          <t>X &lt; 42.44</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.198369237325771</v>
+        <v>-3.377246353248417</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.584704753420766</v>
+        <v>-4.505181854883929</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.418077550613219</v>
+        <v>-3.224043542222041</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.296408301010231</v>
+        <v>-2.934417075098622</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.573498563913901</v>
+        <v>-4.31251104761251</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.326589231110304</v>
+        <v>-2.060759360026765</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.258951242355216</v>
+        <v>-2.304573456052211</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.869011239446827</v>
+        <v>-1.837718816770639</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9853205233560871</v>
+        <v>-1.048268407637799</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.137367032327759</v>
+        <v>-1.182798403408412</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.134905554571269</v>
+        <v>-1.241324138528448</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6791493151862227</v>
+        <v>-0.5256238438266365</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1703040468401369</v>
+        <v>-0.09696579589704157</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.01109976468499951</v>
+        <v>0.2060680588771291</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2498174536515165</v>
+        <v>0.4059423429237157</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.8442043755945079</v>
+        <v>1.187753528226288</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.5981796152986547</v>
+        <v>0.7531123667769251</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.4933389114774727</v>
+        <v>0.7304818448567687</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.450197513189643</v>
+        <v>1.606465571451281</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.930237436576512</v>
+        <v>2.041559182993169</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.500050819172273</v>
+        <v>1.584368264853893</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.424204857763172</v>
+        <v>1.61945932614006</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.586320019683434</v>
+        <v>1.642586644935527</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.510487766460159</v>
+        <v>1.811208400370433</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 45.01</t>
+          <t>X &lt; 44.66</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1023</v>
+        <v>1041</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.01764481237732</v>
+        <v>-2.822165633009732</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.263531781263552</v>
+        <v>-4.028687262181428</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.732567072244088</v>
+        <v>-3.45821325648415</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.530443134101667</v>
+        <v>-3.282123620518107</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.393090051455339</v>
+        <v>-4.134050636698134</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.518195833179398</v>
+        <v>-2.151948923111206</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.273985186854198</v>
+        <v>-2.274600579916445</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.499326569094009</v>
+        <v>-2.387398064631498</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.825157015366493</v>
+        <v>-1.97128471690705</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.157590160263652</v>
+        <v>-1.998844377352121</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.313443954956334</v>
+        <v>-2.110855280134913</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.860149263159798</v>
+        <v>-1.522883920485185</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.376908274353838</v>
+        <v>-0.9086694096938857</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.250600788234159</v>
+        <v>-0.7726575537398546</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.9775921520869986</v>
+        <v>-0.5902586215038781</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1311755689187564</v>
+        <v>0.2592298353561304</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1099432205984954</v>
+        <v>0.347472382324689</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4279974312197723</v>
+        <v>0.8870186325905536</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.7025585216482142</v>
+        <v>1.101480859736327</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.338813630396729</v>
+        <v>1.604251742835665</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.051051950456113</v>
+        <v>1.32499167949527</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.9752059890470122</v>
+        <v>1.249829157539985</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.6631704375994474</v>
+        <v>1.013156246084456</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.3918347630662993</v>
+        <v>0.9470787311417723</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 47.28</t>
+          <t>X &lt; 46.89</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.640847113431967</v>
+        <v>-2.462892508841499</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.516908315451509</v>
+        <v>-3.165092167305737</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.827666333099913</v>
+        <v>-3.505405554317854</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.745644599303127</v>
+        <v>-3.349678077315602</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.790146650127205</v>
+        <v>-4.290240373690906</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.802617919425067</v>
+        <v>-2.304545337933895</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.692261072873812</v>
+        <v>-2.351497674356139</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.254332443127552</v>
+        <v>-1.908288441954276</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.57939622685695</v>
+        <v>-1.281606415063195</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.969688310965168</v>
+        <v>-1.74515583214454</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.068664533022982</v>
+        <v>-1.888548415212689</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.0482429644657</v>
+        <v>-1.749502772011503</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.029979562730652</v>
+        <v>-1.534386576910329</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.528939751599424</v>
+        <v>-1.200742001601952</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.379429591471322</v>
+        <v>-1.051641188142035</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.073072497123128</v>
+        <v>-0.8228392474603652</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.9042897823501193</v>
+        <v>-0.6773431005818864</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4523263235979016</v>
+        <v>-0.2283485690020015</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.1017004854088626</v>
+        <v>0.1523646972127608</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.3894559621071423</v>
+        <v>0.6163277008752459</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>0.2982597580979984</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.3301275391571892</v>
+        <v>0.5555993142806983</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.1808734380799208</v>
+        <v>0.383606201886586</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2339418659908148</v>
+        <v>0.05521616852814049</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 49.54</t>
+          <t>X &lt; 49.12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1323</v>
+        <v>1343</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.039953591466215</v>
+        <v>-2.018463159337365</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.93240483577582</v>
+        <v>-2.672462135243038</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.139220887732975</v>
+        <v>-2.811084808563187</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.290776084733125</v>
+        <v>-2.99229404917547</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.587107393056712</v>
+        <v>-3.342312353087166</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.015331580606755</v>
+        <v>-1.845095798466602</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.998753645434952</v>
+        <v>-1.821116008763362</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.711808940259019</v>
+        <v>-1.45589497786073</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.10431893253525</v>
+        <v>-0.8812050853024616</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.310383202813945</v>
+        <v>-1.156035433835278</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.593902985493244</v>
+        <v>-1.479481729729827</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.680318269375313</v>
+        <v>-1.458223028951686</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.559016488461793</v>
+        <v>-1.530672853029408</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.285639842179705</v>
+        <v>-0.9598451125265512</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.147605336335218</v>
+        <v>-0.9718580201003704</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.035962029937927</v>
+        <v>-1.006235311779584</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.050486751738504</v>
+        <v>-0.8867352320675153</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.4324367109481102</v>
+        <v>-0.2005575352931572</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.398223806929785</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2422735108419403</v>
+        <v>0.005110645474530884</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5890045283100491</v>
+        <v>-0.413413528281481</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3625073302331288</v>
+        <v>-0.1162752311749671</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.465961567108593</v>
+        <v>-0.2449415649583884</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.9197227696893933</v>
+        <v>-0.704921214497304</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 51.8</t>
+          <t>X &lt; 51.34</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1467</v>
+        <v>1485</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.387989009867738</v>
+        <v>-1.392089093701998</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.629728891593359</v>
+        <v>-2.34266940779564</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.417009964179776</v>
+        <v>-2.351437625329197</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.487782964083003</v>
+        <v>-2.234956463840867</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.78740431052362</v>
+        <v>-2.577854671280271</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.282168905031988</v>
+        <v>-1.074119718480837</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.611853407719316</v>
+        <v>-1.465161326673162</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.312067881835318</v>
+        <v>-1.096681096681095</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.624188871987208</v>
+        <v>-0.4973717156165236</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6145200383204212</v>
+        <v>-0.3506622680749132</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.046321946699351</v>
+        <v>-0.8191679942113268</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.489883932599511</v>
+        <v>-1.163090016022693</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8797769718500987</v>
+        <v>-0.6618205173118454</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9256149495546495</v>
+        <v>-0.6406943093846849</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.933058772834805</v>
+        <v>-0.6494480178690694</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.909914361001313</v>
+        <v>-0.6268645377699471</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.7320981311475876</v>
+        <v>-0.4613846801346781</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5247813411078681</v>
+        <v>-0.1228883139158157</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.4728221089450244</v>
+        <v>-0.04310622145017362</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4501317885405953</v>
+        <v>0.1041401562687412</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6117266369217162</v>
+        <v>-0.05926394107158472</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.4830736208257136</v>
+        <v>0.06759373899333099</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.7539295150239553</v>
+        <v>-0.2274923144488312</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.034260745752348</v>
+        <v>-0.5243114434184264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 54.06</t>
+          <t>X &lt; 53.57</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5857956917743721</v>
+        <v>-0.6550887341896257</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.433251030425843</v>
+        <v>-1.294616288875297</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.688627818474799</v>
+        <v>-1.604396259741343</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.156900010558545</v>
+        <v>-1.433437416280405</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.883855008897392</v>
+        <v>-1.952600915697651</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.056974664763658</v>
+        <v>-0.7603445325984666</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.066799215926657</v>
+        <v>-0.9464131465364289</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.067987227669612</v>
+        <v>-0.8859255509681816</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7491398061392971</v>
+        <v>-0.5143912819661765</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6969125658696456</v>
+        <v>-0.4578240195728469</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9357195717152678</v>
+        <v>-0.7946024032632693</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.362552269514303</v>
+        <v>-1.192987037393522</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.049578353810254</v>
+        <v>-0.7853456591073922</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.296184496498427</v>
+        <v>-0.9726783807110237</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.186719645148202</v>
+        <v>-0.9240166846423605</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.9837384837384775</v>
+        <v>-0.7890220446290286</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.08192809567872</v>
+        <v>-0.7710997766950953</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6620000427694634</v>
+        <v>-0.3558718233914036</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3488325427211407</v>
+        <v>-0.01960691658667457</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5541876318431704</v>
+        <v>-0.04862583084560157</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.693334210104517</v>
+        <v>-0.3724649729084248</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.3652862195666415</v>
+        <v>-0.2040221355458129</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7648311149277163</v>
+        <v>-0.5694010485621916</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.8406633681509916</v>
+        <v>-0.609737363192707</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 56.33</t>
+          <t>X &lt; 55.79</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1837</v>
+        <v>1823</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3864092436094779</v>
+        <v>-0.2859217472676789</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9616303703393783</v>
+        <v>-0.7764853710433783</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.294095303300658</v>
+        <v>-1.125419446527964</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7925452561175774</v>
+        <v>-0.5917702153914632</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.853223032317608</v>
+        <v>-1.659953775321227</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.151365171775524</v>
+        <v>-0.7350552762896854</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.569766065004828</v>
+        <v>-1.255864112439021</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.494047918027022</v>
+        <v>-1.176802109330914</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.58447238739415</v>
+        <v>-1.048873199646806</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.840793673254403</v>
+        <v>-1.351232977916055</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.91491347067268</v>
+        <v>-1.517835045045139</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.433994023051071</v>
+        <v>-1.739562364299751</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.28177563206868</v>
+        <v>-1.702507142200339</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.20117353013741</v>
+        <v>-1.841031933200092</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.177905029851345</v>
+        <v>-1.864930692485032</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.094425820022344</v>
+        <v>-1.632754484965425</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.142952142485626</v>
+        <v>-1.736634896690433</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.456554701917987</v>
+        <v>-1.046699473601905</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.317658486605524</v>
+        <v>-0.9419465168894803</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.207891532646755</v>
+        <v>-1.00163324791388</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.283826593442065</v>
+        <v>-1.130240667561203</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.218995494353813</v>
+        <v>-0.8214207429997558</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.729112445315067</v>
+        <v>-1.400605785971521</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.5327617916249</v>
+        <v>-1.178762333744253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 58.59</t>
+          <t>X &lt; 58.02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5249756431301194</v>
+        <v>-0.2812240797535637</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9312985342854319</v>
+        <v>-0.5991321899184925</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.271342765881002</v>
+        <v>-0.9440622263344238</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6902244790365941</v>
+        <v>-0.3802271140231142</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.096533794266193</v>
+        <v>-0.7760528694784696</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8337423989650432</v>
+        <v>-0.6682593126204353</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.187994950595758</v>
+        <v>-1.021080882592706</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.536621942490989</v>
+        <v>-1.22772122772124</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.614494995447821</v>
+        <v>-1.394632612877423</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.773391307563529</v>
+        <v>-1.601003518416164</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.81426140190753</v>
+        <v>-1.672748847792185</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.506144095201137</v>
+        <v>-2.342451195383866</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.524724597142686</v>
+        <v>-2.277982133473465</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.326077781712506</v>
+        <v>-2.182235850926233</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.171927028894856</v>
+        <v>-2.078149446570499</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.039584169304618</v>
+        <v>-2.057385968291371</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.998118522768657</v>
+        <v>-1.866426085176087</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.485578030917807</v>
+        <v>-1.262209453236949</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.339321779276602</v>
+        <v>-1.146027324371275</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.418739732625383</v>
+        <v>-1.177141125012533</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.490348350007842</v>
+        <v>-1.302325184132826</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.291547033779189</v>
+        <v>-1.230067558667969</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.72640669003966</v>
+        <v>-1.82181390877043</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.851451541688128</v>
+        <v>-1.709913779463243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.85</t>
+          <t>X &lt; 60.25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.028073553807133</v>
+        <v>-0.8235256045150976</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.071245002040946</v>
+        <v>-0.6410515494259741</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.278640725676432</v>
+        <v>-0.8821840309782019</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.251820593851221</v>
+        <v>-0.6851348150093202</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.205116759290483</v>
+        <v>-0.80087733374463</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.127704167332091</v>
+        <v>-0.5740742184353422</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.427128123457372</v>
+        <v>-0.9187057802176142</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.770025839793277</v>
+        <v>-1.358761358761363</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.882928816751026</v>
+        <v>-1.456057674302478</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.272256526241918</v>
+        <v>-1.801658719071369</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.242349080866347</v>
+        <v>-1.934829109872439</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.765469848243228</v>
+        <v>-2.301501154433822</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.696312099292193</v>
+        <v>-2.29026714575847</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.442777970519415</v>
+        <v>-2.178140846831226</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.266331082651192</v>
+        <v>-2.049484417905468</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.275452365380424</v>
+        <v>-1.938630849536253</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.158719819674893</v>
+        <v>-1.727195945945944</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.742658230837655</v>
+        <v>-1.274494465521968</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.635742177882868</v>
+        <v>-1.150122328466281</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.512924826810483</v>
+        <v>-1.025625973497391</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.623838370714857</v>
+        <v>-1.232710114517758</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.583262138518528</v>
+        <v>-1.217782546382949</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.823744193014164</v>
+        <v>-1.469643556600076</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.783229022571611</v>
+        <v>-1.470562295032053</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.11</t>
+          <t>X &lt; 62.47</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.313803088274732</v>
+        <v>-1.115442262091179</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.207167535942858</v>
+        <v>-0.7902227530036541</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.36412554578969</v>
+        <v>-1.008584657679009</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.130795133068268</v>
+        <v>-0.8173712001017606</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.191492870694432</v>
+        <v>-0.9006171800892986</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.191387653260023</v>
+        <v>-0.8050158199353206</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.309665032562975</v>
+        <v>-0.9655800656705793</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.522385432354724</v>
+        <v>-1.270500509079199</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.541561609311287</v>
+        <v>-1.354077521560903</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.912228744689479</v>
+        <v>-1.684815988015437</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.993476563098177</v>
+        <v>-1.62408689557693</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.375094764488793</v>
+        <v>-1.942970034481391</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.16842682507172</v>
+        <v>-1.8311278033704</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.986041774497849</v>
+        <v>-1.614048836038705</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.818617843558989</v>
+        <v>-1.492480713693645</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.705983889528191</v>
+        <v>-1.438790908071951</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.562246440992723</v>
+        <v>-1.331165397631139</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.26250886454968</v>
+        <v>-1.041037658461093</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.148668203546798</v>
+        <v>-0.9534789846148186</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.275286512249089</v>
+        <v>-1.077302015021139</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.370462519070358</v>
+        <v>-1.17943348763707</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.336969309046083</v>
+        <v>-1.103006322846674</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.50321099925555</v>
+        <v>-1.385045834407094</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.554425799457135</v>
+        <v>-1.353270239340375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.38</t>
+          <t>X &lt; 64.7</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2507</v>
+        <v>2516</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.229779919756083</v>
+        <v>-1.165447647286513</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8716302383930881</v>
+        <v>-0.7564289264779589</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.181048024103916</v>
+        <v>-1.078120607815485</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.001943240643328</v>
+        <v>-0.8161137994607159</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.078381118677683</v>
+        <v>-0.6334102268358279</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.027896514230157</v>
+        <v>-0.732420337480157</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9459436431472596</v>
+        <v>-0.6938381972714254</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.122648379098337</v>
+        <v>-0.8796637617598364</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.058876132545947</v>
+        <v>-0.8708297309959363</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.174820282171929</v>
+        <v>-1.031708538640835</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.354378818737267</v>
+        <v>-1.235853039717327</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.650425335552242</v>
+        <v>-1.472736701215226</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.559762432465867</v>
+        <v>-1.436378322437335</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.599027602402671</v>
+        <v>-1.446422626030035</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.439282619779867</v>
+        <v>-1.255214562500235</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.139677088981259</v>
+        <v>-1.051195180441198</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.091283159975951</v>
+        <v>-0.9565841272991946</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.8544953994331479</v>
+        <v>-0.732183595700171</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.8142194805267096</v>
+        <v>-0.6765145404480108</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9624280935180423</v>
+        <v>-0.8192127321496514</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.163004823425872</v>
+        <v>-1.029372596769761</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.175604368348665</v>
+        <v>-0.9622172113895076</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.475791336336862</v>
+        <v>-1.251558964260411</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.488530712136857</v>
+        <v>-1.191930934567331</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 67.64</t>
+          <t>X &lt; 66.92</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2649</v>
+        <v>2661</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.833960885887052</v>
+        <v>-0.9386552031949051</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7371364539008383</v>
+        <v>-0.4527014798564437</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.069073672423265</v>
+        <v>-0.8625002566321811</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.087256403260383</v>
+        <v>-0.6843920550619131</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.215011140958708</v>
+        <v>-0.7892367851014086</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.194806343570804</v>
+        <v>-0.8368369811981111</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.158397707534995</v>
+        <v>-0.8436307051425302</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.453161132684663</v>
+        <v>-1.111013611013618</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.278088207428127</v>
+        <v>-0.908009626254433</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.016078608959923</v>
+        <v>-0.7656226830353319</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.133814259329739</v>
+        <v>-0.7936879687312981</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.428854855566918</v>
+        <v>-1.145344998277672</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.290124875507544</v>
+        <v>-1.021498376989705</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.376606257842781</v>
+        <v>-1.11958228827266</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.335716698261479</v>
+        <v>-1.088523456944515</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.020317970826063</v>
+        <v>-0.7899822008876072</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.9439755524575801</v>
+        <v>-0.6310998498498606</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.026722230457963</v>
+        <v>-0.6513713423988392</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.052473000030986</v>
+        <v>-0.7747469530909115</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.295917393444199</v>
+        <v>-0.9355358834072973</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.401808282290261</v>
+        <v>-1.090067471875123</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.568772140528758</v>
+        <v>-1.218442237241668</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.762842583666156</v>
+        <v>-1.403717374971414</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.779072423732465</v>
+        <v>-1.506550215961603</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 69.9</t>
+          <t>X &lt; 69.15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2778</v>
+        <v>2788</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8739781380660219</v>
+        <v>-0.7886925364081634</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6184810546389201</v>
+        <v>-0.4432741720434521</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.858444675710949</v>
+        <v>-0.640937042942987</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9800637422283529</v>
+        <v>-0.5693928433900268</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9743645711438731</v>
+        <v>-0.5386951679373908</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.304033569995823</v>
+        <v>-0.6843869675872156</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.376529163475901</v>
+        <v>-0.7987093954415769</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.599024487689562</v>
+        <v>-1.067800387040812</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.573388878668645</v>
+        <v>-1.047359832784863</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.466752009814464</v>
+        <v>-0.9835044845789085</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.459052002951836</v>
+        <v>-0.9979050844496697</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.538402159717265</v>
+        <v>-1.095339779874024</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.386367633711771</v>
+        <v>-0.9562010839962412</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.192167279855667</v>
+        <v>-0.8461406273354797</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.291209833512937</v>
+        <v>-0.9191943284609465</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.070558419804655</v>
+        <v>-0.6086964723070025</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8244399594572016</v>
+        <v>-0.4617707213662925</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9440869944036692</v>
+        <v>-0.6304842783372848</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.9945397141562822</v>
+        <v>-0.6668282138572295</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.253956296813911</v>
+        <v>-0.9896835459390587</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.559878314717814</v>
+        <v>-1.234662981035292</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.65072845401437</v>
+        <v>-1.324825072780321</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.78709455430851</v>
+        <v>-1.41889722044678</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.770103718805295</v>
+        <v>-1.452701030344606</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 72.16</t>
+          <t>X &lt; 71.38</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2914</v>
+        <v>2919</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7978100007319355</v>
+        <v>-0.7079272745586849</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.9102288164139338</v>
+        <v>-0.4574778753962931</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.035448752976315</v>
+        <v>-0.5661258201831458</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.116372031380259</v>
+        <v>-0.5245187534031572</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.058364268350012</v>
+        <v>-0.4734315066655839</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.193565877892311</v>
+        <v>-0.6396461194502763</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.400832932513197</v>
+        <v>-0.9215567324356471</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.455274228113332</v>
+        <v>-0.986997189528843</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.49713620728869</v>
+        <v>-1.030125412927184</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.567938851219253</v>
+        <v>-1.141948375816725</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.616226639519148</v>
+        <v>-1.177616200760802</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.534016807284381</v>
+        <v>-1.112083889067193</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.338707871458965</v>
+        <v>-0.9269417950913521</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9928078991209617</v>
+        <v>-0.6620044572771135</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.117795831427848</v>
+        <v>-0.7625645866818331</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.016582664426608</v>
+        <v>-0.714431967109519</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.890844507222198</v>
+        <v>-0.6130438191355907</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.9413315228243917</v>
+        <v>-0.6775050710642176</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.013632288769649</v>
+        <v>-0.6683114036173805</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.183716248801346</v>
+        <v>-1.001107784422238</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.432082779684485</v>
+        <v>-1.206534041113763</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.487895757208854</v>
+        <v>-1.296013807428317</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.570732806650717</v>
+        <v>-1.340678975580701</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.695268250598147</v>
+        <v>-1.482990387708881</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 74.43</t>
+          <t>X &lt; 73.6</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3016</v>
+        <v>3010</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7616105224480876</v>
+        <v>-0.7804699302277029</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7169010678054804</v>
+        <v>-0.5787387259587433</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7873670306185048</v>
+        <v>-0.5910595094663904</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7906286008088728</v>
+        <v>-0.4038417850440723</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7457482435770828</v>
+        <v>-0.3961167889792918</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9029756503573552</v>
+        <v>-0.5189992627639626</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9972545532993493</v>
+        <v>-0.651390751471169</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.223998281892371</v>
+        <v>-0.8900421425272427</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.295971481662434</v>
+        <v>-0.8946513375482326</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.258330021483822</v>
+        <v>-0.9286087307132291</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.361689105017504</v>
+        <v>-1.020853504047928</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.192479043094878</v>
+        <v>-0.932955670580192</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.041485437467458</v>
+        <v>-0.7887357933324921</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6485050355663375</v>
+        <v>-0.5068174359451874</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6591252139540131</v>
+        <v>-0.6588193990098361</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6403318903318862</v>
+        <v>-0.5613987466580284</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5893898261583956</v>
+        <v>-0.5464693127831239</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6747023286954956</v>
+        <v>-0.626777783322531</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7702860379791048</v>
+        <v>-0.6913800040523057</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.9944593414575778</v>
+        <v>-0.9219356873253446</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.153331690848539</v>
+        <v>-1.138269507299192</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.176594838441623</v>
+        <v>-1.227294049918356</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.180957542296809</v>
+        <v>-1.196800138622145</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.370029623937128</v>
+        <v>-1.339663189002735</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 76.69</t>
+          <t>X &lt; 75.83</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3091</v>
+        <v>3101</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6543345893471866</v>
+        <v>-0.6391939401734774</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5866100987396976</v>
+        <v>-0.5151060926976498</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.754259927393754</v>
+        <v>-0.4685888214042748</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5817560930809762</v>
+        <v>-0.304865574212414</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7389147839924917</v>
+        <v>-0.3056627877809674</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7913427848784451</v>
+        <v>-0.3557968150679685</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.837588740814553</v>
+        <v>-0.3937594259559205</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.065523461650727</v>
+        <v>-0.6343918590784554</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.16690168284817</v>
+        <v>-0.6993269802526001</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.084385090758865</v>
+        <v>-0.6596343417528772</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.081919319473648</v>
+        <v>-0.6263502129691076</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.8589925930705817</v>
+        <v>-0.4344137389385665</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5775116209010136</v>
+        <v>-0.3270478956302512</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2637284044431496</v>
+        <v>0.06801170649405464</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3544064722851274</v>
+        <v>0.02915098816641404</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.418390096512077</v>
+        <v>-0.05283865657133902</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4364094585143405</v>
+        <v>-0.1377493564993628</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4898561666467387</v>
+        <v>-0.1872807632454965</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6424342306048914</v>
+        <v>-0.2435654174019675</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6950552609602951</v>
+        <v>-0.4287247244222243</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7984900319131896</v>
+        <v>-0.5907601748874072</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.9199067098578055</v>
+        <v>-0.6147479939445972</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.9174228760823695</v>
+        <v>-0.674515740195659</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.071310059049935</v>
+        <v>-0.8822713499110719</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 78.95</t>
+          <t>X &lt; 78.05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3186</v>
+        <v>3193</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5401927039586099</v>
+        <v>-0.4915681976000101</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6090403706346521</v>
+        <v>-0.3783809633784685</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8143289601891368</v>
+        <v>-0.5260937093197597</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6368901805050413</v>
+        <v>-0.260123476231314</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.830562179791869</v>
+        <v>-0.4560757851622341</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9695536012871813</v>
+        <v>-0.5313046012971583</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8812756639894559</v>
+        <v>-0.43579929294431</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.9545632816698841</v>
+        <v>-0.5535706409068908</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9579461347087275</v>
+        <v>-0.581599310761149</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9007598894706206</v>
+        <v>-0.4864980045346812</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8589114851955344</v>
+        <v>-0.4461494189455522</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7133569365603165</v>
+        <v>-0.2679065232744193</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5674078546162491</v>
+        <v>0.009224725875810691</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4572547367377524</v>
+        <v>0.2166766510790623</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4083718415617099</v>
+        <v>0.1905672551358961</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4527902696343489</v>
+        <v>0.1270665254394672</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4429501542785772</v>
+        <v>-0.0208333333333357</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4979284947061586</v>
+        <v>-0.1665046376196671</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6395392992046354</v>
+        <v>-0.1837244108488463</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4969401901361863</v>
+        <v>-0.2322442276602175</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5820361299963892</v>
+        <v>-0.2494427420138408</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6706593098315992</v>
+        <v>-0.3686940212380918</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6913670728942236</v>
+        <v>-0.3570281233835146</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7486939061665723</v>
+        <v>-0.4067774016751855</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 81.21</t>
+          <t>X &lt; 80.28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3228</v>
+        <v>3255</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.6725296726445151</v>
+        <v>-0.5835053126133403</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.6217777579356323</v>
+        <v>-0.41654699072933</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8122271405603882</v>
+        <v>-0.5865732090515934</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7694541231126522</v>
+        <v>-0.4905916965753434</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8726122757162429</v>
+        <v>-0.5355007718707867</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.945784791043053</v>
+        <v>-0.606072302679074</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8994500738623259</v>
+        <v>-0.4979916675719522</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.006222579072634</v>
+        <v>-0.6329178142079499</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.9165333130332698</v>
+        <v>-0.5795389537470612</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9317785507907956</v>
+        <v>-0.5630646646314901</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.9794945237665829</v>
+        <v>-0.5487980359588676</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9320700211270605</v>
+        <v>-0.4407147481928817</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8026449840530674</v>
+        <v>-0.2827697524680559</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7277441765177102</v>
+        <v>-0.2068510271493693</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.6263328876239029</v>
+        <v>-0.1050951757221057</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.6316252762482648</v>
+        <v>-0.138499427890892</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.6237068423776932</v>
+        <v>-0.2243319538115713</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.6484671790794252</v>
+        <v>-0.3391571042416359</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6926871536665686</v>
+        <v>-0.3520236162571351</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.6114106889101976</v>
+        <v>-0.3342211596623841</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5786878049013993</v>
+        <v>-0.3005348453259202</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.6361840523839817</v>
+        <v>-0.3575563392117047</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.6840110042882301</v>
+        <v>-0.3721824591389833</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.772555269893104</v>
+        <v>-0.4547991158415883</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 83.48</t>
+          <t>X &lt; 82.51</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3271</v>
+        <v>3290</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4532332700804247</v>
+        <v>-0.5393064745639577</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4074489952922633</v>
+        <v>-0.3465045783072185</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5533756461104673</v>
+        <v>-0.4675707644677445</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5507841574053103</v>
+        <v>-0.4090437617952389</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.6569163281827244</v>
+        <v>-0.5470296486148101</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7874309961064441</v>
+        <v>-0.6151975666929062</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.7213358873354139</v>
+        <v>-0.5166784126625785</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.799874063435233</v>
+        <v>-0.6231618754304833</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7411849012004197</v>
+        <v>-0.5084762047845501</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6749703156502207</v>
+        <v>-0.4703213284119485</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7183948270894547</v>
+        <v>-0.4835685850424269</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6142430561785659</v>
+        <v>-0.3189735026148384</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.531601510422071</v>
+        <v>-0.2350750254345684</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5214541569975353</v>
+        <v>-0.1928828615732456</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4604253550545891</v>
+        <v>-0.1297517115707549</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4578030996146225</v>
+        <v>-0.1568521029303369</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4516922030746855</v>
+        <v>-0.2428817864725588</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4469351278590707</v>
+        <v>-0.2972247200483338</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3961043331121985</v>
+        <v>-0.1862677303172973</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.3438855585345735</v>
+        <v>-0.227040502780774</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.288092742975536</v>
+        <v>-0.1389759308959384</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2846352607413181</v>
+        <v>-0.1353878795411489</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2975567968875552</v>
+        <v>-0.1168139722299202</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3858158069926318</v>
+        <v>-0.2305941284245208</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 85.74</t>
+          <t>X &lt; 84.73</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3314</v>
+        <v>3336</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3294896066893855</v>
+        <v>-0.3422694789292891</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3485255904388538</v>
+        <v>-0.1851982451724155</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4811092276793332</v>
+        <v>-0.2621731527480549</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.487724754700622</v>
+        <v>-0.2423044771483589</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.5667978938468963</v>
+        <v>-0.3523206424675607</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.5731403543404667</v>
+        <v>-0.3875281016566632</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5177992511061191</v>
+        <v>-0.301200413234163</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5688246385920763</v>
+        <v>-0.3208439664286971</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.51028826570208</v>
+        <v>-0.2357281236237796</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4548464279321607</v>
+        <v>-0.1492451114338778</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4640443260583211</v>
+        <v>-0.1584752702161225</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3948325431198967</v>
+        <v>-0.05958181574029453</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3577940484398852</v>
+        <v>0.007918401605444103</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4408383076574722</v>
+        <v>-0.01358238520163013</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4191847041587664</v>
+        <v>0.03935329873493743</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3787878787878753</v>
+        <v>0.05030186308066931</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3443548474151896</v>
+        <v>-0.005998230132618687</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3711054129052584</v>
+        <v>-0.09127354262420084</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3482428510838034</v>
+        <v>-0.008760973097139413</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2339876617973644</v>
+        <v>0.04385668281161514</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1557705708071708</v>
+        <v>0.1229717128621814</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1533015463245988</v>
+        <v>0.09559494135042712</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1926214618357136</v>
+        <v>0.08737345441753774</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.280687567329764</v>
+        <v>-0.05698833221043031</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 88</t>
+          <t>X &lt; 86.96</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3334</v>
+        <v>3358</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2598521774772493</v>
+        <v>-0.3039399490511485</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2807490607686702</v>
+        <v>-0.1494803093765924</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4509007849558486</v>
+        <v>-0.2045179882866961</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4617192223545032</v>
+        <v>-0.159016483815634</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.5721399132859375</v>
+        <v>-0.2404743534439291</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5773305745813033</v>
+        <v>-0.2447757256297436</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4374027766178443</v>
+        <v>-0.134521596033423</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.430059007289131</v>
+        <v>-0.1856142934981193</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.371583016061777</v>
+        <v>-0.07053191729733754</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.321048121250783</v>
+        <v>0.01024214976900595</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3285134382259329</v>
+        <v>0.03256100346843027</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2613410135779759</v>
+        <v>0.0993863799848711</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2311995352510792</v>
+        <v>0.1295302117058412</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3150315031503084</v>
+        <v>0.07689328468747192</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2974072538894319</v>
+        <v>0.09535272693167229</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3434252761003265</v>
+        <v>0.1099150225390275</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3099894433999708</v>
+        <v>0.05332157008420069</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3371973254656879</v>
+        <v>-0.03224746227614617</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3431174876725294</v>
+        <v>0.05114584425595581</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2583838868291508</v>
+        <v>0.07509699813576276</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1539275574224632</v>
+        <v>0.2094952565778172</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1219514755971147</v>
+        <v>0.1223075437071373</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09941014894012312</v>
+        <v>0.1455143223267825</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.157380906996174</v>
+        <v>0.03083301285765572</v>
       </c>
     </row>
   </sheetData>
